--- a/Freight_data.xlsx
+++ b/Freight_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Rake Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9686A9E3-5342-40E3-8423-AB350F974E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716B265A-796D-4990-9818-1A289923334C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4666" uniqueCount="995">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4735" uniqueCount="1008">
   <si>
     <t>ZONE</t>
   </si>
@@ -3021,6 +3021,45 @@
   </si>
   <si>
     <t>SB00DC14F9</t>
+  </si>
+  <si>
+    <t>162006452</t>
+  </si>
+  <si>
+    <t>26080721246</t>
+  </si>
+  <si>
+    <t>9926080915080490</t>
+  </si>
+  <si>
+    <t>SB00DC9781</t>
+  </si>
+  <si>
+    <t>162006453</t>
+  </si>
+  <si>
+    <t>20-08-2026</t>
+  </si>
+  <si>
+    <t>26081220300</t>
+  </si>
+  <si>
+    <t>9926080915080492</t>
+  </si>
+  <si>
+    <t>SB00DC9A81</t>
+  </si>
+  <si>
+    <t>162011721</t>
+  </si>
+  <si>
+    <t>26081323698</t>
+  </si>
+  <si>
+    <t>9926082315080504</t>
+  </si>
+  <si>
+    <t>SB00DC9C5B</t>
   </si>
 </sst>
 </file>
@@ -3399,7 +3438,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AS128"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="11.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
@@ -3420,7 +3459,7 @@
     <col min="45" max="45" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3557,7 +3596,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -3691,7 +3730,7 @@
         <v>5803109</v>
       </c>
     </row>
-    <row r="3" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -3825,7 +3864,7 @@
         <v>5493794</v>
       </c>
     </row>
-    <row r="4" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -3959,7 +3998,7 @@
         <v>5444217</v>
       </c>
     </row>
-    <row r="5" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -4093,7 +4132,7 @@
         <v>5207570</v>
       </c>
     </row>
-    <row r="6" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -4227,7 +4266,7 @@
         <v>5556746</v>
       </c>
     </row>
-    <row r="7" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -4361,7 +4400,7 @@
         <v>5583047</v>
       </c>
     </row>
-    <row r="8" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>45</v>
       </c>
@@ -4495,7 +4534,7 @@
         <v>5379943</v>
       </c>
     </row>
-    <row r="9" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -4629,7 +4668,7 @@
         <v>5316249</v>
       </c>
     </row>
-    <row r="10" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>45</v>
       </c>
@@ -4763,7 +4802,7 @@
         <v>4761492</v>
       </c>
     </row>
-    <row r="11" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -4897,7 +4936,7 @@
         <v>5168470</v>
       </c>
     </row>
-    <row r="12" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -5031,7 +5070,7 @@
         <v>5571233</v>
       </c>
     </row>
-    <row r="13" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -5165,7 +5204,7 @@
         <v>5397085</v>
       </c>
     </row>
-    <row r="14" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -5299,7 +5338,7 @@
         <v>5246130</v>
       </c>
     </row>
-    <row r="15" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>45</v>
       </c>
@@ -5433,7 +5472,7 @@
         <v>5422088</v>
       </c>
     </row>
-    <row r="16" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -5567,7 +5606,7 @@
         <v>5057280</v>
       </c>
     </row>
-    <row r="17" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -5701,7 +5740,7 @@
         <v>5308579</v>
       </c>
     </row>
-    <row r="18" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -5835,7 +5874,7 @@
         <v>5401470</v>
       </c>
     </row>
-    <row r="19" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -5969,7 +6008,7 @@
         <v>5287678</v>
       </c>
     </row>
-    <row r="20" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -6103,7 +6142,7 @@
         <v>5694992</v>
       </c>
     </row>
-    <row r="21" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>45</v>
       </c>
@@ -6237,7 +6276,7 @@
         <v>4962386</v>
       </c>
     </row>
-    <row r="22" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -6371,7 +6410,7 @@
         <v>5000810</v>
       </c>
     </row>
-    <row r="23" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -6505,7 +6544,7 @@
         <v>4757739</v>
       </c>
     </row>
-    <row r="24" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>45</v>
       </c>
@@ -6639,7 +6678,7 @@
         <v>4660020</v>
       </c>
     </row>
-    <row r="25" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>45</v>
       </c>
@@ -6773,7 +6812,7 @@
         <v>4584494</v>
       </c>
     </row>
-    <row r="26" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>45</v>
       </c>
@@ -6907,7 +6946,7 @@
         <v>4414375</v>
       </c>
     </row>
-    <row r="27" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>45</v>
       </c>
@@ -7041,7 +7080,7 @@
         <v>4578513</v>
       </c>
     </row>
-    <row r="28" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>45</v>
       </c>
@@ -7175,7 +7214,7 @@
         <v>4422127</v>
       </c>
     </row>
-    <row r="29" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>45</v>
       </c>
@@ -7309,7 +7348,7 @@
         <v>5368439</v>
       </c>
     </row>
-    <row r="30" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>45</v>
       </c>
@@ -7443,7 +7482,7 @@
         <v>5362250</v>
       </c>
     </row>
-    <row r="31" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>45</v>
       </c>
@@ -7577,7 +7616,7 @@
         <v>5116749</v>
       </c>
     </row>
-    <row r="32" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>45</v>
       </c>
@@ -7711,7 +7750,7 @@
         <v>4819928</v>
       </c>
     </row>
-    <row r="33" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -7845,7 +7884,7 @@
         <v>5459471</v>
       </c>
     </row>
-    <row r="34" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>45</v>
       </c>
@@ -7979,7 +8018,7 @@
         <v>4925144</v>
       </c>
     </row>
-    <row r="35" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>45</v>
       </c>
@@ -8113,7 +8152,7 @@
         <v>5128095</v>
       </c>
     </row>
-    <row r="36" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>45</v>
       </c>
@@ -8247,7 +8286,7 @@
         <v>5424657</v>
       </c>
     </row>
-    <row r="37" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -8381,7 +8420,7 @@
         <v>4879668</v>
       </c>
     </row>
-    <row r="38" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -8515,7 +8554,7 @@
         <v>5457925</v>
       </c>
     </row>
-    <row r="39" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>45</v>
       </c>
@@ -8649,7 +8688,7 @@
         <v>5280281</v>
       </c>
     </row>
-    <row r="40" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -8783,7 +8822,7 @@
         <v>5424141</v>
       </c>
     </row>
-    <row r="41" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -8917,7 +8956,7 @@
         <v>5303197</v>
       </c>
     </row>
-    <row r="42" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -9051,7 +9090,7 @@
         <v>5197208</v>
       </c>
     </row>
-    <row r="43" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -9185,7 +9224,7 @@
         <v>5276100</v>
       </c>
     </row>
-    <row r="44" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>45</v>
       </c>
@@ -9319,7 +9358,7 @@
         <v>5192564</v>
       </c>
     </row>
-    <row r="45" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -9453,7 +9492,7 @@
         <v>5226090</v>
       </c>
     </row>
-    <row r="46" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -9587,7 +9626,7 @@
         <v>4764485</v>
       </c>
     </row>
-    <row r="47" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -9721,7 +9760,7 @@
         <v>4619814</v>
       </c>
     </row>
-    <row r="48" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>45</v>
       </c>
@@ -9855,7 +9894,7 @@
         <v>5062365</v>
       </c>
     </row>
-    <row r="49" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>45</v>
       </c>
@@ -9989,7 +10028,7 @@
         <v>5144947</v>
       </c>
     </row>
-    <row r="50" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>45</v>
       </c>
@@ -10123,7 +10162,7 @@
         <v>5196289</v>
       </c>
     </row>
-    <row r="51" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>45</v>
       </c>
@@ -10257,7 +10296,7 @@
         <v>5324810</v>
       </c>
     </row>
-    <row r="52" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -10391,7 +10430,7 @@
         <v>4800588</v>
       </c>
     </row>
-    <row r="53" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -10525,7 +10564,7 @@
         <v>5349479</v>
       </c>
     </row>
-    <row r="54" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>45</v>
       </c>
@@ -10659,7 +10698,7 @@
         <v>5346262</v>
       </c>
     </row>
-    <row r="55" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>45</v>
       </c>
@@ -10793,7 +10832,7 @@
         <v>5203145</v>
       </c>
     </row>
-    <row r="56" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>45</v>
       </c>
@@ -10927,7 +10966,7 @@
         <v>5299902</v>
       </c>
     </row>
-    <row r="57" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>45</v>
       </c>
@@ -11061,7 +11100,7 @@
         <v>4659889</v>
       </c>
     </row>
-    <row r="58" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>45</v>
       </c>
@@ -11195,7 +11234,7 @@
         <v>5252234</v>
       </c>
     </row>
-    <row r="59" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>45</v>
       </c>
@@ -11329,7 +11368,7 @@
         <v>5203306</v>
       </c>
     </row>
-    <row r="60" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>45</v>
       </c>
@@ -11463,7 +11502,7 @@
         <v>5244294</v>
       </c>
     </row>
-    <row r="61" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>45</v>
       </c>
@@ -11597,7 +11636,7 @@
         <v>4986257</v>
       </c>
     </row>
-    <row r="62" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>45</v>
       </c>
@@ -11731,7 +11770,7 @@
         <v>5263281</v>
       </c>
     </row>
-    <row r="63" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>45</v>
       </c>
@@ -11865,7 +11904,7 @@
         <v>5110834</v>
       </c>
     </row>
-    <row r="64" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>45</v>
       </c>
@@ -11999,7 +12038,7 @@
         <v>5012800</v>
       </c>
     </row>
-    <row r="65" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>45</v>
       </c>
@@ -12133,7 +12172,7 @@
         <v>4982491</v>
       </c>
     </row>
-    <row r="66" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>45</v>
       </c>
@@ -12267,7 +12306,7 @@
         <v>5240887</v>
       </c>
     </row>
-    <row r="67" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>45</v>
       </c>
@@ -12401,7 +12440,7 @@
         <v>5106153</v>
       </c>
     </row>
-    <row r="68" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>45</v>
       </c>
@@ -12535,7 +12574,7 @@
         <v>5192532</v>
       </c>
     </row>
-    <row r="69" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>45</v>
       </c>
@@ -12669,7 +12708,7 @@
         <v>5150085</v>
       </c>
     </row>
-    <row r="70" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>45</v>
       </c>
@@ -12803,7 +12842,7 @@
         <v>5134778</v>
       </c>
     </row>
-    <row r="71" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>45</v>
       </c>
@@ -12937,7 +12976,7 @@
         <v>5123332</v>
       </c>
     </row>
-    <row r="72" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>45</v>
       </c>
@@ -13071,7 +13110,7 @@
         <v>4987420</v>
       </c>
     </row>
-    <row r="73" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>45</v>
       </c>
@@ -13205,7 +13244,7 @@
         <v>5372732</v>
       </c>
     </row>
-    <row r="74" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>45</v>
       </c>
@@ -13339,7 +13378,7 @@
         <v>5404531</v>
       </c>
     </row>
-    <row r="75" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>45</v>
       </c>
@@ -13473,7 +13512,7 @@
         <v>5195228</v>
       </c>
     </row>
-    <row r="76" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>45</v>
       </c>
@@ -13607,7 +13646,7 @@
         <v>5168302</v>
       </c>
     </row>
-    <row r="77" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>45</v>
       </c>
@@ -13741,7 +13780,7 @@
         <v>5169839</v>
       </c>
     </row>
-    <row r="78" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>45</v>
       </c>
@@ -13875,7 +13914,7 @@
         <v>5204663</v>
       </c>
     </row>
-    <row r="79" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>45</v>
       </c>
@@ -14009,7 +14048,7 @@
         <v>5224764</v>
       </c>
     </row>
-    <row r="80" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>45</v>
       </c>
@@ -14143,7 +14182,7 @@
         <v>5173281</v>
       </c>
     </row>
-    <row r="81" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>45</v>
       </c>
@@ -14277,7 +14316,7 @@
         <v>5239788</v>
       </c>
     </row>
-    <row r="82" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>45</v>
       </c>
@@ -14411,7 +14450,7 @@
         <v>5087070</v>
       </c>
     </row>
-    <row r="83" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>45</v>
       </c>
@@ -14545,7 +14584,7 @@
         <v>5264878</v>
       </c>
     </row>
-    <row r="84" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>45</v>
       </c>
@@ -14679,7 +14718,7 @@
         <v>5281103</v>
       </c>
     </row>
-    <row r="85" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>45</v>
       </c>
@@ -14813,7 +14852,7 @@
         <v>4967024</v>
       </c>
     </row>
-    <row r="86" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>45</v>
       </c>
@@ -14947,7 +14986,7 @@
         <v>5141135</v>
       </c>
     </row>
-    <row r="87" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>45</v>
       </c>
@@ -15081,7 +15120,7 @@
         <v>5245013</v>
       </c>
     </row>
-    <row r="88" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>45</v>
       </c>
@@ -15215,7 +15254,7 @@
         <v>5263201</v>
       </c>
     </row>
-    <row r="89" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>45</v>
       </c>
@@ -15349,7 +15388,7 @@
         <v>5059829</v>
       </c>
     </row>
-    <row r="90" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>45</v>
       </c>
@@ -15483,7 +15522,7 @@
         <v>5312445</v>
       </c>
     </row>
-    <row r="91" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>45</v>
       </c>
@@ -15617,7 +15656,7 @@
         <v>5287735</v>
       </c>
     </row>
-    <row r="92" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>45</v>
       </c>
@@ -15751,7 +15790,7 @@
         <v>5324222</v>
       </c>
     </row>
-    <row r="93" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>45</v>
       </c>
@@ -15885,7 +15924,7 @@
         <v>5130784</v>
       </c>
     </row>
-    <row r="94" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>45</v>
       </c>
@@ -16019,7 +16058,7 @@
         <v>5322777</v>
       </c>
     </row>
-    <row r="95" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>45</v>
       </c>
@@ -16153,7 +16192,7 @@
         <v>5167265</v>
       </c>
     </row>
-    <row r="96" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>45</v>
       </c>
@@ -16287,7 +16326,7 @@
         <v>4903007</v>
       </c>
     </row>
-    <row r="97" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>45</v>
       </c>
@@ -16421,7 +16460,7 @@
         <v>4785605</v>
       </c>
     </row>
-    <row r="98" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>45</v>
       </c>
@@ -16555,7 +16594,7 @@
         <v>6080998</v>
       </c>
     </row>
-    <row r="99" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>45</v>
       </c>
@@ -16689,7 +16728,7 @@
         <v>5391966</v>
       </c>
     </row>
-    <row r="100" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>45</v>
       </c>
@@ -16823,7 +16862,7 @@
         <v>5341899</v>
       </c>
     </row>
-    <row r="101" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>45</v>
       </c>
@@ -16957,7 +16996,7 @@
         <v>5259890</v>
       </c>
     </row>
-    <row r="102" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>45</v>
       </c>
@@ -17091,7 +17130,7 @@
         <v>5493117</v>
       </c>
     </row>
-    <row r="103" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>45</v>
       </c>
@@ -17225,7 +17264,7 @@
         <v>5484814</v>
       </c>
     </row>
-    <row r="104" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>45</v>
       </c>
@@ -17359,7 +17398,7 @@
         <v>5599431</v>
       </c>
     </row>
-    <row r="105" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>45</v>
       </c>
@@ -17493,7 +17532,7 @@
         <v>5620112</v>
       </c>
     </row>
-    <row r="106" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>45</v>
       </c>
@@ -17627,7 +17666,7 @@
         <v>5418272</v>
       </c>
     </row>
-    <row r="107" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>45</v>
       </c>
@@ -17761,7 +17800,7 @@
         <v>5655376</v>
       </c>
     </row>
-    <row r="108" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>45</v>
       </c>
@@ -17895,7 +17934,7 @@
         <v>5266955</v>
       </c>
     </row>
-    <row r="109" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>45</v>
       </c>
@@ -18029,7 +18068,7 @@
         <v>4703825</v>
       </c>
     </row>
-    <row r="110" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>45</v>
       </c>
@@ -18163,7 +18202,7 @@
         <v>5549702</v>
       </c>
     </row>
-    <row r="111" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>45</v>
       </c>
@@ -18297,7 +18336,7 @@
         <v>5334524</v>
       </c>
     </row>
-    <row r="112" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>45</v>
       </c>
@@ -18431,7 +18470,7 @@
         <v>5319563</v>
       </c>
     </row>
-    <row r="113" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>45</v>
       </c>
@@ -18565,7 +18604,7 @@
         <v>4537979</v>
       </c>
     </row>
-    <row r="114" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>45</v>
       </c>
@@ -18699,7 +18738,7 @@
         <v>5515294</v>
       </c>
     </row>
-    <row r="115" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>45</v>
       </c>
@@ -18833,7 +18872,7 @@
         <v>5242874</v>
       </c>
     </row>
-    <row r="116" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>45</v>
       </c>
@@ -18967,7 +19006,7 @@
         <v>5502318</v>
       </c>
     </row>
-    <row r="117" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>45</v>
       </c>
@@ -19101,7 +19140,7 @@
         <v>5280861</v>
       </c>
     </row>
-    <row r="118" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>45</v>
       </c>
@@ -19235,7 +19274,7 @@
         <v>5186501</v>
       </c>
     </row>
-    <row r="119" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>45</v>
       </c>
@@ -19369,7 +19408,7 @@
         <v>5350766</v>
       </c>
     </row>
-    <row r="120" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>45</v>
       </c>
@@ -19503,7 +19542,7 @@
         <v>5380151</v>
       </c>
     </row>
-    <row r="121" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>45</v>
       </c>
@@ -19637,7 +19676,7 @@
         <v>5378496</v>
       </c>
     </row>
-    <row r="122" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>45</v>
       </c>
@@ -19771,7 +19810,7 @@
         <v>5401622</v>
       </c>
     </row>
-    <row r="123" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>45</v>
       </c>
@@ -19905,7 +19944,7 @@
         <v>5462572</v>
       </c>
     </row>
-    <row r="124" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>45</v>
       </c>
@@ -20039,7 +20078,7 @@
         <v>5515383</v>
       </c>
     </row>
-    <row r="125" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>45</v>
       </c>
@@ -20173,7 +20212,7 @@
         <v>5535083</v>
       </c>
     </row>
-    <row r="126" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>45</v>
       </c>
@@ -20307,7 +20346,7 @@
         <v>5803836</v>
       </c>
     </row>
-    <row r="127" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>45</v>
       </c>
@@ -20441,7 +20480,7 @@
         <v>5670591</v>
       </c>
     </row>
-    <row r="128" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>45</v>
       </c>
@@ -20586,7 +20625,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C78B9EE1-1D80-475C-BF5D-33B3ADA7B761}">
-  <dimension ref="A1:AR73"/>
+  <dimension ref="A1:AR76"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="11.83203125" customWidth="1"/>
@@ -23370,19 +23409,19 @@
         <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>357</v>
+        <v>219</v>
       </c>
       <c r="D22" t="s">
         <v>48</v>
       </c>
       <c r="E22" t="s">
-        <v>776</v>
+        <v>995</v>
       </c>
       <c r="F22" t="s">
-        <v>664</v>
+        <v>909</v>
       </c>
       <c r="G22" t="s">
-        <v>777</v>
+        <v>996</v>
       </c>
       <c r="H22" t="s">
         <v>52</v>
@@ -23394,13 +23433,13 @@
         <v>54</v>
       </c>
       <c r="K22" t="s">
-        <v>309</v>
+        <v>869</v>
       </c>
       <c r="L22" t="s">
-        <v>664</v>
+        <v>909</v>
       </c>
       <c r="M22" t="s">
-        <v>368</v>
+        <v>56</v>
       </c>
       <c r="N22" t="s">
         <v>57</v>
@@ -23409,28 +23448,28 @@
         <v>58</v>
       </c>
       <c r="P22" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="Q22" t="s">
         <v>60</v>
       </c>
       <c r="R22" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S22" t="s">
         <v>61</v>
       </c>
       <c r="T22" t="s">
-        <v>778</v>
+        <v>997</v>
       </c>
       <c r="U22" s="1">
-        <v>3845.4</v>
+        <v>3703.4</v>
       </c>
       <c r="V22" s="1">
-        <v>3826.8</v>
+        <v>3701.6</v>
       </c>
       <c r="W22" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X22" s="1">
         <v>0</v>
@@ -23442,55 +23481,55 @@
         <v>1228</v>
       </c>
       <c r="AA22" s="1">
-        <v>4722151.2</v>
+        <v>4547775.2</v>
       </c>
       <c r="AB22" s="1">
-        <v>0</v>
+        <v>11052</v>
       </c>
       <c r="AC22" s="1">
-        <v>4907240</v>
+        <v>4868766</v>
       </c>
       <c r="AD22" s="1">
-        <v>25200</v>
+        <v>7950</v>
       </c>
       <c r="AE22" s="1">
-        <v>0</v>
+        <v>23850</v>
       </c>
       <c r="AF22" t="s">
         <v>64</v>
       </c>
       <c r="AH22" t="s">
-        <v>779</v>
+        <v>998</v>
       </c>
       <c r="AI22" s="1">
-        <v>0</v>
+        <v>7950</v>
       </c>
       <c r="AJ22" s="1">
-        <v>0</v>
+        <v>35480</v>
       </c>
       <c r="AK22" s="1">
-        <v>0</v>
+        <v>11052</v>
       </c>
       <c r="AL22" s="1">
-        <v>0</v>
+        <v>11052</v>
       </c>
       <c r="AM22" s="1">
-        <v>78648</v>
+        <v>78056</v>
       </c>
       <c r="AN22" s="1">
-        <v>106440</v>
+        <v>177400</v>
       </c>
       <c r="AO22" s="1">
-        <v>245362</v>
+        <v>243439</v>
       </c>
       <c r="AP22" s="1">
-        <v>185088</v>
+        <v>320990</v>
       </c>
       <c r="AQ22" s="1">
-        <v>5152602</v>
+        <v>5112205</v>
       </c>
       <c r="AR22" s="1">
-        <v>5177802</v>
+        <v>5144005</v>
       </c>
     </row>
     <row r="23" spans="1:44" x14ac:dyDescent="0.35">
@@ -23501,19 +23540,19 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>357</v>
+        <v>219</v>
       </c>
       <c r="D23" t="s">
         <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>780</v>
+        <v>999</v>
       </c>
       <c r="F23" t="s">
-        <v>664</v>
+        <v>1000</v>
       </c>
       <c r="G23" t="s">
-        <v>781</v>
+        <v>1001</v>
       </c>
       <c r="H23" t="s">
         <v>52</v>
@@ -23525,13 +23564,13 @@
         <v>54</v>
       </c>
       <c r="K23" t="s">
-        <v>315</v>
+        <v>874</v>
       </c>
       <c r="L23" t="s">
-        <v>664</v>
+        <v>1000</v>
       </c>
       <c r="M23" t="s">
-        <v>368</v>
+        <v>56</v>
       </c>
       <c r="N23" t="s">
         <v>57</v>
@@ -23540,7 +23579,7 @@
         <v>58</v>
       </c>
       <c r="P23" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="Q23" t="s">
         <v>60</v>
@@ -23552,16 +23591,16 @@
         <v>61</v>
       </c>
       <c r="T23" t="s">
-        <v>782</v>
+        <v>1002</v>
       </c>
       <c r="U23" s="1">
-        <v>3784.4</v>
+        <v>3912.2</v>
       </c>
       <c r="V23" s="1">
-        <v>3769.4</v>
+        <v>3910.8</v>
       </c>
       <c r="W23" s="1">
-        <v>0.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="X23" s="1">
         <v>0</v>
@@ -23573,25 +23612,25 @@
         <v>1228</v>
       </c>
       <c r="AA23" s="1">
-        <v>4647243.2</v>
+        <v>4804181.5999999996</v>
       </c>
       <c r="AB23" s="1">
-        <v>491.2</v>
+        <v>16209.6</v>
       </c>
       <c r="AC23" s="1">
-        <v>4736435</v>
+        <v>5075848</v>
       </c>
       <c r="AD23" s="1">
-        <v>16500</v>
+        <v>8400</v>
       </c>
       <c r="AE23" s="1">
-        <v>0</v>
+        <v>59640</v>
       </c>
       <c r="AF23" t="s">
         <v>64</v>
       </c>
       <c r="AH23" t="s">
-        <v>783</v>
+        <v>1003</v>
       </c>
       <c r="AI23" s="1">
         <v>0</v>
@@ -23603,25 +23642,25 @@
         <v>0</v>
       </c>
       <c r="AL23" s="1">
-        <v>491.2</v>
+        <v>16209.6</v>
       </c>
       <c r="AM23" s="1">
-        <v>0</v>
+        <v>78056</v>
       </c>
       <c r="AN23" s="1">
-        <v>88700</v>
+        <v>177400</v>
       </c>
       <c r="AO23" s="1">
-        <v>236822</v>
+        <v>253793</v>
       </c>
       <c r="AP23" s="1">
-        <v>89191.2</v>
+        <v>271665.59999999998</v>
       </c>
       <c r="AQ23" s="1">
-        <v>4973257</v>
+        <v>5329641</v>
       </c>
       <c r="AR23" s="1">
-        <v>4989757</v>
+        <v>5397681</v>
       </c>
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.35">
@@ -23638,13 +23677,13 @@
         <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="F24" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="G24" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="H24" t="s">
         <v>52</v>
@@ -23656,10 +23695,10 @@
         <v>54</v>
       </c>
       <c r="K24" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="L24" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="M24" t="s">
         <v>368</v>
@@ -23677,19 +23716,19 @@
         <v>60</v>
       </c>
       <c r="R24" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="S24" t="s">
         <v>61</v>
       </c>
       <c r="T24" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="U24" s="1">
-        <v>4062.6</v>
+        <v>3845.4</v>
       </c>
       <c r="V24" s="1">
-        <v>4049.8</v>
+        <v>3826.8</v>
       </c>
       <c r="W24" s="1">
         <v>0</v>
@@ -23704,25 +23743,25 @@
         <v>1228</v>
       </c>
       <c r="AA24" s="1">
-        <v>4988872.8</v>
+        <v>4722151.2</v>
       </c>
       <c r="AB24" s="1">
         <v>0</v>
       </c>
       <c r="AC24" s="1">
-        <v>5041553</v>
+        <v>4907240</v>
       </c>
       <c r="AD24" s="1">
-        <v>0</v>
+        <v>25200</v>
       </c>
       <c r="AE24" s="1">
-        <v>35400</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="s">
         <v>64</v>
       </c>
       <c r="AH24" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="AI24" s="1">
         <v>0</v>
@@ -23737,22 +23776,22 @@
         <v>0</v>
       </c>
       <c r="AM24" s="1">
-        <v>0</v>
+        <v>78648</v>
       </c>
       <c r="AN24" s="1">
-        <v>52680</v>
+        <v>106440</v>
       </c>
       <c r="AO24" s="1">
-        <v>252078</v>
+        <v>245362</v>
       </c>
       <c r="AP24" s="1">
-        <v>52680</v>
+        <v>185088</v>
       </c>
       <c r="AQ24" s="1">
-        <v>5293631</v>
+        <v>5152602</v>
       </c>
       <c r="AR24" s="1">
-        <v>5329031</v>
+        <v>5177802</v>
       </c>
     </row>
     <row r="25" spans="1:44" x14ac:dyDescent="0.35">
@@ -23769,13 +23808,13 @@
         <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="F25" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="G25" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="H25" t="s">
         <v>52</v>
@@ -23787,10 +23826,10 @@
         <v>54</v>
       </c>
       <c r="K25" t="s">
-        <v>666</v>
+        <v>315</v>
       </c>
       <c r="L25" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="M25" t="s">
         <v>368</v>
@@ -23814,16 +23853,16 @@
         <v>61</v>
       </c>
       <c r="T25" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="U25" s="1">
-        <v>4060.4</v>
+        <v>3784.4</v>
       </c>
       <c r="V25" s="1">
-        <v>4044.5</v>
+        <v>3769.4</v>
       </c>
       <c r="W25" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="X25" s="1">
         <v>0</v>
@@ -23835,25 +23874,25 @@
         <v>1228</v>
       </c>
       <c r="AA25" s="1">
-        <v>4986171.2</v>
+        <v>4647243.2</v>
       </c>
       <c r="AB25" s="1">
-        <v>0</v>
+        <v>491.2</v>
       </c>
       <c r="AC25" s="1">
-        <v>5092612</v>
+        <v>4736435</v>
       </c>
       <c r="AD25" s="1">
-        <v>26550</v>
+        <v>16500</v>
       </c>
       <c r="AE25" s="1">
-        <v>26550</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="s">
         <v>64</v>
       </c>
       <c r="AH25" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="AI25" s="1">
         <v>0</v>
@@ -23865,25 +23904,25 @@
         <v>0</v>
       </c>
       <c r="AL25" s="1">
-        <v>0</v>
+        <v>491.2</v>
       </c>
       <c r="AM25" s="1">
         <v>0</v>
       </c>
       <c r="AN25" s="1">
-        <v>106440</v>
+        <v>88700</v>
       </c>
       <c r="AO25" s="1">
-        <v>254631</v>
+        <v>236822</v>
       </c>
       <c r="AP25" s="1">
-        <v>106440</v>
+        <v>89191.2</v>
       </c>
       <c r="AQ25" s="1">
-        <v>5347243</v>
+        <v>4973257</v>
       </c>
       <c r="AR25" s="1">
-        <v>5400343</v>
+        <v>4989757</v>
       </c>
     </row>
     <row r="26" spans="1:44" x14ac:dyDescent="0.35">
@@ -23900,13 +23939,13 @@
         <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="F26" t="s">
         <v>680</v>
       </c>
       <c r="G26" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="H26" t="s">
         <v>52</v>
@@ -23918,7 +23957,7 @@
         <v>54</v>
       </c>
       <c r="K26" t="s">
-        <v>671</v>
+        <v>321</v>
       </c>
       <c r="L26" t="s">
         <v>680</v>
@@ -23945,13 +23984,13 @@
         <v>61</v>
       </c>
       <c r="T26" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="U26" s="1">
-        <v>3705.2</v>
+        <v>4062.6</v>
       </c>
       <c r="V26" s="1">
-        <v>3684.6</v>
+        <v>4049.8</v>
       </c>
       <c r="W26" s="1">
         <v>0</v>
@@ -23966,25 +24005,25 @@
         <v>1228</v>
       </c>
       <c r="AA26" s="1">
-        <v>4549985.5999999996</v>
+        <v>4988872.8</v>
       </c>
       <c r="AB26" s="1">
         <v>0</v>
       </c>
       <c r="AC26" s="1">
-        <v>4603206</v>
+        <v>5041553</v>
       </c>
       <c r="AD26" s="1">
         <v>0</v>
       </c>
       <c r="AE26" s="1">
-        <v>16200</v>
+        <v>35400</v>
       </c>
       <c r="AF26" t="s">
         <v>64</v>
       </c>
       <c r="AH26" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="AI26" s="1">
         <v>0</v>
@@ -24002,19 +24041,19 @@
         <v>0</v>
       </c>
       <c r="AN26" s="1">
-        <v>53220</v>
+        <v>52680</v>
       </c>
       <c r="AO26" s="1">
-        <v>230161</v>
+        <v>252078</v>
       </c>
       <c r="AP26" s="1">
-        <v>53220</v>
+        <v>52680</v>
       </c>
       <c r="AQ26" s="1">
-        <v>4833367</v>
+        <v>5293631</v>
       </c>
       <c r="AR26" s="1">
-        <v>4849567</v>
+        <v>5329031</v>
       </c>
     </row>
     <row r="27" spans="1:44" x14ac:dyDescent="0.35">
@@ -24031,13 +24070,13 @@
         <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="F27" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="G27" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="H27" t="s">
         <v>52</v>
@@ -24049,10 +24088,10 @@
         <v>54</v>
       </c>
       <c r="K27" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="L27" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="M27" t="s">
         <v>368</v>
@@ -24070,19 +24109,19 @@
         <v>60</v>
       </c>
       <c r="R27" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S27" t="s">
         <v>61</v>
       </c>
       <c r="T27" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="U27" s="1">
-        <v>4050.4</v>
+        <v>4060.4</v>
       </c>
       <c r="V27" s="1">
-        <v>4031</v>
+        <v>4044.5</v>
       </c>
       <c r="W27" s="1">
         <v>0</v>
@@ -24097,25 +24136,25 @@
         <v>1228</v>
       </c>
       <c r="AA27" s="1">
-        <v>4973891.2</v>
+        <v>4986171.2</v>
       </c>
       <c r="AB27" s="1">
         <v>0</v>
       </c>
       <c r="AC27" s="1">
-        <v>5027652</v>
+        <v>5092612</v>
       </c>
       <c r="AD27" s="1">
-        <v>0</v>
+        <v>26550</v>
       </c>
       <c r="AE27" s="1">
-        <v>0</v>
+        <v>26550</v>
       </c>
       <c r="AF27" t="s">
         <v>64</v>
       </c>
       <c r="AH27" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="AI27" s="1">
         <v>0</v>
@@ -24124,7 +24163,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="1">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="AL27" s="1">
         <v>0</v>
@@ -24133,19 +24172,19 @@
         <v>0</v>
       </c>
       <c r="AN27" s="1">
-        <v>53220</v>
+        <v>106440</v>
       </c>
       <c r="AO27" s="1">
-        <v>251383</v>
+        <v>254631</v>
       </c>
       <c r="AP27" s="1">
-        <v>53760</v>
+        <v>106440</v>
       </c>
       <c r="AQ27" s="1">
-        <v>5279035</v>
+        <v>5347243</v>
       </c>
       <c r="AR27" s="1">
-        <v>5279035</v>
+        <v>5400343</v>
       </c>
     </row>
     <row r="28" spans="1:44" x14ac:dyDescent="0.35">
@@ -24162,13 +24201,13 @@
         <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="F28" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="G28" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="H28" t="s">
         <v>52</v>
@@ -24180,10 +24219,10 @@
         <v>54</v>
       </c>
       <c r="K28" t="s">
-        <v>682</v>
+        <v>671</v>
       </c>
       <c r="L28" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="M28" t="s">
         <v>368</v>
@@ -24201,22 +24240,22 @@
         <v>60</v>
       </c>
       <c r="R28" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S28" t="s">
         <v>61</v>
       </c>
       <c r="T28" t="s">
-        <v>694</v>
+        <v>794</v>
       </c>
       <c r="U28" s="1">
-        <v>3440.8</v>
+        <v>3705.2</v>
       </c>
       <c r="V28" s="1">
-        <v>3429.5</v>
+        <v>3684.6</v>
       </c>
       <c r="W28" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="X28" s="1">
         <v>0</v>
@@ -24228,25 +24267,25 @@
         <v>1228</v>
       </c>
       <c r="AA28" s="1">
-        <v>4225302.4000000004</v>
+        <v>4549985.5999999996</v>
       </c>
       <c r="AB28" s="1">
-        <v>491.2</v>
+        <v>0</v>
       </c>
       <c r="AC28" s="1">
-        <v>4302994</v>
+        <v>4603206</v>
       </c>
       <c r="AD28" s="1">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="AE28" s="1">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="AF28" t="s">
         <v>64</v>
       </c>
       <c r="AH28" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="AI28" s="1">
         <v>0</v>
@@ -24258,25 +24297,25 @@
         <v>0</v>
       </c>
       <c r="AL28" s="1">
-        <v>491.2</v>
+        <v>0</v>
       </c>
       <c r="AM28" s="1">
         <v>0</v>
       </c>
       <c r="AN28" s="1">
-        <v>77200</v>
+        <v>53220</v>
       </c>
       <c r="AO28" s="1">
-        <v>215150</v>
+        <v>230161</v>
       </c>
       <c r="AP28" s="1">
-        <v>77691.199999999997</v>
+        <v>53220</v>
       </c>
       <c r="AQ28" s="1">
-        <v>4518144</v>
+        <v>4833367</v>
       </c>
       <c r="AR28" s="1">
-        <v>4533144</v>
+        <v>4849567</v>
       </c>
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.35">
@@ -24293,13 +24332,13 @@
         <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="F29" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="G29" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="H29" t="s">
         <v>52</v>
@@ -24311,10 +24350,10 @@
         <v>54</v>
       </c>
       <c r="K29" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="L29" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="M29" t="s">
         <v>368</v>
@@ -24332,19 +24371,19 @@
         <v>60</v>
       </c>
       <c r="R29" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="S29" t="s">
         <v>61</v>
       </c>
       <c r="T29" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="U29" s="1">
-        <v>3916.8</v>
+        <v>4050.4</v>
       </c>
       <c r="V29" s="1">
-        <v>3907.2</v>
+        <v>4031</v>
       </c>
       <c r="W29" s="1">
         <v>0</v>
@@ -24359,25 +24398,25 @@
         <v>1228</v>
       </c>
       <c r="AA29" s="1">
-        <v>4809830.4000000004</v>
+        <v>4973891.2</v>
       </c>
       <c r="AB29" s="1">
         <v>0</v>
       </c>
       <c r="AC29" s="1">
-        <v>4987231</v>
+        <v>5027652</v>
       </c>
       <c r="AD29" s="1">
-        <v>60705</v>
+        <v>0</v>
       </c>
       <c r="AE29" s="1">
-        <v>60705</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="s">
         <v>64</v>
       </c>
       <c r="AH29" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="AI29" s="1">
         <v>0</v>
@@ -24386,7 +24425,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="1">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="AL29" s="1">
         <v>0</v>
@@ -24395,19 +24434,19 @@
         <v>0</v>
       </c>
       <c r="AN29" s="1">
-        <v>177400</v>
+        <v>53220</v>
       </c>
       <c r="AO29" s="1">
-        <v>249362</v>
+        <v>251383</v>
       </c>
       <c r="AP29" s="1">
-        <v>177400</v>
+        <v>53760</v>
       </c>
       <c r="AQ29" s="1">
-        <v>5236593</v>
+        <v>5279035</v>
       </c>
       <c r="AR29" s="1">
-        <v>5358003</v>
+        <v>5279035</v>
       </c>
     </row>
     <row r="30" spans="1:44" x14ac:dyDescent="0.35">
@@ -24424,13 +24463,13 @@
         <v>48</v>
       </c>
       <c r="E30" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="F30" t="s">
-        <v>708</v>
+        <v>686</v>
       </c>
       <c r="G30" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="H30" t="s">
         <v>52</v>
@@ -24442,10 +24481,10 @@
         <v>54</v>
       </c>
       <c r="K30" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="L30" t="s">
-        <v>708</v>
+        <v>686</v>
       </c>
       <c r="M30" t="s">
         <v>368</v>
@@ -24463,22 +24502,22 @@
         <v>60</v>
       </c>
       <c r="R30" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="S30" t="s">
         <v>61</v>
       </c>
       <c r="T30" t="s">
-        <v>716</v>
+        <v>694</v>
       </c>
       <c r="U30" s="1">
-        <v>3569.6</v>
+        <v>3440.8</v>
       </c>
       <c r="V30" s="1">
-        <v>3551.4</v>
+        <v>3429.5</v>
       </c>
       <c r="W30" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="X30" s="1">
         <v>0</v>
@@ -24490,25 +24529,25 @@
         <v>1228</v>
       </c>
       <c r="AA30" s="1">
-        <v>4383468.8</v>
+        <v>4225302.4000000004</v>
       </c>
       <c r="AB30" s="1">
-        <v>0</v>
+        <v>491.2</v>
       </c>
       <c r="AC30" s="1">
-        <v>4596349</v>
+        <v>4302994</v>
       </c>
       <c r="AD30" s="1">
-        <v>81120</v>
+        <v>15000</v>
       </c>
       <c r="AE30" s="1">
-        <v>89700</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="s">
         <v>64</v>
       </c>
       <c r="AH30" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="AI30" s="1">
         <v>0</v>
@@ -24520,25 +24559,25 @@
         <v>0</v>
       </c>
       <c r="AL30" s="1">
-        <v>0</v>
+        <v>491.2</v>
       </c>
       <c r="AM30" s="1">
         <v>0</v>
       </c>
       <c r="AN30" s="1">
-        <v>212880</v>
+        <v>77200</v>
       </c>
       <c r="AO30" s="1">
-        <v>229818</v>
+        <v>215150</v>
       </c>
       <c r="AP30" s="1">
-        <v>212880</v>
+        <v>77691.199999999997</v>
       </c>
       <c r="AQ30" s="1">
-        <v>4826167</v>
+        <v>4518144</v>
       </c>
       <c r="AR30" s="1">
-        <v>4996987</v>
+        <v>4533144</v>
       </c>
     </row>
     <row r="31" spans="1:44" x14ac:dyDescent="0.35">
@@ -24555,13 +24594,13 @@
         <v>48</v>
       </c>
       <c r="E31" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="F31" t="s">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="G31" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="H31" t="s">
         <v>52</v>
@@ -24573,13 +24612,13 @@
         <v>54</v>
       </c>
       <c r="K31" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="L31" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="M31" t="s">
-        <v>212</v>
+        <v>368</v>
       </c>
       <c r="N31" t="s">
         <v>57</v>
@@ -24600,13 +24639,13 @@
         <v>61</v>
       </c>
       <c r="T31" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="U31" s="1">
-        <v>3854.8</v>
+        <v>3916.8</v>
       </c>
       <c r="V31" s="1">
-        <v>3841.9</v>
+        <v>3907.2</v>
       </c>
       <c r="W31" s="1">
         <v>0</v>
@@ -24621,25 +24660,25 @@
         <v>1228</v>
       </c>
       <c r="AA31" s="1">
-        <v>4733694.4000000004</v>
+        <v>4809830.4000000004</v>
       </c>
       <c r="AB31" s="1">
         <v>0</v>
       </c>
       <c r="AC31" s="1">
-        <v>4875615</v>
+        <v>4987231</v>
       </c>
       <c r="AD31" s="1">
-        <v>50400</v>
+        <v>60705</v>
       </c>
       <c r="AE31" s="1">
-        <v>87360</v>
+        <v>60705</v>
       </c>
       <c r="AF31" t="s">
         <v>64</v>
       </c>
       <c r="AH31" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="AI31" s="1">
         <v>0</v>
@@ -24657,19 +24696,19 @@
         <v>0</v>
       </c>
       <c r="AN31" s="1">
-        <v>141920</v>
+        <v>177400</v>
       </c>
       <c r="AO31" s="1">
-        <v>243781</v>
+        <v>249362</v>
       </c>
       <c r="AP31" s="1">
-        <v>141920</v>
+        <v>177400</v>
       </c>
       <c r="AQ31" s="1">
-        <v>5119396</v>
+        <v>5236593</v>
       </c>
       <c r="AR31" s="1">
-        <v>5257156</v>
+        <v>5358003</v>
       </c>
     </row>
     <row r="32" spans="1:44" x14ac:dyDescent="0.35">
@@ -24686,13 +24725,13 @@
         <v>48</v>
       </c>
       <c r="E32" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="F32" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="G32" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="H32" t="s">
         <v>52</v>
@@ -24704,10 +24743,10 @@
         <v>54</v>
       </c>
       <c r="K32" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="L32" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="M32" t="s">
         <v>368</v>
@@ -24731,13 +24770,13 @@
         <v>61</v>
       </c>
       <c r="T32" t="s">
-        <v>816</v>
+        <v>716</v>
       </c>
       <c r="U32" s="1">
-        <v>3990.4</v>
+        <v>3569.6</v>
       </c>
       <c r="V32" s="1">
-        <v>3973.8</v>
+        <v>3551.4</v>
       </c>
       <c r="W32" s="1">
         <v>0</v>
@@ -24752,25 +24791,25 @@
         <v>1228</v>
       </c>
       <c r="AA32" s="1">
-        <v>4900211.2</v>
+        <v>4383468.8</v>
       </c>
       <c r="AB32" s="1">
         <v>0</v>
       </c>
       <c r="AC32" s="1">
-        <v>5042132</v>
+        <v>4596349</v>
       </c>
       <c r="AD32" s="1">
-        <v>43500</v>
+        <v>81120</v>
       </c>
       <c r="AE32" s="1">
-        <v>26100</v>
+        <v>89700</v>
       </c>
       <c r="AF32" t="s">
         <v>64</v>
       </c>
       <c r="AH32" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="AI32" s="1">
         <v>0</v>
@@ -24788,19 +24827,19 @@
         <v>0</v>
       </c>
       <c r="AN32" s="1">
-        <v>141920</v>
+        <v>212880</v>
       </c>
       <c r="AO32" s="1">
-        <v>252107</v>
+        <v>229818</v>
       </c>
       <c r="AP32" s="1">
-        <v>141920</v>
+        <v>212880</v>
       </c>
       <c r="AQ32" s="1">
-        <v>5294239</v>
+        <v>4826167</v>
       </c>
       <c r="AR32" s="1">
-        <v>5363839</v>
+        <v>4996987</v>
       </c>
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.35">
@@ -24817,13 +24856,13 @@
         <v>48</v>
       </c>
       <c r="E33" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="F33" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="G33" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="H33" t="s">
         <v>52</v>
@@ -24835,13 +24874,13 @@
         <v>54</v>
       </c>
       <c r="K33" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="L33" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="M33" t="s">
-        <v>368</v>
+        <v>212</v>
       </c>
       <c r="N33" t="s">
         <v>57</v>
@@ -24862,13 +24901,13 @@
         <v>61</v>
       </c>
       <c r="T33" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="U33" s="1">
-        <v>3711</v>
+        <v>3854.8</v>
       </c>
       <c r="V33" s="1">
-        <v>3692.5</v>
+        <v>3841.9</v>
       </c>
       <c r="W33" s="1">
         <v>0</v>
@@ -24883,25 +24922,25 @@
         <v>1228</v>
       </c>
       <c r="AA33" s="1">
-        <v>4557108</v>
+        <v>4733694.4000000004</v>
       </c>
       <c r="AB33" s="1">
         <v>0</v>
       </c>
       <c r="AC33" s="1">
-        <v>4628068</v>
+        <v>4875615</v>
       </c>
       <c r="AD33" s="1">
-        <v>8100</v>
+        <v>50400</v>
       </c>
       <c r="AE33" s="1">
-        <v>8100</v>
+        <v>87360</v>
       </c>
       <c r="AF33" t="s">
         <v>64</v>
       </c>
       <c r="AH33" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="AI33" s="1">
         <v>0</v>
@@ -24919,19 +24958,19 @@
         <v>0</v>
       </c>
       <c r="AN33" s="1">
-        <v>70960</v>
+        <v>141920</v>
       </c>
       <c r="AO33" s="1">
-        <v>231404</v>
+        <v>243781</v>
       </c>
       <c r="AP33" s="1">
-        <v>70960</v>
+        <v>141920</v>
       </c>
       <c r="AQ33" s="1">
-        <v>4859472</v>
+        <v>5119396</v>
       </c>
       <c r="AR33" s="1">
-        <v>4875672</v>
+        <v>5257156</v>
       </c>
     </row>
     <row r="34" spans="1:44" x14ac:dyDescent="0.35">
@@ -24948,13 +24987,13 @@
         <v>48</v>
       </c>
       <c r="E34" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="F34" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="G34" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="H34" t="s">
         <v>52</v>
@@ -24966,10 +25005,10 @@
         <v>54</v>
       </c>
       <c r="K34" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="L34" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="M34" t="s">
         <v>368</v>
@@ -24993,13 +25032,13 @@
         <v>61</v>
       </c>
       <c r="T34" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="U34" s="1">
-        <v>3904.6</v>
+        <v>3990.4</v>
       </c>
       <c r="V34" s="1">
-        <v>3874.6</v>
+        <v>3973.8</v>
       </c>
       <c r="W34" s="1">
         <v>0</v>
@@ -25014,25 +25053,25 @@
         <v>1228</v>
       </c>
       <c r="AA34" s="1">
-        <v>4794848.8</v>
+        <v>4900211.2</v>
       </c>
       <c r="AB34" s="1">
         <v>0</v>
       </c>
       <c r="AC34" s="1">
-        <v>4848069</v>
+        <v>5042132</v>
       </c>
       <c r="AD34" s="1">
-        <v>0</v>
+        <v>43500</v>
       </c>
       <c r="AE34" s="1">
-        <v>8550</v>
+        <v>26100</v>
       </c>
       <c r="AF34" t="s">
         <v>64</v>
       </c>
       <c r="AH34" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="AI34" s="1">
         <v>0</v>
@@ -25050,19 +25089,19 @@
         <v>0</v>
       </c>
       <c r="AN34" s="1">
-        <v>53220</v>
+        <v>141920</v>
       </c>
       <c r="AO34" s="1">
-        <v>242404</v>
+        <v>252107</v>
       </c>
       <c r="AP34" s="1">
-        <v>53220</v>
+        <v>141920</v>
       </c>
       <c r="AQ34" s="1">
-        <v>5090473</v>
+        <v>5294239</v>
       </c>
       <c r="AR34" s="1">
-        <v>5099023</v>
+        <v>5363839</v>
       </c>
     </row>
     <row r="35" spans="1:44" x14ac:dyDescent="0.35">
@@ -25079,13 +25118,13 @@
         <v>48</v>
       </c>
       <c r="E35" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="F35" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="G35" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="H35" t="s">
         <v>52</v>
@@ -25097,10 +25136,10 @@
         <v>54</v>
       </c>
       <c r="K35" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="L35" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="M35" t="s">
         <v>368</v>
@@ -25124,13 +25163,13 @@
         <v>61</v>
       </c>
       <c r="T35" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="U35" s="1">
-        <v>3840.8</v>
+        <v>3711</v>
       </c>
       <c r="V35" s="1">
-        <v>3818.8</v>
+        <v>3692.5</v>
       </c>
       <c r="W35" s="1">
         <v>0</v>
@@ -25145,25 +25184,25 @@
         <v>1228</v>
       </c>
       <c r="AA35" s="1">
-        <v>4716502.4000000004</v>
+        <v>4557108</v>
       </c>
       <c r="AB35" s="1">
         <v>0</v>
       </c>
       <c r="AC35" s="1">
-        <v>4769723</v>
+        <v>4628068</v>
       </c>
       <c r="AD35" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="AE35" s="1">
-        <v>8400</v>
+        <v>8100</v>
       </c>
       <c r="AF35" t="s">
         <v>64</v>
       </c>
       <c r="AH35" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="AI35" s="1">
         <v>0</v>
@@ -25181,19 +25220,19 @@
         <v>0</v>
       </c>
       <c r="AN35" s="1">
-        <v>53220</v>
+        <v>70960</v>
       </c>
       <c r="AO35" s="1">
-        <v>238487</v>
+        <v>231404</v>
       </c>
       <c r="AP35" s="1">
-        <v>53220</v>
+        <v>70960</v>
       </c>
       <c r="AQ35" s="1">
-        <v>5008210</v>
+        <v>4859472</v>
       </c>
       <c r="AR35" s="1">
-        <v>5016610</v>
+        <v>4875672</v>
       </c>
     </row>
     <row r="36" spans="1:44" x14ac:dyDescent="0.35">
@@ -25210,13 +25249,13 @@
         <v>48</v>
       </c>
       <c r="E36" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="F36" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="G36" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="H36" t="s">
         <v>52</v>
@@ -25228,10 +25267,10 @@
         <v>54</v>
       </c>
       <c r="K36" t="s">
-        <v>727</v>
+        <v>715</v>
       </c>
       <c r="L36" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="M36" t="s">
         <v>368</v>
@@ -25255,13 +25294,13 @@
         <v>61</v>
       </c>
       <c r="T36" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="U36" s="1">
-        <v>3841.8</v>
+        <v>3904.6</v>
       </c>
       <c r="V36" s="1">
-        <v>3817.2</v>
+        <v>3874.6</v>
       </c>
       <c r="W36" s="1">
         <v>0</v>
@@ -25276,25 +25315,25 @@
         <v>1228</v>
       </c>
       <c r="AA36" s="1">
-        <v>4717730.4000000004</v>
+        <v>4794848.8</v>
       </c>
       <c r="AB36" s="1">
         <v>0</v>
       </c>
       <c r="AC36" s="1">
-        <v>4770951</v>
+        <v>4848069</v>
       </c>
       <c r="AD36" s="1">
         <v>0</v>
       </c>
       <c r="AE36" s="1">
-        <v>0</v>
+        <v>8550</v>
       </c>
       <c r="AF36" t="s">
         <v>64</v>
       </c>
       <c r="AH36" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="AI36" s="1">
         <v>0</v>
@@ -25315,16 +25354,16 @@
         <v>53220</v>
       </c>
       <c r="AO36" s="1">
-        <v>238548</v>
+        <v>242404</v>
       </c>
       <c r="AP36" s="1">
         <v>53220</v>
       </c>
       <c r="AQ36" s="1">
-        <v>5009499</v>
+        <v>5090473</v>
       </c>
       <c r="AR36" s="1">
-        <v>5009499</v>
+        <v>5099023</v>
       </c>
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.35">
@@ -25341,13 +25380,13 @@
         <v>48</v>
       </c>
       <c r="E37" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="F37" t="s">
         <v>731</v>
       </c>
       <c r="G37" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="H37" t="s">
         <v>52</v>
@@ -25359,10 +25398,10 @@
         <v>54</v>
       </c>
       <c r="K37" t="s">
-        <v>733</v>
+        <v>721</v>
       </c>
       <c r="L37" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="M37" t="s">
         <v>368</v>
@@ -25386,13 +25425,13 @@
         <v>61</v>
       </c>
       <c r="T37" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="U37" s="1">
-        <v>3978.2</v>
+        <v>3840.8</v>
       </c>
       <c r="V37" s="1">
-        <v>3953.4</v>
+        <v>3818.8</v>
       </c>
       <c r="W37" s="1">
         <v>0</v>
@@ -25407,25 +25446,25 @@
         <v>1228</v>
       </c>
       <c r="AA37" s="1">
-        <v>4885229.5999999996</v>
+        <v>4716502.4000000004</v>
       </c>
       <c r="AB37" s="1">
         <v>0</v>
       </c>
       <c r="AC37" s="1">
-        <v>4938450</v>
+        <v>4769723</v>
       </c>
       <c r="AD37" s="1">
         <v>0</v>
       </c>
       <c r="AE37" s="1">
-        <v>26100</v>
+        <v>8400</v>
       </c>
       <c r="AF37" t="s">
         <v>64</v>
       </c>
       <c r="AH37" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="AI37" s="1">
         <v>0</v>
@@ -25446,16 +25485,16 @@
         <v>53220</v>
       </c>
       <c r="AO37" s="1">
-        <v>246923</v>
+        <v>238487</v>
       </c>
       <c r="AP37" s="1">
         <v>53220</v>
       </c>
       <c r="AQ37" s="1">
-        <v>5185373</v>
+        <v>5008210</v>
       </c>
       <c r="AR37" s="1">
-        <v>5211473</v>
+        <v>5016610</v>
       </c>
     </row>
     <row r="38" spans="1:44" x14ac:dyDescent="0.35">
@@ -25472,13 +25511,13 @@
         <v>48</v>
       </c>
       <c r="E38" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="F38" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="G38" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="H38" t="s">
         <v>52</v>
@@ -25490,10 +25529,10 @@
         <v>54</v>
       </c>
       <c r="K38" t="s">
-        <v>738</v>
+        <v>727</v>
       </c>
       <c r="L38" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="M38" t="s">
         <v>368</v>
@@ -25517,13 +25556,13 @@
         <v>61</v>
       </c>
       <c r="T38" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="U38" s="1">
-        <v>3923.4</v>
+        <v>3841.8</v>
       </c>
       <c r="V38" s="1">
-        <v>3912.4</v>
+        <v>3817.2</v>
       </c>
       <c r="W38" s="1">
         <v>0</v>
@@ -25538,25 +25577,25 @@
         <v>1228</v>
       </c>
       <c r="AA38" s="1">
-        <v>4817935.2</v>
+        <v>4717730.4000000004</v>
       </c>
       <c r="AB38" s="1">
         <v>0</v>
       </c>
       <c r="AC38" s="1">
-        <v>4871156</v>
+        <v>4770951</v>
       </c>
       <c r="AD38" s="1">
         <v>0</v>
       </c>
       <c r="AE38" s="1">
-        <v>25650</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="s">
         <v>64</v>
       </c>
       <c r="AH38" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="AI38" s="1">
         <v>0</v>
@@ -25577,16 +25616,16 @@
         <v>53220</v>
       </c>
       <c r="AO38" s="1">
-        <v>243558</v>
+        <v>238548</v>
       </c>
       <c r="AP38" s="1">
         <v>53220</v>
       </c>
       <c r="AQ38" s="1">
-        <v>5114714</v>
+        <v>5009499</v>
       </c>
       <c r="AR38" s="1">
-        <v>5140364</v>
+        <v>5009499</v>
       </c>
     </row>
     <row r="39" spans="1:44" x14ac:dyDescent="0.35">
@@ -25603,13 +25642,13 @@
         <v>48</v>
       </c>
       <c r="E39" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="F39" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="G39" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="H39" t="s">
         <v>52</v>
@@ -25621,10 +25660,10 @@
         <v>54</v>
       </c>
       <c r="K39" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="L39" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="M39" t="s">
         <v>368</v>
@@ -25648,13 +25687,13 @@
         <v>61</v>
       </c>
       <c r="T39" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="U39" s="1">
-        <v>3901.2</v>
+        <v>3978.2</v>
       </c>
       <c r="V39" s="1">
-        <v>3870.4</v>
+        <v>3953.4</v>
       </c>
       <c r="W39" s="1">
         <v>0</v>
@@ -25669,25 +25708,25 @@
         <v>1228</v>
       </c>
       <c r="AA39" s="1">
-        <v>4790673.5999999996</v>
+        <v>4885229.5999999996</v>
       </c>
       <c r="AB39" s="1">
         <v>0</v>
       </c>
       <c r="AC39" s="1">
-        <v>4843894</v>
+        <v>4938450</v>
       </c>
       <c r="AD39" s="1">
         <v>0</v>
       </c>
       <c r="AE39" s="1">
-        <v>0</v>
+        <v>26100</v>
       </c>
       <c r="AF39" t="s">
         <v>64</v>
       </c>
       <c r="AH39" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
       <c r="AI39" s="1">
         <v>0</v>
@@ -25708,16 +25747,16 @@
         <v>53220</v>
       </c>
       <c r="AO39" s="1">
-        <v>242195</v>
+        <v>246923</v>
       </c>
       <c r="AP39" s="1">
         <v>53220</v>
       </c>
       <c r="AQ39" s="1">
-        <v>5086089</v>
+        <v>5185373</v>
       </c>
       <c r="AR39" s="1">
-        <v>5086089</v>
+        <v>5211473</v>
       </c>
     </row>
     <row r="40" spans="1:44" x14ac:dyDescent="0.35">
@@ -25734,13 +25773,13 @@
         <v>48</v>
       </c>
       <c r="E40" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="F40" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="G40" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="H40" t="s">
         <v>52</v>
@@ -25752,13 +25791,13 @@
         <v>54</v>
       </c>
       <c r="K40" t="s">
-        <v>750</v>
+        <v>738</v>
       </c>
       <c r="L40" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="M40" t="s">
-        <v>212</v>
+        <v>368</v>
       </c>
       <c r="N40" t="s">
         <v>57</v>
@@ -25779,13 +25818,13 @@
         <v>61</v>
       </c>
       <c r="T40" t="s">
-        <v>756</v>
+        <v>840</v>
       </c>
       <c r="U40" s="1">
-        <v>3918.2</v>
+        <v>3923.4</v>
       </c>
       <c r="V40" s="1">
-        <v>3902.7</v>
+        <v>3912.4</v>
       </c>
       <c r="W40" s="1">
         <v>0</v>
@@ -25800,25 +25839,25 @@
         <v>1228</v>
       </c>
       <c r="AA40" s="1">
-        <v>4811549.5999999996</v>
+        <v>4817935.2</v>
       </c>
       <c r="AB40" s="1">
         <v>0</v>
       </c>
       <c r="AC40" s="1">
-        <v>4864770</v>
+        <v>4871156</v>
       </c>
       <c r="AD40" s="1">
         <v>0</v>
       </c>
       <c r="AE40" s="1">
-        <v>0</v>
+        <v>25650</v>
       </c>
       <c r="AF40" t="s">
         <v>64</v>
       </c>
       <c r="AH40" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
       <c r="AI40" s="1">
         <v>0</v>
@@ -25839,16 +25878,16 @@
         <v>53220</v>
       </c>
       <c r="AO40" s="1">
-        <v>243239</v>
+        <v>243558</v>
       </c>
       <c r="AP40" s="1">
         <v>53220</v>
       </c>
       <c r="AQ40" s="1">
-        <v>5108009</v>
+        <v>5114714</v>
       </c>
       <c r="AR40" s="1">
-        <v>5108009</v>
+        <v>5140364</v>
       </c>
     </row>
     <row r="41" spans="1:44" x14ac:dyDescent="0.35">
@@ -25865,13 +25904,13 @@
         <v>48</v>
       </c>
       <c r="E41" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="F41" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="G41" t="s">
-        <v>850</v>
+        <v>843</v>
       </c>
       <c r="H41" t="s">
         <v>52</v>
@@ -25883,10 +25922,10 @@
         <v>54</v>
       </c>
       <c r="K41" t="s">
-        <v>755</v>
+        <v>744</v>
       </c>
       <c r="L41" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="M41" t="s">
         <v>368</v>
@@ -25910,13 +25949,13 @@
         <v>61</v>
       </c>
       <c r="T41" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="U41" s="1">
-        <v>4118</v>
+        <v>3901.2</v>
       </c>
       <c r="V41" s="1">
-        <v>4117.8</v>
+        <v>3870.4</v>
       </c>
       <c r="W41" s="1">
         <v>0</v>
@@ -25931,25 +25970,25 @@
         <v>1228</v>
       </c>
       <c r="AA41" s="1">
-        <v>5056904</v>
+        <v>4790673.5999999996</v>
       </c>
       <c r="AB41" s="1">
         <v>0</v>
       </c>
       <c r="AC41" s="1">
-        <v>5118664</v>
+        <v>4843894</v>
       </c>
       <c r="AD41" s="1">
-        <v>8850</v>
+        <v>0</v>
       </c>
       <c r="AE41" s="1">
-        <v>17700</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="s">
         <v>64</v>
       </c>
       <c r="AH41" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="AI41" s="1">
         <v>0</v>
@@ -25967,19 +26006,19 @@
         <v>0</v>
       </c>
       <c r="AN41" s="1">
-        <v>61760</v>
+        <v>53220</v>
       </c>
       <c r="AO41" s="1">
-        <v>255934</v>
+        <v>242195</v>
       </c>
       <c r="AP41" s="1">
-        <v>61760</v>
+        <v>53220</v>
       </c>
       <c r="AQ41" s="1">
-        <v>5374598</v>
+        <v>5086089</v>
       </c>
       <c r="AR41" s="1">
-        <v>5401148</v>
+        <v>5086089</v>
       </c>
     </row>
     <row r="42" spans="1:44" x14ac:dyDescent="0.35">
@@ -25996,13 +26035,13 @@
         <v>48</v>
       </c>
       <c r="E42" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="F42" t="s">
-        <v>854</v>
+        <v>748</v>
       </c>
       <c r="G42" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="H42" t="s">
         <v>52</v>
@@ -26014,10 +26053,10 @@
         <v>54</v>
       </c>
       <c r="K42" t="s">
-        <v>761</v>
+        <v>750</v>
       </c>
       <c r="L42" t="s">
-        <v>854</v>
+        <v>748</v>
       </c>
       <c r="M42" t="s">
         <v>212</v>
@@ -26035,19 +26074,19 @@
         <v>60</v>
       </c>
       <c r="R42" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S42" t="s">
         <v>61</v>
       </c>
       <c r="T42" t="s">
-        <v>856</v>
+        <v>756</v>
       </c>
       <c r="U42" s="1">
-        <v>3792.2</v>
+        <v>3918.2</v>
       </c>
       <c r="V42" s="1">
-        <v>3785.7</v>
+        <v>3902.7</v>
       </c>
       <c r="W42" s="1">
         <v>0</v>
@@ -26062,25 +26101,25 @@
         <v>1228</v>
       </c>
       <c r="AA42" s="1">
-        <v>4656821.5999999996</v>
+        <v>4811549.5999999996</v>
       </c>
       <c r="AB42" s="1">
         <v>0</v>
       </c>
       <c r="AC42" s="1">
-        <v>4710042</v>
+        <v>4864770</v>
       </c>
       <c r="AD42" s="1">
         <v>0</v>
       </c>
       <c r="AE42" s="1">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="s">
         <v>64</v>
       </c>
       <c r="AH42" t="s">
-        <v>857</v>
+        <v>848</v>
       </c>
       <c r="AI42" s="1">
         <v>0</v>
@@ -26101,16 +26140,16 @@
         <v>53220</v>
       </c>
       <c r="AO42" s="1">
-        <v>235503</v>
+        <v>243239</v>
       </c>
       <c r="AP42" s="1">
         <v>53220</v>
       </c>
       <c r="AQ42" s="1">
-        <v>4945545</v>
+        <v>5108009</v>
       </c>
       <c r="AR42" s="1">
-        <v>4978545</v>
+        <v>5108009</v>
       </c>
     </row>
     <row r="43" spans="1:44" x14ac:dyDescent="0.35">
@@ -26127,13 +26166,13 @@
         <v>48</v>
       </c>
       <c r="E43" t="s">
-        <v>858</v>
+        <v>849</v>
       </c>
       <c r="F43" t="s">
-        <v>854</v>
+        <v>748</v>
       </c>
       <c r="G43" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="H43" t="s">
         <v>52</v>
@@ -26145,10 +26184,10 @@
         <v>54</v>
       </c>
       <c r="K43" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="L43" t="s">
-        <v>854</v>
+        <v>748</v>
       </c>
       <c r="M43" t="s">
         <v>368</v>
@@ -26166,19 +26205,19 @@
         <v>60</v>
       </c>
       <c r="R43" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S43" t="s">
         <v>61</v>
       </c>
       <c r="T43" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
       <c r="U43" s="1">
-        <v>3916</v>
+        <v>4118</v>
       </c>
       <c r="V43" s="1">
-        <v>3896.8</v>
+        <v>4117.8</v>
       </c>
       <c r="W43" s="1">
         <v>0</v>
@@ -26193,25 +26232,25 @@
         <v>1228</v>
       </c>
       <c r="AA43" s="1">
-        <v>4808848</v>
+        <v>5056904</v>
       </c>
       <c r="AB43" s="1">
         <v>0</v>
       </c>
       <c r="AC43" s="1">
-        <v>4862068</v>
+        <v>5118664</v>
       </c>
       <c r="AD43" s="1">
-        <v>0</v>
+        <v>8850</v>
       </c>
       <c r="AE43" s="1">
-        <v>42750</v>
+        <v>17700</v>
       </c>
       <c r="AF43" t="s">
         <v>64</v>
       </c>
       <c r="AH43" t="s">
-        <v>861</v>
+        <v>852</v>
       </c>
       <c r="AI43" s="1">
         <v>0</v>
@@ -26229,19 +26268,19 @@
         <v>0</v>
       </c>
       <c r="AN43" s="1">
-        <v>53220</v>
+        <v>61760</v>
       </c>
       <c r="AO43" s="1">
-        <v>243104</v>
+        <v>255934</v>
       </c>
       <c r="AP43" s="1">
-        <v>53220</v>
+        <v>61760</v>
       </c>
       <c r="AQ43" s="1">
-        <v>5105172</v>
+        <v>5374598</v>
       </c>
       <c r="AR43" s="1">
-        <v>5147922</v>
+        <v>5401148</v>
       </c>
     </row>
     <row r="44" spans="1:44" x14ac:dyDescent="0.35">
@@ -26258,13 +26297,13 @@
         <v>48</v>
       </c>
       <c r="E44" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="F44" t="s">
-        <v>759</v>
+        <v>854</v>
       </c>
       <c r="G44" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="H44" t="s">
         <v>52</v>
@@ -26276,13 +26315,13 @@
         <v>54</v>
       </c>
       <c r="K44" t="s">
-        <v>773</v>
+        <v>761</v>
       </c>
       <c r="L44" t="s">
-        <v>759</v>
+        <v>854</v>
       </c>
       <c r="M44" t="s">
-        <v>368</v>
+        <v>212</v>
       </c>
       <c r="N44" t="s">
         <v>57</v>
@@ -26297,19 +26336,19 @@
         <v>60</v>
       </c>
       <c r="R44" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="S44" t="s">
         <v>61</v>
       </c>
       <c r="T44" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
       <c r="U44" s="1">
-        <v>3994.8</v>
+        <v>3792.2</v>
       </c>
       <c r="V44" s="1">
-        <v>3985.6</v>
+        <v>3785.7</v>
       </c>
       <c r="W44" s="1">
         <v>0</v>
@@ -26324,25 +26363,25 @@
         <v>1228</v>
       </c>
       <c r="AA44" s="1">
-        <v>4905614.4000000004</v>
+        <v>4656821.5999999996</v>
       </c>
       <c r="AB44" s="1">
         <v>0</v>
       </c>
       <c r="AC44" s="1">
-        <v>4958835</v>
+        <v>4710042</v>
       </c>
       <c r="AD44" s="1">
         <v>0</v>
       </c>
       <c r="AE44" s="1">
-        <v>71340</v>
+        <v>33000</v>
       </c>
       <c r="AF44" t="s">
         <v>64</v>
       </c>
       <c r="AH44" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="AI44" s="1">
         <v>0</v>
@@ -26363,16 +26402,16 @@
         <v>53220</v>
       </c>
       <c r="AO44" s="1">
-        <v>247942</v>
+        <v>235503</v>
       </c>
       <c r="AP44" s="1">
         <v>53220</v>
       </c>
       <c r="AQ44" s="1">
-        <v>5206777</v>
+        <v>4945545</v>
       </c>
       <c r="AR44" s="1">
-        <v>5278117</v>
+        <v>4978545</v>
       </c>
     </row>
     <row r="45" spans="1:44" x14ac:dyDescent="0.35">
@@ -26389,13 +26428,13 @@
         <v>48</v>
       </c>
       <c r="E45" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="F45" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
       <c r="G45" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="H45" t="s">
         <v>52</v>
@@ -26407,10 +26446,10 @@
         <v>54</v>
       </c>
       <c r="K45" t="s">
-        <v>869</v>
+        <v>767</v>
       </c>
       <c r="L45" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
       <c r="M45" t="s">
         <v>368</v>
@@ -26428,19 +26467,19 @@
         <v>60</v>
       </c>
       <c r="R45" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="S45" t="s">
         <v>61</v>
       </c>
       <c r="T45" t="s">
-        <v>870</v>
+        <v>860</v>
       </c>
       <c r="U45" s="1">
-        <v>3697.2</v>
+        <v>3916</v>
       </c>
       <c r="V45" s="1">
-        <v>3667.5</v>
+        <v>3896.8</v>
       </c>
       <c r="W45" s="1">
         <v>0</v>
@@ -26455,25 +26494,25 @@
         <v>1228</v>
       </c>
       <c r="AA45" s="1">
-        <v>4540161.5999999996</v>
+        <v>4808848</v>
       </c>
       <c r="AB45" s="1">
         <v>0</v>
       </c>
       <c r="AC45" s="1">
-        <v>4628862</v>
+        <v>4862068</v>
       </c>
       <c r="AD45" s="1">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="AE45" s="1">
-        <v>40500</v>
+        <v>42750</v>
       </c>
       <c r="AF45" t="s">
         <v>64</v>
       </c>
       <c r="AH45" t="s">
-        <v>871</v>
+        <v>861</v>
       </c>
       <c r="AI45" s="1">
         <v>0</v>
@@ -26491,19 +26530,19 @@
         <v>0</v>
       </c>
       <c r="AN45" s="1">
-        <v>88700</v>
+        <v>53220</v>
       </c>
       <c r="AO45" s="1">
-        <v>231444</v>
+        <v>243104</v>
       </c>
       <c r="AP45" s="1">
-        <v>88700</v>
+        <v>53220</v>
       </c>
       <c r="AQ45" s="1">
-        <v>4860306</v>
+        <v>5105172</v>
       </c>
       <c r="AR45" s="1">
-        <v>4917006</v>
+        <v>5147922</v>
       </c>
     </row>
     <row r="46" spans="1:44" x14ac:dyDescent="0.35">
@@ -26520,13 +26559,13 @@
         <v>48</v>
       </c>
       <c r="E46" t="s">
-        <v>872</v>
+        <v>862</v>
       </c>
       <c r="F46" t="s">
-        <v>867</v>
+        <v>759</v>
       </c>
       <c r="G46" t="s">
-        <v>873</v>
+        <v>863</v>
       </c>
       <c r="H46" t="s">
         <v>52</v>
@@ -26538,10 +26577,10 @@
         <v>54</v>
       </c>
       <c r="K46" t="s">
-        <v>874</v>
+        <v>773</v>
       </c>
       <c r="L46" t="s">
-        <v>867</v>
+        <v>759</v>
       </c>
       <c r="M46" t="s">
         <v>368</v>
@@ -26565,13 +26604,13 @@
         <v>61</v>
       </c>
       <c r="T46" t="s">
-        <v>875</v>
+        <v>864</v>
       </c>
       <c r="U46" s="1">
-        <v>3585</v>
+        <v>3994.8</v>
       </c>
       <c r="V46" s="1">
-        <v>3576.4</v>
+        <v>3985.6</v>
       </c>
       <c r="W46" s="1">
         <v>0</v>
@@ -26586,25 +26625,25 @@
         <v>1228</v>
       </c>
       <c r="AA46" s="1">
-        <v>4402380</v>
+        <v>4905614.4000000004</v>
       </c>
       <c r="AB46" s="1">
         <v>0</v>
       </c>
       <c r="AC46" s="1">
-        <v>4455600</v>
+        <v>4958835</v>
       </c>
       <c r="AD46" s="1">
         <v>0</v>
       </c>
       <c r="AE46" s="1">
-        <v>15600</v>
+        <v>71340</v>
       </c>
       <c r="AF46" t="s">
         <v>64</v>
       </c>
       <c r="AH46" t="s">
-        <v>876</v>
+        <v>865</v>
       </c>
       <c r="AI46" s="1">
         <v>0</v>
@@ -26625,16 +26664,16 @@
         <v>53220</v>
       </c>
       <c r="AO46" s="1">
-        <v>222780</v>
+        <v>247942</v>
       </c>
       <c r="AP46" s="1">
         <v>53220</v>
       </c>
       <c r="AQ46" s="1">
-        <v>4678380</v>
+        <v>5206777</v>
       </c>
       <c r="AR46" s="1">
-        <v>4693980</v>
+        <v>5278117</v>
       </c>
     </row>
     <row r="47" spans="1:44" x14ac:dyDescent="0.35">
@@ -26651,13 +26690,13 @@
         <v>48</v>
       </c>
       <c r="E47" t="s">
-        <v>877</v>
+        <v>866</v>
       </c>
       <c r="F47" t="s">
-        <v>765</v>
+        <v>867</v>
       </c>
       <c r="G47" t="s">
-        <v>878</v>
+        <v>868</v>
       </c>
       <c r="H47" t="s">
         <v>52</v>
@@ -26669,10 +26708,10 @@
         <v>54</v>
       </c>
       <c r="K47" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="L47" t="s">
-        <v>765</v>
+        <v>867</v>
       </c>
       <c r="M47" t="s">
         <v>368</v>
@@ -26696,13 +26735,13 @@
         <v>61</v>
       </c>
       <c r="T47" t="s">
-        <v>880</v>
+        <v>870</v>
       </c>
       <c r="U47" s="1">
-        <v>3780.2</v>
+        <v>3697.2</v>
       </c>
       <c r="V47" s="1">
-        <v>3765.2</v>
+        <v>3667.5</v>
       </c>
       <c r="W47" s="1">
         <v>0</v>
@@ -26717,25 +26756,25 @@
         <v>1228</v>
       </c>
       <c r="AA47" s="1">
-        <v>4642085.5999999996</v>
+        <v>4540161.5999999996</v>
       </c>
       <c r="AB47" s="1">
         <v>0</v>
       </c>
       <c r="AC47" s="1">
-        <v>4695306</v>
+        <v>4628862</v>
       </c>
       <c r="AD47" s="1">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="AE47" s="1">
-        <v>41250</v>
+        <v>40500</v>
       </c>
       <c r="AF47" t="s">
         <v>64</v>
       </c>
       <c r="AH47" t="s">
-        <v>881</v>
+        <v>871</v>
       </c>
       <c r="AI47" s="1">
         <v>0</v>
@@ -26753,19 +26792,19 @@
         <v>0</v>
       </c>
       <c r="AN47" s="1">
-        <v>53220</v>
+        <v>88700</v>
       </c>
       <c r="AO47" s="1">
-        <v>234766</v>
+        <v>231444</v>
       </c>
       <c r="AP47" s="1">
-        <v>53220</v>
+        <v>88700</v>
       </c>
       <c r="AQ47" s="1">
-        <v>4930072</v>
+        <v>4860306</v>
       </c>
       <c r="AR47" s="1">
-        <v>4971322</v>
+        <v>4917006</v>
       </c>
     </row>
     <row r="48" spans="1:44" x14ac:dyDescent="0.35">
@@ -26782,13 +26821,13 @@
         <v>48</v>
       </c>
       <c r="E48" t="s">
-        <v>882</v>
+        <v>872</v>
       </c>
       <c r="F48" t="s">
-        <v>765</v>
+        <v>867</v>
       </c>
       <c r="G48" t="s">
-        <v>883</v>
+        <v>873</v>
       </c>
       <c r="H48" t="s">
         <v>52</v>
@@ -26800,10 +26839,10 @@
         <v>54</v>
       </c>
       <c r="K48" t="s">
-        <v>884</v>
+        <v>874</v>
       </c>
       <c r="L48" t="s">
-        <v>765</v>
+        <v>867</v>
       </c>
       <c r="M48" t="s">
         <v>368</v>
@@ -26827,13 +26866,13 @@
         <v>61</v>
       </c>
       <c r="T48" t="s">
-        <v>768</v>
+        <v>875</v>
       </c>
       <c r="U48" s="1">
-        <v>3515.2</v>
+        <v>3585</v>
       </c>
       <c r="V48" s="1">
-        <v>3502.2</v>
+        <v>3576.4</v>
       </c>
       <c r="W48" s="1">
         <v>0</v>
@@ -26848,25 +26887,25 @@
         <v>1228</v>
       </c>
       <c r="AA48" s="1">
-        <v>4316665.5999999996</v>
+        <v>4402380</v>
       </c>
       <c r="AB48" s="1">
         <v>0</v>
       </c>
       <c r="AC48" s="1">
-        <v>4369886</v>
+        <v>4455600</v>
       </c>
       <c r="AD48" s="1">
         <v>0</v>
       </c>
       <c r="AE48" s="1">
-        <v>45900</v>
+        <v>15600</v>
       </c>
       <c r="AF48" t="s">
         <v>64</v>
       </c>
       <c r="AH48" t="s">
-        <v>885</v>
+        <v>876</v>
       </c>
       <c r="AI48" s="1">
         <v>0</v>
@@ -26887,16 +26926,16 @@
         <v>53220</v>
       </c>
       <c r="AO48" s="1">
-        <v>218495</v>
+        <v>222780</v>
       </c>
       <c r="AP48" s="1">
         <v>53220</v>
       </c>
       <c r="AQ48" s="1">
-        <v>4588381</v>
+        <v>4678380</v>
       </c>
       <c r="AR48" s="1">
-        <v>4634281</v>
+        <v>4693980</v>
       </c>
     </row>
     <row r="49" spans="1:44" x14ac:dyDescent="0.35">
@@ -26913,13 +26952,13 @@
         <v>48</v>
       </c>
       <c r="E49" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="F49" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="G49" t="s">
-        <v>887</v>
+        <v>878</v>
       </c>
       <c r="H49" t="s">
         <v>52</v>
@@ -26931,10 +26970,10 @@
         <v>54</v>
       </c>
       <c r="K49" t="s">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="L49" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="M49" t="s">
         <v>368</v>
@@ -26958,13 +26997,13 @@
         <v>61</v>
       </c>
       <c r="T49" t="s">
-        <v>889</v>
+        <v>880</v>
       </c>
       <c r="U49" s="1">
-        <v>3708.2</v>
+        <v>3780.2</v>
       </c>
       <c r="V49" s="1">
-        <v>3691</v>
+        <v>3765.2</v>
       </c>
       <c r="W49" s="1">
         <v>0</v>
@@ -26979,25 +27018,25 @@
         <v>1228</v>
       </c>
       <c r="AA49" s="1">
-        <v>4553669.5999999996</v>
+        <v>4642085.5999999996</v>
       </c>
       <c r="AB49" s="1">
         <v>0</v>
       </c>
       <c r="AC49" s="1">
-        <v>4606890</v>
+        <v>4695306</v>
       </c>
       <c r="AD49" s="1">
         <v>0</v>
       </c>
       <c r="AE49" s="1">
-        <v>0</v>
+        <v>41250</v>
       </c>
       <c r="AF49" t="s">
         <v>64</v>
       </c>
       <c r="AH49" t="s">
-        <v>890</v>
+        <v>881</v>
       </c>
       <c r="AI49" s="1">
         <v>0</v>
@@ -27018,16 +27057,16 @@
         <v>53220</v>
       </c>
       <c r="AO49" s="1">
-        <v>230345</v>
+        <v>234766</v>
       </c>
       <c r="AP49" s="1">
         <v>53220</v>
       </c>
       <c r="AQ49" s="1">
-        <v>4837235</v>
+        <v>4930072</v>
       </c>
       <c r="AR49" s="1">
-        <v>4837235</v>
+        <v>4971322</v>
       </c>
     </row>
     <row r="50" spans="1:44" x14ac:dyDescent="0.35">
@@ -27044,13 +27083,13 @@
         <v>48</v>
       </c>
       <c r="E50" t="s">
-        <v>891</v>
+        <v>882</v>
       </c>
       <c r="F50" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="G50" t="s">
-        <v>892</v>
+        <v>883</v>
       </c>
       <c r="H50" t="s">
         <v>52</v>
@@ -27062,13 +27101,13 @@
         <v>54</v>
       </c>
       <c r="K50" t="s">
-        <v>893</v>
+        <v>884</v>
       </c>
       <c r="L50" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="M50" t="s">
-        <v>56</v>
+        <v>368</v>
       </c>
       <c r="N50" t="s">
         <v>57</v>
@@ -27089,13 +27128,13 @@
         <v>61</v>
       </c>
       <c r="T50" t="s">
-        <v>894</v>
+        <v>768</v>
       </c>
       <c r="U50" s="1">
-        <v>3922.2</v>
+        <v>3515.2</v>
       </c>
       <c r="V50" s="1">
-        <v>3906</v>
+        <v>3502.2</v>
       </c>
       <c r="W50" s="1">
         <v>0</v>
@@ -27110,25 +27149,25 @@
         <v>1228</v>
       </c>
       <c r="AA50" s="1">
-        <v>4816461.5999999996</v>
+        <v>4316665.5999999996</v>
       </c>
       <c r="AB50" s="1">
         <v>0</v>
       </c>
       <c r="AC50" s="1">
-        <v>4905162</v>
+        <v>4369886</v>
       </c>
       <c r="AD50" s="1">
-        <v>17100</v>
+        <v>0</v>
       </c>
       <c r="AE50" s="1">
-        <v>129105</v>
+        <v>45900</v>
       </c>
       <c r="AF50" t="s">
         <v>64</v>
       </c>
       <c r="AH50" t="s">
-        <v>895</v>
+        <v>885</v>
       </c>
       <c r="AI50" s="1">
         <v>0</v>
@@ -27146,19 +27185,19 @@
         <v>0</v>
       </c>
       <c r="AN50" s="1">
-        <v>88700</v>
+        <v>53220</v>
       </c>
       <c r="AO50" s="1">
-        <v>245259</v>
+        <v>218495</v>
       </c>
       <c r="AP50" s="1">
-        <v>88700</v>
+        <v>53220</v>
       </c>
       <c r="AQ50" s="1">
-        <v>5150421</v>
+        <v>4588381</v>
       </c>
       <c r="AR50" s="1">
-        <v>5296626</v>
+        <v>4634281</v>
       </c>
     </row>
     <row r="51" spans="1:44" x14ac:dyDescent="0.35">
@@ -27175,13 +27214,13 @@
         <v>48</v>
       </c>
       <c r="E51" t="s">
-        <v>896</v>
+        <v>886</v>
       </c>
       <c r="F51" t="s">
-        <v>897</v>
+        <v>771</v>
       </c>
       <c r="G51" t="s">
-        <v>898</v>
+        <v>887</v>
       </c>
       <c r="H51" t="s">
         <v>52</v>
@@ -27193,13 +27232,13 @@
         <v>54</v>
       </c>
       <c r="K51" t="s">
-        <v>899</v>
+        <v>888</v>
       </c>
       <c r="L51" t="s">
-        <v>897</v>
+        <v>771</v>
       </c>
       <c r="M51" t="s">
-        <v>56</v>
+        <v>368</v>
       </c>
       <c r="N51" t="s">
         <v>57</v>
@@ -27220,13 +27259,13 @@
         <v>61</v>
       </c>
       <c r="T51" t="s">
-        <v>900</v>
+        <v>889</v>
       </c>
       <c r="U51" s="1">
-        <v>3899.8</v>
+        <v>3708.2</v>
       </c>
       <c r="V51" s="1">
-        <v>3879.3</v>
+        <v>3691</v>
       </c>
       <c r="W51" s="1">
         <v>0</v>
@@ -27241,25 +27280,25 @@
         <v>1228</v>
       </c>
       <c r="AA51" s="1">
-        <v>4788954.4000000004</v>
+        <v>4553669.5999999996</v>
       </c>
       <c r="AB51" s="1">
         <v>0</v>
       </c>
       <c r="AC51" s="1">
-        <v>4895395</v>
+        <v>4606890</v>
       </c>
       <c r="AD51" s="1">
-        <v>25200</v>
+        <v>0</v>
       </c>
       <c r="AE51" s="1">
-        <v>33600</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="s">
         <v>64</v>
       </c>
       <c r="AH51" t="s">
-        <v>901</v>
+        <v>890</v>
       </c>
       <c r="AI51" s="1">
         <v>0</v>
@@ -27277,19 +27316,19 @@
         <v>0</v>
       </c>
       <c r="AN51" s="1">
-        <v>106440</v>
+        <v>53220</v>
       </c>
       <c r="AO51" s="1">
-        <v>244770</v>
+        <v>230345</v>
       </c>
       <c r="AP51" s="1">
-        <v>106440</v>
+        <v>53220</v>
       </c>
       <c r="AQ51" s="1">
-        <v>5140165</v>
+        <v>4837235</v>
       </c>
       <c r="AR51" s="1">
-        <v>5198965</v>
+        <v>4837235</v>
       </c>
     </row>
     <row r="52" spans="1:44" x14ac:dyDescent="0.35">
@@ -27306,13 +27345,13 @@
         <v>48</v>
       </c>
       <c r="E52" t="s">
-        <v>902</v>
+        <v>891</v>
       </c>
       <c r="F52" t="s">
-        <v>903</v>
+        <v>771</v>
       </c>
       <c r="G52" t="s">
-        <v>904</v>
+        <v>892</v>
       </c>
       <c r="H52" t="s">
         <v>52</v>
@@ -27324,10 +27363,10 @@
         <v>54</v>
       </c>
       <c r="K52" t="s">
-        <v>905</v>
+        <v>893</v>
       </c>
       <c r="L52" t="s">
-        <v>903</v>
+        <v>771</v>
       </c>
       <c r="M52" t="s">
         <v>56</v>
@@ -27351,13 +27390,13 @@
         <v>61</v>
       </c>
       <c r="T52" t="s">
-        <v>906</v>
+        <v>894</v>
       </c>
       <c r="U52" s="1">
-        <v>4118.8</v>
+        <v>3922.2</v>
       </c>
       <c r="V52" s="1">
-        <v>4105.3</v>
+        <v>3906</v>
       </c>
       <c r="W52" s="1">
         <v>0</v>
@@ -27372,25 +27411,25 @@
         <v>1228</v>
       </c>
       <c r="AA52" s="1">
-        <v>5057886.4000000004</v>
+        <v>4816461.5999999996</v>
       </c>
       <c r="AB52" s="1">
         <v>0</v>
       </c>
       <c r="AC52" s="1">
-        <v>5253027</v>
+        <v>4905162</v>
       </c>
       <c r="AD52" s="1">
-        <v>72570</v>
+        <v>17100</v>
       </c>
       <c r="AE52" s="1">
-        <v>26550</v>
+        <v>129105</v>
       </c>
       <c r="AF52" t="s">
         <v>64</v>
       </c>
       <c r="AH52" t="s">
-        <v>907</v>
+        <v>895</v>
       </c>
       <c r="AI52" s="1">
         <v>0</v>
@@ -27408,19 +27447,19 @@
         <v>0</v>
       </c>
       <c r="AN52" s="1">
-        <v>195140</v>
+        <v>88700</v>
       </c>
       <c r="AO52" s="1">
-        <v>262652</v>
+        <v>245259</v>
       </c>
       <c r="AP52" s="1">
-        <v>195140</v>
+        <v>88700</v>
       </c>
       <c r="AQ52" s="1">
-        <v>5515679</v>
+        <v>5150421</v>
       </c>
       <c r="AR52" s="1">
-        <v>5614799</v>
+        <v>5296626</v>
       </c>
     </row>
     <row r="53" spans="1:44" x14ac:dyDescent="0.35">
@@ -27437,13 +27476,13 @@
         <v>48</v>
       </c>
       <c r="E53" t="s">
-        <v>908</v>
+        <v>896</v>
       </c>
       <c r="F53" t="s">
-        <v>909</v>
+        <v>897</v>
       </c>
       <c r="G53" t="s">
-        <v>910</v>
+        <v>898</v>
       </c>
       <c r="H53" t="s">
         <v>52</v>
@@ -27455,10 +27494,10 @@
         <v>54</v>
       </c>
       <c r="K53" t="s">
-        <v>911</v>
+        <v>899</v>
       </c>
       <c r="L53" t="s">
-        <v>909</v>
+        <v>897</v>
       </c>
       <c r="M53" t="s">
         <v>56</v>
@@ -27482,13 +27521,13 @@
         <v>61</v>
       </c>
       <c r="T53" t="s">
-        <v>912</v>
+        <v>900</v>
       </c>
       <c r="U53" s="1">
-        <v>3908.8</v>
+        <v>3899.8</v>
       </c>
       <c r="V53" s="1">
-        <v>3894.4</v>
+        <v>3879.3</v>
       </c>
       <c r="W53" s="1">
         <v>0</v>
@@ -27503,25 +27542,25 @@
         <v>1228</v>
       </c>
       <c r="AA53" s="1">
-        <v>4800006.4000000004</v>
+        <v>4788954.4000000004</v>
       </c>
       <c r="AB53" s="1">
         <v>0</v>
       </c>
       <c r="AC53" s="1">
-        <v>4870967</v>
+        <v>4895395</v>
       </c>
       <c r="AD53" s="1">
-        <v>0</v>
+        <v>25200</v>
       </c>
       <c r="AE53" s="1">
-        <v>0</v>
+        <v>33600</v>
       </c>
       <c r="AF53" t="s">
         <v>64</v>
       </c>
       <c r="AH53" t="s">
-        <v>913</v>
+        <v>901</v>
       </c>
       <c r="AI53" s="1">
         <v>0</v>
@@ -27539,19 +27578,19 @@
         <v>0</v>
       </c>
       <c r="AN53" s="1">
-        <v>70960</v>
+        <v>106440</v>
       </c>
       <c r="AO53" s="1">
-        <v>243549</v>
+        <v>244770</v>
       </c>
       <c r="AP53" s="1">
-        <v>70960</v>
+        <v>106440</v>
       </c>
       <c r="AQ53" s="1">
-        <v>5114516</v>
+        <v>5140165</v>
       </c>
       <c r="AR53" s="1">
-        <v>5114516</v>
+        <v>5198965</v>
       </c>
     </row>
     <row r="54" spans="1:44" x14ac:dyDescent="0.35">
@@ -27562,19 +27601,19 @@
         <v>46</v>
       </c>
       <c r="C54" t="s">
-        <v>506</v>
+        <v>357</v>
       </c>
       <c r="D54" t="s">
         <v>48</v>
       </c>
       <c r="E54" t="s">
-        <v>914</v>
+        <v>902</v>
       </c>
       <c r="F54" t="s">
-        <v>680</v>
+        <v>903</v>
       </c>
       <c r="G54" t="s">
-        <v>915</v>
+        <v>904</v>
       </c>
       <c r="H54" t="s">
         <v>52</v>
@@ -27586,10 +27625,10 @@
         <v>54</v>
       </c>
       <c r="K54" t="s">
-        <v>222</v>
+        <v>905</v>
       </c>
       <c r="L54" t="s">
-        <v>680</v>
+        <v>903</v>
       </c>
       <c r="M54" t="s">
         <v>56</v>
@@ -27601,28 +27640,28 @@
         <v>58</v>
       </c>
       <c r="P54" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="Q54" t="s">
         <v>60</v>
       </c>
       <c r="R54" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S54" t="s">
         <v>61</v>
       </c>
       <c r="T54" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="U54" s="1">
-        <v>3803.8</v>
+        <v>4118.8</v>
       </c>
       <c r="V54" s="1">
-        <v>3754.2</v>
+        <v>4105.3</v>
       </c>
       <c r="W54" s="1">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="X54" s="1">
         <v>0</v>
@@ -27634,55 +27673,55 @@
         <v>1228</v>
       </c>
       <c r="AA54" s="1">
-        <v>4671066.4000000004</v>
+        <v>5057886.4000000004</v>
       </c>
       <c r="AB54" s="1">
-        <v>15227.2</v>
+        <v>0</v>
       </c>
       <c r="AC54" s="1">
-        <v>4807354</v>
+        <v>5253027</v>
       </c>
       <c r="AD54" s="1">
-        <v>24750</v>
+        <v>72570</v>
       </c>
       <c r="AE54" s="1">
-        <v>0</v>
+        <v>26550</v>
       </c>
       <c r="AF54" t="s">
         <v>64</v>
       </c>
       <c r="AH54" t="s">
-        <v>917</v>
+        <v>907</v>
       </c>
       <c r="AI54" s="1">
-        <v>16500</v>
+        <v>0</v>
       </c>
       <c r="AJ54" s="1">
-        <v>30880</v>
+        <v>0</v>
       </c>
       <c r="AK54" s="1">
-        <v>73680</v>
+        <v>0</v>
       </c>
       <c r="AL54" s="1">
-        <v>15227.2</v>
+        <v>0</v>
       </c>
       <c r="AM54" s="1">
         <v>0</v>
       </c>
       <c r="AN54" s="1">
-        <v>0</v>
+        <v>195140</v>
       </c>
       <c r="AO54" s="1">
-        <v>240368</v>
+        <v>262652</v>
       </c>
       <c r="AP54" s="1">
-        <v>136287.20000000001</v>
+        <v>195140</v>
       </c>
       <c r="AQ54" s="1">
-        <v>5047722</v>
+        <v>5515679</v>
       </c>
       <c r="AR54" s="1">
-        <v>5072472</v>
+        <v>5614799</v>
       </c>
     </row>
     <row r="55" spans="1:44" x14ac:dyDescent="0.35">
@@ -27693,19 +27732,19 @@
         <v>46</v>
       </c>
       <c r="C55" t="s">
-        <v>506</v>
+        <v>357</v>
       </c>
       <c r="D55" t="s">
         <v>48</v>
       </c>
       <c r="E55" t="s">
-        <v>918</v>
+        <v>908</v>
       </c>
       <c r="F55" t="s">
-        <v>686</v>
+        <v>909</v>
       </c>
       <c r="G55" t="s">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="H55" t="s">
         <v>52</v>
@@ -27717,13 +27756,13 @@
         <v>54</v>
       </c>
       <c r="K55" t="s">
-        <v>227</v>
+        <v>911</v>
       </c>
       <c r="L55" t="s">
-        <v>686</v>
+        <v>909</v>
       </c>
       <c r="M55" t="s">
-        <v>212</v>
+        <v>56</v>
       </c>
       <c r="N55" t="s">
         <v>57</v>
@@ -27732,7 +27771,7 @@
         <v>58</v>
       </c>
       <c r="P55" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="Q55" t="s">
         <v>60</v>
@@ -27744,16 +27783,16 @@
         <v>61</v>
       </c>
       <c r="T55" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="U55" s="1">
-        <v>3999.2</v>
+        <v>3908.8</v>
       </c>
       <c r="V55" s="1">
-        <v>3885</v>
+        <v>3894.4</v>
       </c>
       <c r="W55" s="1">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="X55" s="1">
         <v>0</v>
@@ -27765,55 +27804,55 @@
         <v>1228</v>
       </c>
       <c r="AA55" s="1">
-        <v>4911017.5999999996</v>
+        <v>4800006.4000000004</v>
       </c>
       <c r="AB55" s="1">
-        <v>13753.6</v>
+        <v>0</v>
       </c>
       <c r="AC55" s="1">
-        <v>5007136</v>
+        <v>4870967</v>
       </c>
       <c r="AD55" s="1">
-        <v>8550</v>
+        <v>0</v>
       </c>
       <c r="AE55" s="1">
-        <v>42750</v>
+        <v>59640</v>
       </c>
       <c r="AF55" t="s">
         <v>64</v>
       </c>
       <c r="AH55" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="AI55" s="1">
-        <v>17100</v>
+        <v>0</v>
       </c>
       <c r="AJ55" s="1">
-        <v>30880</v>
+        <v>0</v>
       </c>
       <c r="AK55" s="1">
-        <v>34384</v>
+        <v>0</v>
       </c>
       <c r="AL55" s="1">
-        <v>13753.6</v>
+        <v>0</v>
       </c>
       <c r="AM55" s="1">
         <v>0</v>
       </c>
       <c r="AN55" s="1">
-        <v>0</v>
+        <v>70960</v>
       </c>
       <c r="AO55" s="1">
-        <v>250357</v>
+        <v>243549</v>
       </c>
       <c r="AP55" s="1">
-        <v>96117.6</v>
+        <v>70960</v>
       </c>
       <c r="AQ55" s="1">
-        <v>5257493</v>
+        <v>5114516</v>
       </c>
       <c r="AR55" s="1">
-        <v>5308793</v>
+        <v>5174156</v>
       </c>
     </row>
     <row r="56" spans="1:44" x14ac:dyDescent="0.35">
@@ -27830,13 +27869,13 @@
         <v>48</v>
       </c>
       <c r="E56" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
       <c r="F56" t="s">
-        <v>708</v>
+        <v>680</v>
       </c>
       <c r="G56" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="H56" t="s">
         <v>52</v>
@@ -27848,13 +27887,13 @@
         <v>54</v>
       </c>
       <c r="K56" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="L56" t="s">
-        <v>708</v>
+        <v>680</v>
       </c>
       <c r="M56" t="s">
-        <v>212</v>
+        <v>56</v>
       </c>
       <c r="N56" t="s">
         <v>57</v>
@@ -27869,22 +27908,22 @@
         <v>60</v>
       </c>
       <c r="R56" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="S56" t="s">
         <v>61</v>
       </c>
       <c r="T56" t="s">
-        <v>924</v>
+        <v>916</v>
       </c>
       <c r="U56" s="1">
-        <v>3957.4</v>
+        <v>3803.8</v>
       </c>
       <c r="V56" s="1">
-        <v>3934</v>
+        <v>3754.2</v>
       </c>
       <c r="W56" s="1">
-        <v>17.8</v>
+        <v>6.2</v>
       </c>
       <c r="X56" s="1">
         <v>0</v>
@@ -27896,37 +27935,37 @@
         <v>1228</v>
       </c>
       <c r="AA56" s="1">
-        <v>4859687.2</v>
+        <v>4671066.4000000004</v>
       </c>
       <c r="AB56" s="1">
-        <v>65575.199999999997</v>
+        <v>15227.2</v>
       </c>
       <c r="AC56" s="1">
-        <v>5269371</v>
+        <v>4807354</v>
       </c>
       <c r="AD56" s="1">
-        <v>17100</v>
+        <v>24750</v>
       </c>
       <c r="AE56" s="1">
-        <v>79515</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="s">
         <v>64</v>
       </c>
       <c r="AH56" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="AI56" s="1">
-        <v>17100</v>
+        <v>16500</v>
       </c>
       <c r="AJ56" s="1">
-        <v>61760</v>
+        <v>30880</v>
       </c>
       <c r="AK56" s="1">
-        <v>265248</v>
+        <v>73680</v>
       </c>
       <c r="AL56" s="1">
-        <v>65575.199999999997</v>
+        <v>15227.2</v>
       </c>
       <c r="AM56" s="1">
         <v>0</v>
@@ -27935,16 +27974,16 @@
         <v>0</v>
       </c>
       <c r="AO56" s="1">
-        <v>263469</v>
+        <v>240368</v>
       </c>
       <c r="AP56" s="1">
-        <v>409683.20000000001</v>
+        <v>136287.20000000001</v>
       </c>
       <c r="AQ56" s="1">
-        <v>5532840</v>
+        <v>5047722</v>
       </c>
       <c r="AR56" s="1">
-        <v>5629455</v>
+        <v>5072472</v>
       </c>
     </row>
     <row r="57" spans="1:44" x14ac:dyDescent="0.35">
@@ -27961,13 +28000,13 @@
         <v>48</v>
       </c>
       <c r="E57" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="F57" t="s">
-        <v>719</v>
+        <v>686</v>
       </c>
       <c r="G57" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="H57" t="s">
         <v>52</v>
@@ -27979,10 +28018,10 @@
         <v>54</v>
       </c>
       <c r="K57" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="L57" t="s">
-        <v>719</v>
+        <v>686</v>
       </c>
       <c r="M57" t="s">
         <v>212</v>
@@ -28006,16 +28045,16 @@
         <v>61</v>
       </c>
       <c r="T57" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="U57" s="1">
-        <v>3753.6</v>
+        <v>3999.2</v>
       </c>
       <c r="V57" s="1">
-        <v>3737.7</v>
+        <v>3885</v>
       </c>
       <c r="W57" s="1">
-        <v>26</v>
+        <v>5.6</v>
       </c>
       <c r="X57" s="1">
         <v>0</v>
@@ -28027,37 +28066,37 @@
         <v>1228</v>
       </c>
       <c r="AA57" s="1">
-        <v>4609420.8</v>
+        <v>4911017.5999999996</v>
       </c>
       <c r="AB57" s="1">
-        <v>95784</v>
+        <v>13753.6</v>
       </c>
       <c r="AC57" s="1">
-        <v>4884909</v>
+        <v>5007136</v>
       </c>
       <c r="AD57" s="1">
-        <v>40500</v>
+        <v>8550</v>
       </c>
       <c r="AE57" s="1">
-        <v>24300</v>
+        <v>42750</v>
       </c>
       <c r="AF57" t="s">
         <v>64</v>
       </c>
       <c r="AH57" t="s">
-        <v>929</v>
+        <v>921</v>
       </c>
       <c r="AI57" s="1">
-        <v>16200</v>
+        <v>17100</v>
       </c>
       <c r="AJ57" s="1">
         <v>30880</v>
       </c>
       <c r="AK57" s="1">
-        <v>132624</v>
+        <v>34384</v>
       </c>
       <c r="AL57" s="1">
-        <v>95784</v>
+        <v>13753.6</v>
       </c>
       <c r="AM57" s="1">
         <v>0</v>
@@ -28066,16 +28105,16 @@
         <v>0</v>
       </c>
       <c r="AO57" s="1">
-        <v>244246</v>
+        <v>250357</v>
       </c>
       <c r="AP57" s="1">
-        <v>275488</v>
+        <v>96117.6</v>
       </c>
       <c r="AQ57" s="1">
-        <v>5129155</v>
+        <v>5257493</v>
       </c>
       <c r="AR57" s="1">
-        <v>5193955</v>
+        <v>5308793</v>
       </c>
     </row>
     <row r="58" spans="1:44" x14ac:dyDescent="0.35">
@@ -28092,13 +28131,13 @@
         <v>48</v>
       </c>
       <c r="E58" t="s">
-        <v>930</v>
+        <v>922</v>
       </c>
       <c r="F58" t="s">
-        <v>725</v>
+        <v>708</v>
       </c>
       <c r="G58" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="H58" t="s">
         <v>52</v>
@@ -28110,10 +28149,10 @@
         <v>54</v>
       </c>
       <c r="K58" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="L58" t="s">
-        <v>725</v>
+        <v>708</v>
       </c>
       <c r="M58" t="s">
         <v>212</v>
@@ -28137,16 +28176,16 @@
         <v>61</v>
       </c>
       <c r="T58" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="U58" s="1">
-        <v>3788.4</v>
+        <v>3957.4</v>
       </c>
       <c r="V58" s="1">
-        <v>3738.9</v>
+        <v>3934</v>
       </c>
       <c r="W58" s="1">
-        <v>11.4</v>
+        <v>17.8</v>
       </c>
       <c r="X58" s="1">
         <v>0</v>
@@ -28158,37 +28197,37 @@
         <v>1228</v>
       </c>
       <c r="AA58" s="1">
-        <v>4652155.2</v>
+        <v>4859687.2</v>
       </c>
       <c r="AB58" s="1">
-        <v>27998.400000000001</v>
+        <v>65575.199999999997</v>
       </c>
       <c r="AC58" s="1">
-        <v>4766830</v>
+        <v>5269371</v>
       </c>
       <c r="AD58" s="1">
-        <v>33000</v>
+        <v>17100</v>
       </c>
       <c r="AE58" s="1">
-        <v>0</v>
+        <v>79515</v>
       </c>
       <c r="AF58" t="s">
         <v>64</v>
       </c>
       <c r="AH58" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="AI58" s="1">
-        <v>16500</v>
+        <v>17100</v>
       </c>
       <c r="AJ58" s="1">
-        <v>30880</v>
+        <v>61760</v>
       </c>
       <c r="AK58" s="1">
-        <v>39296</v>
+        <v>265248</v>
       </c>
       <c r="AL58" s="1">
-        <v>27998.400000000001</v>
+        <v>65575.199999999997</v>
       </c>
       <c r="AM58" s="1">
         <v>0</v>
@@ -28197,16 +28236,16 @@
         <v>0</v>
       </c>
       <c r="AO58" s="1">
-        <v>238342</v>
+        <v>263469</v>
       </c>
       <c r="AP58" s="1">
-        <v>114674.4</v>
+        <v>409683.20000000001</v>
       </c>
       <c r="AQ58" s="1">
-        <v>5005172</v>
+        <v>5532840</v>
       </c>
       <c r="AR58" s="1">
-        <v>5038172</v>
+        <v>5629455</v>
       </c>
     </row>
     <row r="59" spans="1:44" x14ac:dyDescent="0.35">
@@ -28223,13 +28262,13 @@
         <v>48</v>
       </c>
       <c r="E59" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="F59" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="G59" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="H59" t="s">
         <v>52</v>
@@ -28241,10 +28280,10 @@
         <v>54</v>
       </c>
       <c r="K59" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="L59" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="M59" t="s">
         <v>212</v>
@@ -28268,16 +28307,16 @@
         <v>61</v>
       </c>
       <c r="T59" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="U59" s="1">
-        <v>4032.2</v>
+        <v>3753.6</v>
       </c>
       <c r="V59" s="1">
-        <v>3959.3</v>
+        <v>3737.7</v>
       </c>
       <c r="W59" s="1">
-        <v>9.8000000000000007</v>
+        <v>26</v>
       </c>
       <c r="X59" s="1">
         <v>0</v>
@@ -28289,37 +28328,37 @@
         <v>1228</v>
       </c>
       <c r="AA59" s="1">
-        <v>4951541.5999999996</v>
+        <v>4609420.8</v>
       </c>
       <c r="AB59" s="1">
-        <v>24068.799999999999</v>
+        <v>95784</v>
       </c>
       <c r="AC59" s="1">
-        <v>5077923</v>
+        <v>4884909</v>
       </c>
       <c r="AD59" s="1">
-        <v>17400</v>
+        <v>40500</v>
       </c>
       <c r="AE59" s="1">
-        <v>17400</v>
+        <v>24300</v>
       </c>
       <c r="AF59" t="s">
         <v>64</v>
       </c>
       <c r="AH59" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="AI59" s="1">
-        <v>17400</v>
+        <v>16200</v>
       </c>
       <c r="AJ59" s="1">
         <v>30880</v>
       </c>
       <c r="AK59" s="1">
-        <v>54032</v>
+        <v>132624</v>
       </c>
       <c r="AL59" s="1">
-        <v>24068.799999999999</v>
+        <v>95784</v>
       </c>
       <c r="AM59" s="1">
         <v>0</v>
@@ -28328,16 +28367,16 @@
         <v>0</v>
       </c>
       <c r="AO59" s="1">
-        <v>253897</v>
+        <v>244246</v>
       </c>
       <c r="AP59" s="1">
-        <v>126380.8</v>
+        <v>275488</v>
       </c>
       <c r="AQ59" s="1">
-        <v>5331820</v>
+        <v>5129155</v>
       </c>
       <c r="AR59" s="1">
-        <v>5366620</v>
+        <v>5193955</v>
       </c>
     </row>
     <row r="60" spans="1:44" x14ac:dyDescent="0.35">
@@ -28354,13 +28393,13 @@
         <v>48</v>
       </c>
       <c r="E60" t="s">
-        <v>938</v>
+        <v>930</v>
       </c>
       <c r="F60" t="s">
-        <v>742</v>
+        <v>725</v>
       </c>
       <c r="G60" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="H60" t="s">
         <v>52</v>
@@ -28372,10 +28411,10 @@
         <v>54</v>
       </c>
       <c r="K60" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="L60" t="s">
-        <v>742</v>
+        <v>725</v>
       </c>
       <c r="M60" t="s">
         <v>212</v>
@@ -28399,16 +28438,16 @@
         <v>61</v>
       </c>
       <c r="T60" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="U60" s="1">
-        <v>3595</v>
+        <v>3788.4</v>
       </c>
       <c r="V60" s="1">
-        <v>3496.1</v>
+        <v>3738.9</v>
       </c>
       <c r="W60" s="1">
-        <v>4.2</v>
+        <v>11.4</v>
       </c>
       <c r="X60" s="1">
         <v>0</v>
@@ -28420,16 +28459,16 @@
         <v>1228</v>
       </c>
       <c r="AA60" s="1">
-        <v>4414660</v>
+        <v>4652155.2</v>
       </c>
       <c r="AB60" s="1">
-        <v>10315.200000000001</v>
+        <v>27998.400000000001</v>
       </c>
       <c r="AC60" s="1">
-        <v>4500928</v>
+        <v>4766830</v>
       </c>
       <c r="AD60" s="1">
-        <v>15600</v>
+        <v>33000</v>
       </c>
       <c r="AE60" s="1">
         <v>0</v>
@@ -28438,19 +28477,19 @@
         <v>64</v>
       </c>
       <c r="AH60" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="AI60" s="1">
-        <v>15600</v>
+        <v>16500</v>
       </c>
       <c r="AJ60" s="1">
         <v>30880</v>
       </c>
       <c r="AK60" s="1">
-        <v>29472</v>
+        <v>39296</v>
       </c>
       <c r="AL60" s="1">
-        <v>10315.200000000001</v>
+        <v>27998.400000000001</v>
       </c>
       <c r="AM60" s="1">
         <v>0</v>
@@ -28459,16 +28498,16 @@
         <v>0</v>
       </c>
       <c r="AO60" s="1">
-        <v>225047</v>
+        <v>238342</v>
       </c>
       <c r="AP60" s="1">
-        <v>86267.199999999997</v>
+        <v>114674.4</v>
       </c>
       <c r="AQ60" s="1">
-        <v>4725975</v>
+        <v>5005172</v>
       </c>
       <c r="AR60" s="1">
-        <v>4741575</v>
+        <v>5038172</v>
       </c>
     </row>
     <row r="61" spans="1:44" x14ac:dyDescent="0.35">
@@ -28485,13 +28524,13 @@
         <v>48</v>
       </c>
       <c r="E61" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="F61" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
       <c r="G61" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="H61" t="s">
         <v>52</v>
@@ -28503,10 +28542,10 @@
         <v>54</v>
       </c>
       <c r="K61" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="L61" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
       <c r="M61" t="s">
         <v>212</v>
@@ -28530,16 +28569,16 @@
         <v>61</v>
       </c>
       <c r="T61" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="U61" s="1">
-        <v>4075</v>
+        <v>4032.2</v>
       </c>
       <c r="V61" s="1">
-        <v>4008.6</v>
+        <v>3959.3</v>
       </c>
       <c r="W61" s="1">
-        <v>7.4</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="X61" s="1">
         <v>0</v>
@@ -28551,37 +28590,37 @@
         <v>1228</v>
       </c>
       <c r="AA61" s="1">
-        <v>5004100</v>
+        <v>4951541.5999999996</v>
       </c>
       <c r="AB61" s="1">
-        <v>18174.400000000001</v>
+        <v>24068.799999999999</v>
       </c>
       <c r="AC61" s="1">
-        <v>5250855</v>
+        <v>5077923</v>
       </c>
       <c r="AD61" s="1">
-        <v>17700</v>
+        <v>17400</v>
       </c>
       <c r="AE61" s="1">
-        <v>0</v>
+        <v>17400</v>
       </c>
       <c r="AF61" t="s">
         <v>64</v>
       </c>
       <c r="AH61" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="AI61" s="1">
-        <v>17700</v>
+        <v>17400</v>
       </c>
       <c r="AJ61" s="1">
-        <v>61760</v>
+        <v>30880</v>
       </c>
       <c r="AK61" s="1">
-        <v>149120</v>
+        <v>54032</v>
       </c>
       <c r="AL61" s="1">
-        <v>18174.400000000001</v>
+        <v>24068.799999999999</v>
       </c>
       <c r="AM61" s="1">
         <v>0</v>
@@ -28590,16 +28629,16 @@
         <v>0</v>
       </c>
       <c r="AO61" s="1">
-        <v>262543</v>
+        <v>253897</v>
       </c>
       <c r="AP61" s="1">
-        <v>246754.4</v>
+        <v>126380.8</v>
       </c>
       <c r="AQ61" s="1">
-        <v>5513398</v>
+        <v>5331820</v>
       </c>
       <c r="AR61" s="1">
-        <v>5531098</v>
+        <v>5366620</v>
       </c>
     </row>
     <row r="62" spans="1:44" x14ac:dyDescent="0.35">
@@ -28616,13 +28655,13 @@
         <v>48</v>
       </c>
       <c r="E62" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="F62" t="s">
-        <v>854</v>
+        <v>742</v>
       </c>
       <c r="G62" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="H62" t="s">
         <v>52</v>
@@ -28634,13 +28673,13 @@
         <v>54</v>
       </c>
       <c r="K62" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="L62" t="s">
-        <v>854</v>
+        <v>742</v>
       </c>
       <c r="M62" t="s">
-        <v>56</v>
+        <v>212</v>
       </c>
       <c r="N62" t="s">
         <v>57</v>
@@ -28661,16 +28700,16 @@
         <v>61</v>
       </c>
       <c r="T62" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="U62" s="1">
-        <v>3831.4</v>
+        <v>3595</v>
       </c>
       <c r="V62" s="1">
-        <v>3667.1</v>
+        <v>3496.1</v>
       </c>
       <c r="W62" s="1">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="X62" s="1">
         <v>0</v>
@@ -28682,16 +28721,16 @@
         <v>1228</v>
       </c>
       <c r="AA62" s="1">
-        <v>4704959.2</v>
+        <v>4414660</v>
       </c>
       <c r="AB62" s="1">
-        <v>12280</v>
+        <v>10315.200000000001</v>
       </c>
       <c r="AC62" s="1">
-        <v>4871256</v>
+        <v>4500928</v>
       </c>
       <c r="AD62" s="1">
-        <v>25200</v>
+        <v>15600</v>
       </c>
       <c r="AE62" s="1">
         <v>0</v>
@@ -28700,19 +28739,19 @@
         <v>64</v>
       </c>
       <c r="AH62" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="AI62" s="1">
-        <v>8400</v>
+        <v>15600</v>
       </c>
       <c r="AJ62" s="1">
         <v>30880</v>
       </c>
       <c r="AK62" s="1">
-        <v>114736</v>
+        <v>29472</v>
       </c>
       <c r="AL62" s="1">
-        <v>12280</v>
+        <v>10315.200000000001</v>
       </c>
       <c r="AM62" s="1">
         <v>0</v>
@@ -28721,16 +28760,16 @@
         <v>0</v>
       </c>
       <c r="AO62" s="1">
-        <v>243563</v>
+        <v>225047</v>
       </c>
       <c r="AP62" s="1">
-        <v>166296</v>
+        <v>86267.199999999997</v>
       </c>
       <c r="AQ62" s="1">
-        <v>5114819</v>
+        <v>4725975</v>
       </c>
       <c r="AR62" s="1">
-        <v>5140019</v>
+        <v>4741575</v>
       </c>
     </row>
     <row r="63" spans="1:44" x14ac:dyDescent="0.35">
@@ -28747,13 +28786,13 @@
         <v>48</v>
       </c>
       <c r="E63" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="F63" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="G63" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="H63" t="s">
         <v>52</v>
@@ -28765,10 +28804,10 @@
         <v>54</v>
       </c>
       <c r="K63" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="L63" t="s">
-        <v>854</v>
+        <v>748</v>
       </c>
       <c r="M63" t="s">
         <v>212</v>
@@ -28792,16 +28831,16 @@
         <v>61</v>
       </c>
       <c r="T63" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="U63" s="1">
-        <v>3953.4</v>
+        <v>4075</v>
       </c>
       <c r="V63" s="1">
-        <v>3916</v>
+        <v>4008.6</v>
       </c>
       <c r="W63" s="1">
-        <v>13.6</v>
+        <v>7.4</v>
       </c>
       <c r="X63" s="1">
         <v>0</v>
@@ -28813,37 +28852,37 @@
         <v>1228</v>
       </c>
       <c r="AA63" s="1">
-        <v>4854775.2</v>
+        <v>5004100</v>
       </c>
       <c r="AB63" s="1">
-        <v>33401.599999999999</v>
+        <v>18174.400000000001</v>
       </c>
       <c r="AC63" s="1">
-        <v>4965629</v>
+        <v>5250855</v>
       </c>
       <c r="AD63" s="1">
-        <v>17100</v>
+        <v>17700</v>
       </c>
       <c r="AE63" s="1">
-        <v>139792.5</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="s">
         <v>64</v>
       </c>
       <c r="AH63" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="AI63" s="1">
-        <v>17100</v>
+        <v>17700</v>
       </c>
       <c r="AJ63" s="1">
-        <v>30880</v>
+        <v>61760</v>
       </c>
       <c r="AK63" s="1">
-        <v>29472</v>
+        <v>149120</v>
       </c>
       <c r="AL63" s="1">
-        <v>33401.599999999999</v>
+        <v>18174.400000000001</v>
       </c>
       <c r="AM63" s="1">
         <v>0</v>
@@ -28852,16 +28891,16 @@
         <v>0</v>
       </c>
       <c r="AO63" s="1">
-        <v>248282</v>
+        <v>262543</v>
       </c>
       <c r="AP63" s="1">
-        <v>110853.6</v>
+        <v>246754.4</v>
       </c>
       <c r="AQ63" s="1">
-        <v>5213911</v>
+        <v>5513398</v>
       </c>
       <c r="AR63" s="1">
-        <v>5370803.5</v>
+        <v>5531098</v>
       </c>
     </row>
     <row r="64" spans="1:44" x14ac:dyDescent="0.35">
@@ -28878,13 +28917,13 @@
         <v>48</v>
       </c>
       <c r="E64" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="F64" t="s">
-        <v>759</v>
+        <v>854</v>
       </c>
       <c r="G64" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
       <c r="H64" t="s">
         <v>52</v>
@@ -28896,10 +28935,10 @@
         <v>54</v>
       </c>
       <c r="K64" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="L64" t="s">
-        <v>759</v>
+        <v>854</v>
       </c>
       <c r="M64" t="s">
         <v>56</v>
@@ -28917,22 +28956,22 @@
         <v>60</v>
       </c>
       <c r="R64" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S64" t="s">
         <v>61</v>
       </c>
       <c r="T64" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="U64" s="1">
-        <v>4076.4</v>
+        <v>3831.4</v>
       </c>
       <c r="V64" s="1">
-        <v>4057</v>
+        <v>3667.1</v>
       </c>
       <c r="W64" s="1">
-        <v>22.6</v>
+        <v>5</v>
       </c>
       <c r="X64" s="1">
         <v>0</v>
@@ -28944,37 +28983,37 @@
         <v>1228</v>
       </c>
       <c r="AA64" s="1">
-        <v>5005819.2</v>
+        <v>4704959.2</v>
       </c>
       <c r="AB64" s="1">
-        <v>83258.399999999994</v>
+        <v>12280</v>
       </c>
       <c r="AC64" s="1">
-        <v>5433786</v>
+        <v>4871256</v>
       </c>
       <c r="AD64" s="1">
-        <v>17700</v>
+        <v>25200</v>
       </c>
       <c r="AE64" s="1">
-        <v>26550</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="s">
         <v>64</v>
       </c>
       <c r="AH64" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="AI64" s="1">
-        <v>17700</v>
+        <v>8400</v>
       </c>
       <c r="AJ64" s="1">
-        <v>61760</v>
+        <v>30880</v>
       </c>
       <c r="AK64" s="1">
-        <v>265248</v>
+        <v>114736</v>
       </c>
       <c r="AL64" s="1">
-        <v>83258.399999999994</v>
+        <v>12280</v>
       </c>
       <c r="AM64" s="1">
         <v>0</v>
@@ -28983,16 +29022,16 @@
         <v>0</v>
       </c>
       <c r="AO64" s="1">
-        <v>271690</v>
+        <v>243563</v>
       </c>
       <c r="AP64" s="1">
-        <v>427966.4</v>
+        <v>166296</v>
       </c>
       <c r="AQ64" s="1">
-        <v>5705476</v>
+        <v>5114819</v>
       </c>
       <c r="AR64" s="1">
-        <v>5749726</v>
+        <v>5140019</v>
       </c>
     </row>
     <row r="65" spans="1:44" x14ac:dyDescent="0.35">
@@ -29009,13 +29048,13 @@
         <v>48</v>
       </c>
       <c r="E65" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="F65" t="s">
-        <v>867</v>
+        <v>759</v>
       </c>
       <c r="G65" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
       <c r="H65" t="s">
         <v>52</v>
@@ -29027,13 +29066,13 @@
         <v>54</v>
       </c>
       <c r="K65" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="L65" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
       <c r="M65" t="s">
-        <v>56</v>
+        <v>212</v>
       </c>
       <c r="N65" t="s">
         <v>57</v>
@@ -29048,22 +29087,22 @@
         <v>60</v>
       </c>
       <c r="R65" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S65" t="s">
         <v>61</v>
       </c>
       <c r="T65" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="U65" s="1">
-        <v>3942.2</v>
+        <v>3953.4</v>
       </c>
       <c r="V65" s="1">
-        <v>3927.6</v>
+        <v>3916</v>
       </c>
       <c r="W65" s="1">
-        <v>25.6</v>
+        <v>13.6</v>
       </c>
       <c r="X65" s="1">
         <v>0</v>
@@ -29075,25 +29114,25 @@
         <v>1228</v>
       </c>
       <c r="AA65" s="1">
-        <v>4841021.5999999996</v>
+        <v>4854775.2</v>
       </c>
       <c r="AB65" s="1">
-        <v>94310.399999999994</v>
+        <v>33401.599999999999</v>
       </c>
       <c r="AC65" s="1">
-        <v>5171196</v>
+        <v>4965629</v>
       </c>
       <c r="AD65" s="1">
-        <v>25650</v>
+        <v>17100</v>
       </c>
       <c r="AE65" s="1">
-        <v>51300</v>
+        <v>139792.5</v>
       </c>
       <c r="AF65" t="s">
         <v>64</v>
       </c>
       <c r="AH65" t="s">
-        <v>961</v>
+        <v>953</v>
       </c>
       <c r="AI65" s="1">
         <v>17100</v>
@@ -29102,10 +29141,10 @@
         <v>30880</v>
       </c>
       <c r="AK65" s="1">
-        <v>187884</v>
+        <v>29472</v>
       </c>
       <c r="AL65" s="1">
-        <v>94310.399999999994</v>
+        <v>33401.599999999999</v>
       </c>
       <c r="AM65" s="1">
         <v>0</v>
@@ -29114,16 +29153,16 @@
         <v>0</v>
       </c>
       <c r="AO65" s="1">
-        <v>258560</v>
+        <v>248282</v>
       </c>
       <c r="AP65" s="1">
-        <v>330174.40000000002</v>
+        <v>110853.6</v>
       </c>
       <c r="AQ65" s="1">
-        <v>5429756</v>
+        <v>5213911</v>
       </c>
       <c r="AR65" s="1">
-        <v>5506706</v>
+        <v>5370803.5</v>
       </c>
     </row>
     <row r="66" spans="1:44" x14ac:dyDescent="0.35">
@@ -29140,13 +29179,13 @@
         <v>48</v>
       </c>
       <c r="E66" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="F66" t="s">
-        <v>867</v>
+        <v>759</v>
       </c>
       <c r="G66" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="H66" t="s">
         <v>52</v>
@@ -29158,13 +29197,13 @@
         <v>54</v>
       </c>
       <c r="K66" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="L66" t="s">
-        <v>867</v>
+        <v>759</v>
       </c>
       <c r="M66" t="s">
-        <v>212</v>
+        <v>56</v>
       </c>
       <c r="N66" t="s">
         <v>57</v>
@@ -29179,22 +29218,22 @@
         <v>60</v>
       </c>
       <c r="R66" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="S66" t="s">
         <v>61</v>
       </c>
       <c r="T66" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="U66" s="1">
-        <v>3893</v>
+        <v>4076.4</v>
       </c>
       <c r="V66" s="1">
-        <v>3866.9</v>
+        <v>4057</v>
       </c>
       <c r="W66" s="1">
-        <v>16</v>
+        <v>22.6</v>
       </c>
       <c r="X66" s="1">
         <v>0</v>
@@ -29206,37 +29245,37 @@
         <v>1228</v>
       </c>
       <c r="AA66" s="1">
-        <v>4780604</v>
+        <v>5005819.2</v>
       </c>
       <c r="AB66" s="1">
-        <v>58944</v>
+        <v>83258.399999999994</v>
       </c>
       <c r="AC66" s="1">
-        <v>5076778</v>
+        <v>5433786</v>
       </c>
       <c r="AD66" s="1">
-        <v>25200</v>
+        <v>17700</v>
       </c>
       <c r="AE66" s="1">
-        <v>87360</v>
+        <v>26550</v>
       </c>
       <c r="AF66" t="s">
         <v>64</v>
       </c>
       <c r="AH66" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
       <c r="AI66" s="1">
-        <v>16800</v>
+        <v>17700</v>
       </c>
       <c r="AJ66" s="1">
         <v>61760</v>
       </c>
       <c r="AK66" s="1">
-        <v>158670</v>
+        <v>265248</v>
       </c>
       <c r="AL66" s="1">
-        <v>58944</v>
+        <v>83258.399999999994</v>
       </c>
       <c r="AM66" s="1">
         <v>0</v>
@@ -29245,16 +29284,16 @@
         <v>0</v>
       </c>
       <c r="AO66" s="1">
-        <v>253839</v>
+        <v>271690</v>
       </c>
       <c r="AP66" s="1">
-        <v>296174</v>
+        <v>427966.4</v>
       </c>
       <c r="AQ66" s="1">
-        <v>5330617</v>
+        <v>5705476</v>
       </c>
       <c r="AR66" s="1">
-        <v>5443177</v>
+        <v>5749726</v>
       </c>
     </row>
     <row r="67" spans="1:44" x14ac:dyDescent="0.35">
@@ -29271,13 +29310,13 @@
         <v>48</v>
       </c>
       <c r="E67" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="F67" t="s">
-        <v>765</v>
+        <v>867</v>
       </c>
       <c r="G67" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="H67" t="s">
         <v>52</v>
@@ -29289,13 +29328,13 @@
         <v>54</v>
       </c>
       <c r="K67" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="L67" t="s">
-        <v>765</v>
+        <v>867</v>
       </c>
       <c r="M67" t="s">
-        <v>212</v>
+        <v>56</v>
       </c>
       <c r="N67" t="s">
         <v>57</v>
@@ -29310,22 +29349,22 @@
         <v>60</v>
       </c>
       <c r="R67" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="S67" t="s">
         <v>61</v>
       </c>
       <c r="T67" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="U67" s="1">
-        <v>3817.8</v>
+        <v>3942.2</v>
       </c>
       <c r="V67" s="1">
-        <v>3804.9</v>
+        <v>3927.6</v>
       </c>
       <c r="W67" s="1">
-        <v>23.2</v>
+        <v>25.6</v>
       </c>
       <c r="X67" s="1">
         <v>0</v>
@@ -29337,37 +29376,37 @@
         <v>1228</v>
       </c>
       <c r="AA67" s="1">
-        <v>4688258.4000000004</v>
+        <v>4841021.5999999996</v>
       </c>
       <c r="AB67" s="1">
-        <v>85468.800000000003</v>
+        <v>94310.399999999994</v>
       </c>
       <c r="AC67" s="1">
-        <v>5183548</v>
+        <v>5171196</v>
       </c>
       <c r="AD67" s="1">
-        <v>49500</v>
+        <v>25650</v>
       </c>
       <c r="AE67" s="1">
-        <v>58575</v>
+        <v>51300</v>
       </c>
       <c r="AF67" t="s">
         <v>64</v>
       </c>
       <c r="AH67" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="AI67" s="1">
-        <v>16500</v>
+        <v>17100</v>
       </c>
       <c r="AJ67" s="1">
-        <v>61760</v>
+        <v>30880</v>
       </c>
       <c r="AK67" s="1">
-        <v>331560</v>
+        <v>187884</v>
       </c>
       <c r="AL67" s="1">
-        <v>85468.800000000003</v>
+        <v>94310.399999999994</v>
       </c>
       <c r="AM67" s="1">
         <v>0</v>
@@ -29376,16 +29415,16 @@
         <v>0</v>
       </c>
       <c r="AO67" s="1">
-        <v>259178</v>
+        <v>258560</v>
       </c>
       <c r="AP67" s="1">
-        <v>495288.8</v>
+        <v>330174.40000000002</v>
       </c>
       <c r="AQ67" s="1">
-        <v>5442726</v>
+        <v>5429756</v>
       </c>
       <c r="AR67" s="1">
-        <v>5550801</v>
+        <v>5506706</v>
       </c>
     </row>
     <row r="68" spans="1:44" x14ac:dyDescent="0.35">
@@ -29402,13 +29441,13 @@
         <v>48</v>
       </c>
       <c r="E68" t="s">
-        <v>970</v>
+        <v>962</v>
       </c>
       <c r="F68" t="s">
-        <v>771</v>
+        <v>867</v>
       </c>
       <c r="G68" t="s">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="H68" t="s">
         <v>52</v>
@@ -29420,13 +29459,13 @@
         <v>54</v>
       </c>
       <c r="K68" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="L68" t="s">
-        <v>771</v>
+        <v>867</v>
       </c>
       <c r="M68" t="s">
-        <v>56</v>
+        <v>212</v>
       </c>
       <c r="N68" t="s">
         <v>57</v>
@@ -29447,16 +29486,16 @@
         <v>61</v>
       </c>
       <c r="T68" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
       <c r="U68" s="1">
-        <v>3744.6</v>
+        <v>3893</v>
       </c>
       <c r="V68" s="1">
-        <v>3728.9</v>
+        <v>3866.9</v>
       </c>
       <c r="W68" s="1">
-        <v>23.2</v>
+        <v>16</v>
       </c>
       <c r="X68" s="1">
         <v>0</v>
@@ -29468,37 +29507,37 @@
         <v>1228</v>
       </c>
       <c r="AA68" s="1">
-        <v>4598368.8</v>
+        <v>4780604</v>
       </c>
       <c r="AB68" s="1">
-        <v>85468.800000000003</v>
+        <v>58944</v>
       </c>
       <c r="AC68" s="1">
-        <v>5038098</v>
+        <v>5076778</v>
       </c>
       <c r="AD68" s="1">
-        <v>24300</v>
+        <v>25200</v>
       </c>
       <c r="AE68" s="1">
-        <v>122310</v>
+        <v>87360</v>
       </c>
       <c r="AF68" t="s">
         <v>64</v>
       </c>
       <c r="AH68" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="AI68" s="1">
-        <v>16200</v>
+        <v>16800</v>
       </c>
       <c r="AJ68" s="1">
         <v>61760</v>
       </c>
       <c r="AK68" s="1">
-        <v>276300</v>
+        <v>158670</v>
       </c>
       <c r="AL68" s="1">
-        <v>85468.800000000003</v>
+        <v>58944</v>
       </c>
       <c r="AM68" s="1">
         <v>0</v>
@@ -29507,16 +29546,16 @@
         <v>0</v>
       </c>
       <c r="AO68" s="1">
-        <v>251905</v>
+        <v>253839</v>
       </c>
       <c r="AP68" s="1">
-        <v>439728.8</v>
+        <v>296174</v>
       </c>
       <c r="AQ68" s="1">
-        <v>5290003</v>
+        <v>5330617</v>
       </c>
       <c r="AR68" s="1">
-        <v>5436613</v>
+        <v>5443177</v>
       </c>
     </row>
     <row r="69" spans="1:44" x14ac:dyDescent="0.35">
@@ -29533,13 +29572,13 @@
         <v>48</v>
       </c>
       <c r="E69" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="F69" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="G69" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="H69" t="s">
         <v>52</v>
@@ -29551,10 +29590,10 @@
         <v>54</v>
       </c>
       <c r="K69" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="L69" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="M69" t="s">
         <v>212</v>
@@ -29578,16 +29617,16 @@
         <v>61</v>
       </c>
       <c r="T69" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="U69" s="1">
-        <v>3870.4</v>
+        <v>3817.8</v>
       </c>
       <c r="V69" s="1">
-        <v>3795</v>
+        <v>3804.9</v>
       </c>
       <c r="W69" s="1">
-        <v>10.4</v>
+        <v>23.2</v>
       </c>
       <c r="X69" s="1">
         <v>0</v>
@@ -29599,37 +29638,37 @@
         <v>1228</v>
       </c>
       <c r="AA69" s="1">
-        <v>4752851.2</v>
+        <v>4688258.4000000004</v>
       </c>
       <c r="AB69" s="1">
-        <v>25542.400000000001</v>
+        <v>85468.800000000003</v>
       </c>
       <c r="AC69" s="1">
-        <v>4855546</v>
+        <v>5183548</v>
       </c>
       <c r="AD69" s="1">
-        <v>16800</v>
+        <v>49500</v>
       </c>
       <c r="AE69" s="1">
-        <v>147840</v>
+        <v>58575</v>
       </c>
       <c r="AF69" t="s">
         <v>64</v>
       </c>
       <c r="AH69" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="AI69" s="1">
-        <v>16800</v>
+        <v>16500</v>
       </c>
       <c r="AJ69" s="1">
-        <v>30880</v>
+        <v>61760</v>
       </c>
       <c r="AK69" s="1">
-        <v>29472</v>
+        <v>331560</v>
       </c>
       <c r="AL69" s="1">
-        <v>25542.400000000001</v>
+        <v>85468.800000000003</v>
       </c>
       <c r="AM69" s="1">
         <v>0</v>
@@ -29638,16 +29677,16 @@
         <v>0</v>
       </c>
       <c r="AO69" s="1">
-        <v>242778</v>
+        <v>259178</v>
       </c>
       <c r="AP69" s="1">
-        <v>102694.39999999999</v>
+        <v>495288.8</v>
       </c>
       <c r="AQ69" s="1">
-        <v>5098324</v>
+        <v>5442726</v>
       </c>
       <c r="AR69" s="1">
-        <v>5262964</v>
+        <v>5550801</v>
       </c>
     </row>
     <row r="70" spans="1:44" x14ac:dyDescent="0.35">
@@ -29664,13 +29703,13 @@
         <v>48</v>
       </c>
       <c r="E70" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="F70" t="s">
-        <v>903</v>
+        <v>771</v>
       </c>
       <c r="G70" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="H70" t="s">
         <v>52</v>
@@ -29682,13 +29721,13 @@
         <v>54</v>
       </c>
       <c r="K70" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="L70" t="s">
-        <v>897</v>
+        <v>771</v>
       </c>
       <c r="M70" t="s">
-        <v>212</v>
+        <v>56</v>
       </c>
       <c r="N70" t="s">
         <v>57</v>
@@ -29709,16 +29748,16 @@
         <v>61</v>
       </c>
       <c r="T70" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="U70" s="1">
-        <v>3226.4</v>
+        <v>3744.6</v>
       </c>
       <c r="V70" s="1">
-        <v>3162.6</v>
+        <v>3728.9</v>
       </c>
       <c r="W70" s="1">
-        <v>3.4</v>
+        <v>23.2</v>
       </c>
       <c r="X70" s="1">
         <v>0</v>
@@ -29730,37 +29769,37 @@
         <v>1228</v>
       </c>
       <c r="AA70" s="1">
-        <v>3962019.2</v>
+        <v>4598368.8</v>
       </c>
       <c r="AB70" s="1">
-        <v>8350.4</v>
+        <v>85468.800000000003</v>
       </c>
       <c r="AC70" s="1">
-        <v>4069082</v>
+        <v>5038098</v>
       </c>
       <c r="AD70" s="1">
-        <v>27600</v>
+        <v>24300</v>
       </c>
       <c r="AE70" s="1">
-        <v>0</v>
+        <v>122310</v>
       </c>
       <c r="AF70" t="s">
         <v>64</v>
       </c>
       <c r="AH70" t="s">
-        <v>981</v>
+        <v>973</v>
       </c>
       <c r="AI70" s="1">
-        <v>13800</v>
+        <v>16200</v>
       </c>
       <c r="AJ70" s="1">
-        <v>30880</v>
+        <v>61760</v>
       </c>
       <c r="AK70" s="1">
-        <v>54032</v>
+        <v>276300</v>
       </c>
       <c r="AL70" s="1">
-        <v>8350.4</v>
+        <v>85468.800000000003</v>
       </c>
       <c r="AM70" s="1">
         <v>0</v>
@@ -29769,16 +29808,16 @@
         <v>0</v>
       </c>
       <c r="AO70" s="1">
-        <v>203455</v>
+        <v>251905</v>
       </c>
       <c r="AP70" s="1">
-        <v>107062.39999999999</v>
+        <v>439728.8</v>
       </c>
       <c r="AQ70" s="1">
-        <v>4272537</v>
+        <v>5290003</v>
       </c>
       <c r="AR70" s="1">
-        <v>4300137</v>
+        <v>5436613</v>
       </c>
     </row>
     <row r="71" spans="1:44" x14ac:dyDescent="0.35">
@@ -29795,13 +29834,13 @@
         <v>48</v>
       </c>
       <c r="E71" t="s">
-        <v>982</v>
+        <v>974</v>
       </c>
       <c r="F71" t="s">
-        <v>983</v>
+        <v>771</v>
       </c>
       <c r="G71" t="s">
-        <v>984</v>
+        <v>975</v>
       </c>
       <c r="H71" t="s">
         <v>52</v>
@@ -29813,10 +29852,10 @@
         <v>54</v>
       </c>
       <c r="K71" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="L71" t="s">
-        <v>903</v>
+        <v>771</v>
       </c>
       <c r="M71" t="s">
         <v>212</v>
@@ -29840,16 +29879,16 @@
         <v>61</v>
       </c>
       <c r="T71" t="s">
-        <v>985</v>
+        <v>976</v>
       </c>
       <c r="U71" s="1">
-        <v>4155.8</v>
+        <v>3870.4</v>
       </c>
       <c r="V71" s="1">
-        <v>4131.3</v>
+        <v>3795</v>
       </c>
       <c r="W71" s="1">
-        <v>20.6</v>
+        <v>10.4</v>
       </c>
       <c r="X71" s="1">
         <v>0</v>
@@ -29861,37 +29900,37 @@
         <v>1228</v>
       </c>
       <c r="AA71" s="1">
-        <v>5103322.4000000004</v>
+        <v>4752851.2</v>
       </c>
       <c r="AB71" s="1">
-        <v>75890.399999999994</v>
+        <v>25542.400000000001</v>
       </c>
       <c r="AC71" s="1">
-        <v>5404625</v>
+        <v>4855546</v>
       </c>
       <c r="AD71" s="1">
-        <v>44250</v>
+        <v>16800</v>
       </c>
       <c r="AE71" s="1">
-        <v>17700</v>
+        <v>147840</v>
       </c>
       <c r="AF71" t="s">
         <v>64</v>
       </c>
       <c r="AH71" t="s">
-        <v>986</v>
+        <v>977</v>
       </c>
       <c r="AI71" s="1">
-        <v>17700</v>
+        <v>16800</v>
       </c>
       <c r="AJ71" s="1">
         <v>30880</v>
       </c>
       <c r="AK71" s="1">
-        <v>176832</v>
+        <v>29472</v>
       </c>
       <c r="AL71" s="1">
-        <v>75890.399999999994</v>
+        <v>25542.400000000001</v>
       </c>
       <c r="AM71" s="1">
         <v>0</v>
@@ -29900,16 +29939,16 @@
         <v>0</v>
       </c>
       <c r="AO71" s="1">
-        <v>270232</v>
+        <v>242778</v>
       </c>
       <c r="AP71" s="1">
-        <v>301302.40000000002</v>
+        <v>102694.39999999999</v>
       </c>
       <c r="AQ71" s="1">
-        <v>5674857</v>
+        <v>5098324</v>
       </c>
       <c r="AR71" s="1">
-        <v>5736807</v>
+        <v>5262964</v>
       </c>
     </row>
     <row r="72" spans="1:44" x14ac:dyDescent="0.35">
@@ -29926,13 +29965,13 @@
         <v>48</v>
       </c>
       <c r="E72" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
       <c r="F72" t="s">
-        <v>664</v>
+        <v>903</v>
       </c>
       <c r="G72" t="s">
-        <v>988</v>
+        <v>979</v>
       </c>
       <c r="H72" t="s">
         <v>52</v>
@@ -29944,13 +29983,13 @@
         <v>54</v>
       </c>
       <c r="K72" t="s">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="L72" t="s">
-        <v>664</v>
+        <v>897</v>
       </c>
       <c r="M72" t="s">
-        <v>56</v>
+        <v>212</v>
       </c>
       <c r="N72" t="s">
         <v>57</v>
@@ -29965,22 +30004,22 @@
         <v>60</v>
       </c>
       <c r="R72" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S72" t="s">
         <v>61</v>
       </c>
       <c r="T72" t="s">
-        <v>989</v>
+        <v>980</v>
       </c>
       <c r="U72" s="1">
-        <v>3989.6</v>
+        <v>3226.4</v>
       </c>
       <c r="V72" s="1">
-        <v>3759.2</v>
+        <v>3162.6</v>
       </c>
       <c r="W72" s="1">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="X72" s="1">
         <v>0</v>
@@ -29992,16 +30031,16 @@
         <v>1228</v>
       </c>
       <c r="AA72" s="1">
-        <v>4899228.8</v>
+        <v>3962019.2</v>
       </c>
       <c r="AB72" s="1">
-        <v>2947.2</v>
+        <v>8350.4</v>
       </c>
       <c r="AC72" s="1">
-        <v>4970104</v>
+        <v>4069082</v>
       </c>
       <c r="AD72" s="1">
-        <v>8700</v>
+        <v>27600</v>
       </c>
       <c r="AE72" s="1">
         <v>0</v>
@@ -30010,19 +30049,19 @@
         <v>64</v>
       </c>
       <c r="AH72" t="s">
-        <v>990</v>
+        <v>981</v>
       </c>
       <c r="AI72" s="1">
-        <v>17400</v>
+        <v>13800</v>
       </c>
       <c r="AJ72" s="1">
         <v>30880</v>
       </c>
       <c r="AK72" s="1">
-        <v>19648</v>
+        <v>54032</v>
       </c>
       <c r="AL72" s="1">
-        <v>2947.2</v>
+        <v>8350.4</v>
       </c>
       <c r="AM72" s="1">
         <v>0</v>
@@ -30031,16 +30070,16 @@
         <v>0</v>
       </c>
       <c r="AO72" s="1">
-        <v>248506</v>
+        <v>203455</v>
       </c>
       <c r="AP72" s="1">
-        <v>70875.199999999997</v>
+        <v>107062.39999999999</v>
       </c>
       <c r="AQ72" s="1">
-        <v>5218610</v>
+        <v>4272537</v>
       </c>
       <c r="AR72" s="1">
-        <v>5227310</v>
+        <v>4300137</v>
       </c>
     </row>
     <row r="73" spans="1:44" x14ac:dyDescent="0.35">
@@ -30057,13 +30096,13 @@
         <v>48</v>
       </c>
       <c r="E73" t="s">
-        <v>991</v>
+        <v>982</v>
       </c>
       <c r="F73" t="s">
-        <v>664</v>
+        <v>983</v>
       </c>
       <c r="G73" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="H73" t="s">
         <v>52</v>
@@ -30075,10 +30114,10 @@
         <v>54</v>
       </c>
       <c r="K73" t="s">
-        <v>355</v>
+        <v>315</v>
       </c>
       <c r="L73" t="s">
-        <v>664</v>
+        <v>903</v>
       </c>
       <c r="M73" t="s">
         <v>212</v>
@@ -30096,22 +30135,22 @@
         <v>60</v>
       </c>
       <c r="R73" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S73" t="s">
         <v>61</v>
       </c>
       <c r="T73" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="U73" s="1">
-        <v>3822.4</v>
+        <v>4155.8</v>
       </c>
       <c r="V73" s="1">
-        <v>3799.7</v>
+        <v>4131.3</v>
       </c>
       <c r="W73" s="1">
-        <v>20.399999999999999</v>
+        <v>20.6</v>
       </c>
       <c r="X73" s="1">
         <v>0</v>
@@ -30123,54 +30162,447 @@
         <v>1228</v>
       </c>
       <c r="AA73" s="1">
-        <v>4693907.2</v>
+        <v>5103322.4000000004</v>
       </c>
       <c r="AB73" s="1">
-        <v>75153.600000000006</v>
+        <v>75890.399999999994</v>
       </c>
       <c r="AC73" s="1">
-        <v>5035205</v>
+        <v>5404625</v>
       </c>
       <c r="AD73" s="1">
-        <v>24750</v>
+        <v>44250</v>
       </c>
       <c r="AE73" s="1">
-        <v>0</v>
+        <v>17700</v>
       </c>
       <c r="AF73" t="s">
         <v>64</v>
       </c>
       <c r="AH73" t="s">
+        <v>986</v>
+      </c>
+      <c r="AI73" s="1">
+        <v>17700</v>
+      </c>
+      <c r="AJ73" s="1">
+        <v>30880</v>
+      </c>
+      <c r="AK73" s="1">
+        <v>176832</v>
+      </c>
+      <c r="AL73" s="1">
+        <v>75890.399999999994</v>
+      </c>
+      <c r="AM73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="1">
+        <v>270232</v>
+      </c>
+      <c r="AP73" s="1">
+        <v>301302.40000000002</v>
+      </c>
+      <c r="AQ73" s="1">
+        <v>5674857</v>
+      </c>
+      <c r="AR73" s="1">
+        <v>5736807</v>
+      </c>
+    </row>
+    <row r="74" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>45</v>
+      </c>
+      <c r="B74" t="s">
+        <v>46</v>
+      </c>
+      <c r="C74" t="s">
+        <v>506</v>
+      </c>
+      <c r="D74" t="s">
+        <v>48</v>
+      </c>
+      <c r="E74" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F74" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G74" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H74" t="s">
+        <v>52</v>
+      </c>
+      <c r="I74" t="s">
+        <v>53</v>
+      </c>
+      <c r="J74" t="s">
+        <v>54</v>
+      </c>
+      <c r="K74" t="s">
+        <v>321</v>
+      </c>
+      <c r="L74" t="s">
+        <v>1000</v>
+      </c>
+      <c r="M74" t="s">
+        <v>212</v>
+      </c>
+      <c r="N74" t="s">
+        <v>57</v>
+      </c>
+      <c r="O74" t="s">
+        <v>58</v>
+      </c>
+      <c r="P74" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>60</v>
+      </c>
+      <c r="R74" t="s">
+        <v>88</v>
+      </c>
+      <c r="S74" t="s">
+        <v>61</v>
+      </c>
+      <c r="T74" t="s">
+        <v>1006</v>
+      </c>
+      <c r="U74" s="1">
+        <v>4010.2</v>
+      </c>
+      <c r="V74" s="1">
+        <v>3984.5</v>
+      </c>
+      <c r="W74" s="1">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="X74" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z74" s="1">
+        <v>1228</v>
+      </c>
+      <c r="AA74" s="1">
+        <v>4924525.5999999996</v>
+      </c>
+      <c r="AB74" s="1">
+        <v>64838.400000000001</v>
+      </c>
+      <c r="AC74" s="1">
+        <v>5214176</v>
+      </c>
+      <c r="AD74" s="1">
+        <v>17100</v>
+      </c>
+      <c r="AE74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH74" t="s">
+        <v>1007</v>
+      </c>
+      <c r="AI74" s="1">
+        <v>17100</v>
+      </c>
+      <c r="AJ74" s="1">
+        <v>30880</v>
+      </c>
+      <c r="AK74" s="1">
+        <v>176832</v>
+      </c>
+      <c r="AL74" s="1">
+        <v>64838.400000000001</v>
+      </c>
+      <c r="AM74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="1">
+        <v>260709</v>
+      </c>
+      <c r="AP74" s="1">
+        <v>289650.40000000002</v>
+      </c>
+      <c r="AQ74" s="1">
+        <v>5474885</v>
+      </c>
+      <c r="AR74" s="1">
+        <v>5491985</v>
+      </c>
+    </row>
+    <row r="75" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>45</v>
+      </c>
+      <c r="B75" t="s">
+        <v>46</v>
+      </c>
+      <c r="C75" t="s">
+        <v>506</v>
+      </c>
+      <c r="D75" t="s">
+        <v>48</v>
+      </c>
+      <c r="E75" t="s">
+        <v>987</v>
+      </c>
+      <c r="F75" t="s">
+        <v>664</v>
+      </c>
+      <c r="G75" t="s">
+        <v>988</v>
+      </c>
+      <c r="H75" t="s">
+        <v>52</v>
+      </c>
+      <c r="I75" t="s">
+        <v>53</v>
+      </c>
+      <c r="J75" t="s">
+        <v>54</v>
+      </c>
+      <c r="K75" t="s">
+        <v>350</v>
+      </c>
+      <c r="L75" t="s">
+        <v>664</v>
+      </c>
+      <c r="M75" t="s">
+        <v>56</v>
+      </c>
+      <c r="N75" t="s">
+        <v>57</v>
+      </c>
+      <c r="O75" t="s">
+        <v>58</v>
+      </c>
+      <c r="P75" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>60</v>
+      </c>
+      <c r="R75" t="s">
+        <v>48</v>
+      </c>
+      <c r="S75" t="s">
+        <v>61</v>
+      </c>
+      <c r="T75" t="s">
+        <v>989</v>
+      </c>
+      <c r="U75" s="1">
+        <v>3989.6</v>
+      </c>
+      <c r="V75" s="1">
+        <v>3759.2</v>
+      </c>
+      <c r="W75" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="X75" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z75" s="1">
+        <v>1228</v>
+      </c>
+      <c r="AA75" s="1">
+        <v>4899228.8</v>
+      </c>
+      <c r="AB75" s="1">
+        <v>2947.2</v>
+      </c>
+      <c r="AC75" s="1">
+        <v>4970104</v>
+      </c>
+      <c r="AD75" s="1">
+        <v>8700</v>
+      </c>
+      <c r="AE75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH75" t="s">
+        <v>990</v>
+      </c>
+      <c r="AI75" s="1">
+        <v>17400</v>
+      </c>
+      <c r="AJ75" s="1">
+        <v>30880</v>
+      </c>
+      <c r="AK75" s="1">
+        <v>19648</v>
+      </c>
+      <c r="AL75" s="1">
+        <v>2947.2</v>
+      </c>
+      <c r="AM75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="1">
+        <v>248506</v>
+      </c>
+      <c r="AP75" s="1">
+        <v>70875.199999999997</v>
+      </c>
+      <c r="AQ75" s="1">
+        <v>5218610</v>
+      </c>
+      <c r="AR75" s="1">
+        <v>5227310</v>
+      </c>
+    </row>
+    <row r="76" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>45</v>
+      </c>
+      <c r="B76" t="s">
+        <v>46</v>
+      </c>
+      <c r="C76" t="s">
+        <v>506</v>
+      </c>
+      <c r="D76" t="s">
+        <v>48</v>
+      </c>
+      <c r="E76" t="s">
+        <v>991</v>
+      </c>
+      <c r="F76" t="s">
+        <v>664</v>
+      </c>
+      <c r="G76" t="s">
+        <v>992</v>
+      </c>
+      <c r="H76" t="s">
+        <v>52</v>
+      </c>
+      <c r="I76" t="s">
+        <v>53</v>
+      </c>
+      <c r="J76" t="s">
+        <v>54</v>
+      </c>
+      <c r="K76" t="s">
+        <v>355</v>
+      </c>
+      <c r="L76" t="s">
+        <v>664</v>
+      </c>
+      <c r="M76" t="s">
+        <v>212</v>
+      </c>
+      <c r="N76" t="s">
+        <v>57</v>
+      </c>
+      <c r="O76" t="s">
+        <v>58</v>
+      </c>
+      <c r="P76" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>60</v>
+      </c>
+      <c r="R76" t="s">
+        <v>48</v>
+      </c>
+      <c r="S76" t="s">
+        <v>61</v>
+      </c>
+      <c r="T76" t="s">
+        <v>993</v>
+      </c>
+      <c r="U76" s="1">
+        <v>3822.4</v>
+      </c>
+      <c r="V76" s="1">
+        <v>3799.7</v>
+      </c>
+      <c r="W76" s="1">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="X76" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z76" s="1">
+        <v>1228</v>
+      </c>
+      <c r="AA76" s="1">
+        <v>4693907.2</v>
+      </c>
+      <c r="AB76" s="1">
+        <v>75153.600000000006</v>
+      </c>
+      <c r="AC76" s="1">
+        <v>5035205</v>
+      </c>
+      <c r="AD76" s="1">
+        <v>24750</v>
+      </c>
+      <c r="AE76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH76" t="s">
         <v>994</v>
       </c>
-      <c r="AI73" s="1">
+      <c r="AI76" s="1">
         <v>16500</v>
       </c>
-      <c r="AJ73" s="1">
+      <c r="AJ76" s="1">
         <v>61760</v>
       </c>
-      <c r="AK73" s="1">
+      <c r="AK76" s="1">
         <v>187884</v>
       </c>
-      <c r="AL73" s="1">
+      <c r="AL76" s="1">
         <v>75153.600000000006</v>
       </c>
-      <c r="AM73" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN73" s="1">
-        <v>0</v>
-      </c>
-      <c r="AO73" s="1">
+      <c r="AM76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="1">
         <v>251761</v>
       </c>
-      <c r="AP73" s="1">
+      <c r="AP76" s="1">
         <v>341297.6</v>
       </c>
-      <c r="AQ73" s="1">
+      <c r="AQ76" s="1">
         <v>5286966</v>
       </c>
-      <c r="AR73" s="1">
+      <c r="AR76" s="1">
         <v>5311716</v>
       </c>
     </row>

--- a/Freight_data.xlsx
+++ b/Freight_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Rake Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716B265A-796D-4990-9818-1A289923334C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E6A9CB-2B64-415E-81A1-D6504D0B1286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4735" uniqueCount="1008">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4919" uniqueCount="1047">
   <si>
     <t>ZONE</t>
   </si>
@@ -3060,6 +3060,123 @@
   </si>
   <si>
     <t>SB00DC9C5B</t>
+  </si>
+  <si>
+    <t>162003211</t>
+  </si>
+  <si>
+    <t>22-08-2026</t>
+  </si>
+  <si>
+    <t>26081720059</t>
+  </si>
+  <si>
+    <t>9926082315080568</t>
+  </si>
+  <si>
+    <t>SB00DCAE8F</t>
+  </si>
+  <si>
+    <t>162003213</t>
+  </si>
+  <si>
+    <t>23-08-2026</t>
+  </si>
+  <si>
+    <t>26081818123</t>
+  </si>
+  <si>
+    <t>9926082315080584</t>
+  </si>
+  <si>
+    <t>SB00DCB5B7</t>
+  </si>
+  <si>
+    <t>162006457</t>
+  </si>
+  <si>
+    <t>26081320798</t>
+  </si>
+  <si>
+    <t>9926080915080522</t>
+  </si>
+  <si>
+    <t>SB00DCAA15</t>
+  </si>
+  <si>
+    <t>162004411</t>
+  </si>
+  <si>
+    <t>21-08-2026</t>
+  </si>
+  <si>
+    <t>26081421723</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>9926080915080516</t>
+  </si>
+  <si>
+    <t>SB00DCA6AA</t>
+  </si>
+  <si>
+    <t>162004413</t>
+  </si>
+  <si>
+    <t>26081423679</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>9926080915080544</t>
+  </si>
+  <si>
+    <t>SB00DCB353</t>
+  </si>
+  <si>
+    <t>162004415</t>
+  </si>
+  <si>
+    <t>24-08-2026</t>
+  </si>
+  <si>
+    <t>26081423697</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>9926080915080552</t>
+  </si>
+  <si>
+    <t>SB00DCB63C</t>
+  </si>
+  <si>
+    <t>162011724</t>
+  </si>
+  <si>
+    <t>26081323704</t>
+  </si>
+  <si>
+    <t>9926082315080552</t>
+  </si>
+  <si>
+    <t>SB00DCA926</t>
+  </si>
+  <si>
+    <t>162011726</t>
+  </si>
+  <si>
+    <t>26081421662</t>
+  </si>
+  <si>
+    <t>9926082315080566</t>
+  </si>
+  <si>
+    <t>SB00DCAE78</t>
   </si>
 </sst>
 </file>
@@ -20625,7 +20742,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C78B9EE1-1D80-475C-BF5D-33B3ADA7B761}">
-  <dimension ref="A1:AR76"/>
+  <dimension ref="A1:AR84"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="11.83203125" customWidth="1"/>
@@ -20789,19 +20906,19 @@
         <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="D2" t="s">
         <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>663</v>
+        <v>1008</v>
       </c>
       <c r="F2" t="s">
-        <v>664</v>
+        <v>1009</v>
       </c>
       <c r="G2" t="s">
-        <v>665</v>
+        <v>1010</v>
       </c>
       <c r="H2" t="s">
         <v>52</v>
@@ -20813,13 +20930,13 @@
         <v>54</v>
       </c>
       <c r="K2" t="s">
-        <v>666</v>
+        <v>69</v>
       </c>
       <c r="L2" t="s">
-        <v>664</v>
+        <v>1009</v>
       </c>
       <c r="M2" t="s">
-        <v>56</v>
+        <v>212</v>
       </c>
       <c r="N2" t="s">
         <v>57</v>
@@ -20840,16 +20957,16 @@
         <v>61</v>
       </c>
       <c r="T2" t="s">
-        <v>667</v>
+        <v>1011</v>
       </c>
       <c r="U2" s="1">
-        <v>3921.2</v>
+        <v>4117.3999999999996</v>
       </c>
       <c r="V2" s="1">
-        <v>3915.1</v>
+        <v>4117.2</v>
       </c>
       <c r="W2" s="1">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="X2" s="1">
         <v>0</v>
@@ -20858,16 +20975,16 @@
         <v>63</v>
       </c>
       <c r="Z2" s="1">
-        <v>1228</v>
+        <v>1054.7</v>
       </c>
       <c r="AA2" s="1">
-        <v>4815233.5999999996</v>
+        <v>4342621.78</v>
       </c>
       <c r="AB2" s="1">
-        <v>8841.6</v>
+        <v>0</v>
       </c>
       <c r="AC2" s="1">
-        <v>4973092</v>
+        <v>4495778</v>
       </c>
       <c r="AD2" s="1">
         <v>0</v>
@@ -20879,7 +20996,7 @@
         <v>64</v>
       </c>
       <c r="AH2" t="s">
-        <v>668</v>
+        <v>1012</v>
       </c>
       <c r="AI2" s="1">
         <v>0</v>
@@ -20891,25 +21008,25 @@
         <v>0</v>
       </c>
       <c r="AL2" s="1">
-        <v>8841.6</v>
+        <v>0</v>
       </c>
       <c r="AM2" s="1">
-        <v>78056</v>
+        <v>82196</v>
       </c>
       <c r="AN2" s="1">
         <v>70960</v>
       </c>
       <c r="AO2" s="1">
-        <v>248655</v>
+        <v>224789</v>
       </c>
       <c r="AP2" s="1">
-        <v>157857.60000000001</v>
+        <v>153156</v>
       </c>
       <c r="AQ2" s="1">
-        <v>5221747</v>
+        <v>4720567</v>
       </c>
       <c r="AR2" s="1">
-        <v>5221747</v>
+        <v>4720567</v>
       </c>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.35">
@@ -20920,19 +21037,19 @@
         <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="D3" t="s">
         <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>669</v>
+        <v>1013</v>
       </c>
       <c r="F3" t="s">
-        <v>664</v>
+        <v>1014</v>
       </c>
       <c r="G3" t="s">
-        <v>670</v>
+        <v>1015</v>
       </c>
       <c r="H3" t="s">
         <v>52</v>
@@ -20944,13 +21061,13 @@
         <v>54</v>
       </c>
       <c r="K3" t="s">
-        <v>671</v>
+        <v>76</v>
       </c>
       <c r="L3" t="s">
-        <v>664</v>
+        <v>1014</v>
       </c>
       <c r="M3" t="s">
-        <v>56</v>
+        <v>212</v>
       </c>
       <c r="N3" t="s">
         <v>57</v>
@@ -20971,13 +21088,13 @@
         <v>61</v>
       </c>
       <c r="T3" t="s">
-        <v>672</v>
+        <v>1016</v>
       </c>
       <c r="U3" s="1">
-        <v>3936.4</v>
+        <v>3556.4</v>
       </c>
       <c r="V3" s="1">
-        <v>3935.6</v>
+        <v>3556.2</v>
       </c>
       <c r="W3" s="1">
         <v>0</v>
@@ -20989,16 +21106,16 @@
         <v>63</v>
       </c>
       <c r="Z3" s="1">
-        <v>1228</v>
+        <v>1054.7</v>
       </c>
       <c r="AA3" s="1">
-        <v>4833899.2</v>
+        <v>3750935.08</v>
       </c>
       <c r="AB3" s="1">
         <v>0</v>
       </c>
       <c r="AC3" s="1">
-        <v>4982916</v>
+        <v>3939572</v>
       </c>
       <c r="AD3" s="1">
         <v>0</v>
@@ -21010,7 +21127,7 @@
         <v>64</v>
       </c>
       <c r="AH3" t="s">
-        <v>673</v>
+        <v>1017</v>
       </c>
       <c r="AI3" s="1">
         <v>0</v>
@@ -21025,22 +21142,22 @@
         <v>0</v>
       </c>
       <c r="AM3" s="1">
-        <v>78056</v>
+        <v>82196</v>
       </c>
       <c r="AN3" s="1">
-        <v>70960</v>
+        <v>106440</v>
       </c>
       <c r="AO3" s="1">
-        <v>249146</v>
+        <v>196979</v>
       </c>
       <c r="AP3" s="1">
-        <v>149016</v>
+        <v>188636</v>
       </c>
       <c r="AQ3" s="1">
-        <v>5232062</v>
+        <v>4136551</v>
       </c>
       <c r="AR3" s="1">
-        <v>5232062</v>
+        <v>4136551</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.35">
@@ -21057,13 +21174,13 @@
         <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="F4" t="s">
         <v>664</v>
       </c>
       <c r="G4" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="H4" t="s">
         <v>52</v>
@@ -21075,7 +21192,7 @@
         <v>54</v>
       </c>
       <c r="K4" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="L4" t="s">
         <v>664</v>
@@ -21102,16 +21219,16 @@
         <v>61</v>
       </c>
       <c r="T4" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="U4" s="1">
-        <v>3924.4</v>
+        <v>3921.2</v>
       </c>
       <c r="V4" s="1">
-        <v>3919.2</v>
+        <v>3915.1</v>
       </c>
       <c r="W4" s="1">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X4" s="1">
         <v>0</v>
@@ -21123,13 +21240,13 @@
         <v>1228</v>
       </c>
       <c r="AA4" s="1">
-        <v>4819163.2</v>
+        <v>4815233.5999999996</v>
       </c>
       <c r="AB4" s="1">
-        <v>0</v>
+        <v>8841.6</v>
       </c>
       <c r="AC4" s="1">
-        <v>5003660</v>
+        <v>4973092</v>
       </c>
       <c r="AD4" s="1">
         <v>0</v>
@@ -21141,7 +21258,7 @@
         <v>64</v>
       </c>
       <c r="AH4" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="AI4" s="1">
         <v>0</v>
@@ -21153,25 +21270,25 @@
         <v>0</v>
       </c>
       <c r="AL4" s="1">
-        <v>0</v>
+        <v>8841.6</v>
       </c>
       <c r="AM4" s="1">
         <v>78056</v>
       </c>
       <c r="AN4" s="1">
-        <v>106440</v>
+        <v>70960</v>
       </c>
       <c r="AO4" s="1">
-        <v>250183</v>
+        <v>248655</v>
       </c>
       <c r="AP4" s="1">
-        <v>184496</v>
+        <v>157857.60000000001</v>
       </c>
       <c r="AQ4" s="1">
-        <v>5253843</v>
+        <v>5221747</v>
       </c>
       <c r="AR4" s="1">
-        <v>5253843</v>
+        <v>5221747</v>
       </c>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.35">
@@ -21188,13 +21305,13 @@
         <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="F5" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="G5" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="H5" t="s">
         <v>52</v>
@@ -21206,10 +21323,10 @@
         <v>54</v>
       </c>
       <c r="K5" t="s">
-        <v>682</v>
+        <v>671</v>
       </c>
       <c r="L5" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="M5" t="s">
         <v>56</v>
@@ -21233,13 +21350,13 @@
         <v>61</v>
       </c>
       <c r="T5" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="U5" s="1">
-        <v>3718.8</v>
+        <v>3936.4</v>
       </c>
       <c r="V5" s="1">
-        <v>3714.4</v>
+        <v>3935.6</v>
       </c>
       <c r="W5" s="1">
         <v>0</v>
@@ -21254,25 +21371,25 @@
         <v>1228</v>
       </c>
       <c r="AA5" s="1">
-        <v>4566686.4000000004</v>
+        <v>4833899.2</v>
       </c>
       <c r="AB5" s="1">
         <v>0</v>
       </c>
       <c r="AC5" s="1">
-        <v>4786663</v>
+        <v>4982916</v>
       </c>
       <c r="AD5" s="1">
         <v>0</v>
       </c>
       <c r="AE5" s="1">
-        <v>93150</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="s">
         <v>64</v>
       </c>
       <c r="AH5" t="s">
-        <v>684</v>
+        <v>673</v>
       </c>
       <c r="AI5" s="1">
         <v>0</v>
@@ -21290,19 +21407,19 @@
         <v>78056</v>
       </c>
       <c r="AN5" s="1">
-        <v>141920</v>
+        <v>70960</v>
       </c>
       <c r="AO5" s="1">
-        <v>239334</v>
+        <v>249146</v>
       </c>
       <c r="AP5" s="1">
-        <v>219976</v>
+        <v>149016</v>
       </c>
       <c r="AQ5" s="1">
-        <v>5025997</v>
+        <v>5232062</v>
       </c>
       <c r="AR5" s="1">
-        <v>5119147</v>
+        <v>5232062</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.35">
@@ -21319,13 +21436,13 @@
         <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
       <c r="F6" t="s">
-        <v>686</v>
+        <v>664</v>
       </c>
       <c r="G6" t="s">
-        <v>687</v>
+        <v>675</v>
       </c>
       <c r="H6" t="s">
         <v>52</v>
@@ -21337,10 +21454,10 @@
         <v>54</v>
       </c>
       <c r="K6" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="L6" t="s">
-        <v>686</v>
+        <v>664</v>
       </c>
       <c r="M6" t="s">
         <v>56</v>
@@ -21364,13 +21481,13 @@
         <v>61</v>
       </c>
       <c r="T6" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="U6" s="1">
-        <v>3918.2</v>
+        <v>3924.4</v>
       </c>
       <c r="V6" s="1">
-        <v>3910.1</v>
+        <v>3919.2</v>
       </c>
       <c r="W6" s="1">
         <v>0</v>
@@ -21385,25 +21502,25 @@
         <v>1228</v>
       </c>
       <c r="AA6" s="1">
-        <v>4811549.5999999996</v>
+        <v>4819163.2</v>
       </c>
       <c r="AB6" s="1">
         <v>0</v>
       </c>
       <c r="AC6" s="1">
-        <v>4960566</v>
+        <v>5003660</v>
       </c>
       <c r="AD6" s="1">
         <v>0</v>
       </c>
       <c r="AE6" s="1">
-        <v>34200</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="s">
         <v>64</v>
       </c>
       <c r="AH6" t="s">
-        <v>690</v>
+        <v>678</v>
       </c>
       <c r="AI6" s="1">
         <v>0</v>
@@ -21421,19 +21538,19 @@
         <v>78056</v>
       </c>
       <c r="AN6" s="1">
-        <v>70960</v>
+        <v>106440</v>
       </c>
       <c r="AO6" s="1">
-        <v>248029</v>
+        <v>250183</v>
       </c>
       <c r="AP6" s="1">
-        <v>149016</v>
+        <v>184496</v>
       </c>
       <c r="AQ6" s="1">
-        <v>5208595</v>
+        <v>5253843</v>
       </c>
       <c r="AR6" s="1">
-        <v>5242795</v>
+        <v>5253843</v>
       </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.35">
@@ -21450,13 +21567,13 @@
         <v>48</v>
       </c>
       <c r="E7" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="F7" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="G7" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
       <c r="H7" t="s">
         <v>52</v>
@@ -21468,10 +21585,10 @@
         <v>54</v>
       </c>
       <c r="K7" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="L7" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="M7" t="s">
         <v>56</v>
@@ -21495,16 +21612,16 @@
         <v>61</v>
       </c>
       <c r="T7" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="U7" s="1">
-        <v>4078.2</v>
+        <v>3718.8</v>
       </c>
       <c r="V7" s="1">
-        <v>4078</v>
+        <v>3714.4</v>
       </c>
       <c r="W7" s="1">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X7" s="1">
         <v>0</v>
@@ -21516,25 +21633,25 @@
         <v>1228</v>
       </c>
       <c r="AA7" s="1">
-        <v>5008029.5999999996</v>
+        <v>4566686.4000000004</v>
       </c>
       <c r="AB7" s="1">
-        <v>5157.6000000000004</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="1">
-        <v>5162204</v>
+        <v>4786663</v>
       </c>
       <c r="AD7" s="1">
         <v>0</v>
       </c>
       <c r="AE7" s="1">
-        <v>62835</v>
+        <v>93150</v>
       </c>
       <c r="AF7" t="s">
         <v>64</v>
       </c>
       <c r="AH7" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="AI7" s="1">
         <v>0</v>
@@ -21546,25 +21663,25 @@
         <v>0</v>
       </c>
       <c r="AL7" s="1">
-        <v>5157.6000000000004</v>
+        <v>0</v>
       </c>
       <c r="AM7" s="1">
         <v>78056</v>
       </c>
       <c r="AN7" s="1">
-        <v>70960</v>
+        <v>141920</v>
       </c>
       <c r="AO7" s="1">
-        <v>258111</v>
+        <v>239334</v>
       </c>
       <c r="AP7" s="1">
-        <v>154173.6</v>
+        <v>219976</v>
       </c>
       <c r="AQ7" s="1">
-        <v>5420315</v>
+        <v>5025997</v>
       </c>
       <c r="AR7" s="1">
-        <v>5483150</v>
+        <v>5119147</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.35">
@@ -21581,13 +21698,13 @@
         <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="F8" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="G8" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="H8" t="s">
         <v>52</v>
@@ -21599,10 +21716,10 @@
         <v>54</v>
       </c>
       <c r="K8" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="L8" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="M8" t="s">
         <v>56</v>
@@ -21626,13 +21743,13 @@
         <v>61</v>
       </c>
       <c r="T8" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="U8" s="1">
-        <v>3990.4</v>
+        <v>3918.2</v>
       </c>
       <c r="V8" s="1">
-        <v>3982.3</v>
+        <v>3910.1</v>
       </c>
       <c r="W8" s="1">
         <v>0</v>
@@ -21647,25 +21764,25 @@
         <v>1228</v>
       </c>
       <c r="AA8" s="1">
-        <v>4900211.2</v>
+        <v>4811549.5999999996</v>
       </c>
       <c r="AB8" s="1">
         <v>0</v>
       </c>
       <c r="AC8" s="1">
-        <v>5084708</v>
+        <v>4960566</v>
       </c>
       <c r="AD8" s="1">
         <v>0</v>
       </c>
       <c r="AE8" s="1">
-        <v>34800</v>
+        <v>34200</v>
       </c>
       <c r="AF8" t="s">
         <v>64</v>
       </c>
       <c r="AH8" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="AI8" s="1">
         <v>0</v>
@@ -21683,19 +21800,19 @@
         <v>78056</v>
       </c>
       <c r="AN8" s="1">
-        <v>106440</v>
+        <v>70960</v>
       </c>
       <c r="AO8" s="1">
-        <v>254236</v>
+        <v>248029</v>
       </c>
       <c r="AP8" s="1">
-        <v>184496</v>
+        <v>149016</v>
       </c>
       <c r="AQ8" s="1">
-        <v>5338944</v>
+        <v>5208595</v>
       </c>
       <c r="AR8" s="1">
-        <v>5373744</v>
+        <v>5242795</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.35">
@@ -21712,13 +21829,13 @@
         <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
       <c r="F9" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="G9" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="H9" t="s">
         <v>52</v>
@@ -21730,10 +21847,10 @@
         <v>54</v>
       </c>
       <c r="K9" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="L9" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="M9" t="s">
         <v>56</v>
@@ -21757,16 +21874,16 @@
         <v>61</v>
       </c>
       <c r="T9" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="U9" s="1">
-        <v>3998.6</v>
+        <v>4078.2</v>
       </c>
       <c r="V9" s="1">
-        <v>3995.9</v>
+        <v>4078</v>
       </c>
       <c r="W9" s="1">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="X9" s="1">
         <v>0</v>
@@ -21778,25 +21895,25 @@
         <v>1228</v>
       </c>
       <c r="AA9" s="1">
-        <v>4910280.8</v>
+        <v>5008029.5999999996</v>
       </c>
       <c r="AB9" s="1">
-        <v>6631.2</v>
+        <v>5157.6000000000004</v>
       </c>
       <c r="AC9" s="1">
-        <v>5101408</v>
+        <v>5162204</v>
       </c>
       <c r="AD9" s="1">
         <v>0</v>
       </c>
       <c r="AE9" s="1">
-        <v>100050</v>
+        <v>62835</v>
       </c>
       <c r="AF9" t="s">
         <v>64</v>
       </c>
       <c r="AH9" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
       <c r="AI9" s="1">
         <v>0</v>
@@ -21808,25 +21925,25 @@
         <v>0</v>
       </c>
       <c r="AL9" s="1">
-        <v>6631.2</v>
+        <v>5157.6000000000004</v>
       </c>
       <c r="AM9" s="1">
         <v>78056</v>
       </c>
       <c r="AN9" s="1">
-        <v>106440</v>
+        <v>70960</v>
       </c>
       <c r="AO9" s="1">
-        <v>255071</v>
+        <v>258111</v>
       </c>
       <c r="AP9" s="1">
-        <v>191127.2</v>
+        <v>154173.6</v>
       </c>
       <c r="AQ9" s="1">
-        <v>5356479</v>
+        <v>5420315</v>
       </c>
       <c r="AR9" s="1">
-        <v>5456529</v>
+        <v>5483150</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.35">
@@ -21843,13 +21960,13 @@
         <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="F10" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="G10" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="H10" t="s">
         <v>52</v>
@@ -21861,10 +21978,10 @@
         <v>54</v>
       </c>
       <c r="K10" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="L10" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="M10" t="s">
         <v>56</v>
@@ -21888,13 +22005,13 @@
         <v>61</v>
       </c>
       <c r="T10" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="U10" s="1">
-        <v>3862</v>
+        <v>3990.4</v>
       </c>
       <c r="V10" s="1">
-        <v>3855.5</v>
+        <v>3982.3</v>
       </c>
       <c r="W10" s="1">
         <v>0</v>
@@ -21909,25 +22026,25 @@
         <v>1228</v>
       </c>
       <c r="AA10" s="1">
-        <v>4742536</v>
+        <v>4900211.2</v>
       </c>
       <c r="AB10" s="1">
         <v>0</v>
       </c>
       <c r="AC10" s="1">
-        <v>4927032</v>
+        <v>5084708</v>
       </c>
       <c r="AD10" s="1">
         <v>0</v>
       </c>
       <c r="AE10" s="1">
-        <v>116340</v>
+        <v>34800</v>
       </c>
       <c r="AF10" t="s">
         <v>64</v>
       </c>
       <c r="AH10" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
       <c r="AI10" s="1">
         <v>0</v>
@@ -21948,16 +22065,16 @@
         <v>106440</v>
       </c>
       <c r="AO10" s="1">
-        <v>246352</v>
+        <v>254236</v>
       </c>
       <c r="AP10" s="1">
         <v>184496</v>
       </c>
       <c r="AQ10" s="1">
-        <v>5173384</v>
+        <v>5338944</v>
       </c>
       <c r="AR10" s="1">
-        <v>5289724</v>
+        <v>5373744</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.35">
@@ -21974,13 +22091,13 @@
         <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
       <c r="F11" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="G11" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="H11" t="s">
         <v>52</v>
@@ -21992,10 +22109,10 @@
         <v>54</v>
       </c>
       <c r="K11" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="L11" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="M11" t="s">
         <v>56</v>
@@ -22019,16 +22136,16 @@
         <v>61</v>
       </c>
       <c r="T11" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="U11" s="1">
-        <v>3912.8</v>
+        <v>3998.6</v>
       </c>
       <c r="V11" s="1">
-        <v>3903.1</v>
+        <v>3995.9</v>
       </c>
       <c r="W11" s="1">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="X11" s="1">
         <v>0</v>
@@ -22040,25 +22157,25 @@
         <v>1228</v>
       </c>
       <c r="AA11" s="1">
-        <v>4804918.4000000004</v>
+        <v>4910280.8</v>
       </c>
       <c r="AB11" s="1">
-        <v>1964.8</v>
+        <v>6631.2</v>
       </c>
       <c r="AC11" s="1">
-        <v>4955900</v>
+        <v>5101408</v>
       </c>
       <c r="AD11" s="1">
         <v>0</v>
       </c>
       <c r="AE11" s="1">
-        <v>107730</v>
+        <v>100050</v>
       </c>
       <c r="AF11" t="s">
         <v>64</v>
       </c>
       <c r="AH11" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="AI11" s="1">
         <v>0</v>
@@ -22070,25 +22187,25 @@
         <v>0</v>
       </c>
       <c r="AL11" s="1">
-        <v>1964.8</v>
+        <v>6631.2</v>
       </c>
       <c r="AM11" s="1">
         <v>78056</v>
       </c>
       <c r="AN11" s="1">
-        <v>70960</v>
+        <v>106440</v>
       </c>
       <c r="AO11" s="1">
-        <v>247795</v>
+        <v>255071</v>
       </c>
       <c r="AP11" s="1">
-        <v>150980.79999999999</v>
+        <v>191127.2</v>
       </c>
       <c r="AQ11" s="1">
-        <v>5203695</v>
+        <v>5356479</v>
       </c>
       <c r="AR11" s="1">
-        <v>5311425</v>
+        <v>5456529</v>
       </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.35">
@@ -22105,13 +22222,13 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="F12" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="G12" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="H12" t="s">
         <v>52</v>
@@ -22123,10 +22240,10 @@
         <v>54</v>
       </c>
       <c r="K12" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="L12" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="M12" t="s">
         <v>56</v>
@@ -22150,16 +22267,16 @@
         <v>61</v>
       </c>
       <c r="T12" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="U12" s="1">
-        <v>3787.8</v>
+        <v>3862</v>
       </c>
       <c r="V12" s="1">
-        <v>3785.3</v>
+        <v>3855.5</v>
       </c>
       <c r="W12" s="1">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X12" s="1">
         <v>0</v>
@@ -22171,25 +22288,25 @@
         <v>1228</v>
       </c>
       <c r="AA12" s="1">
-        <v>4651418.4000000004</v>
+        <v>4742536</v>
       </c>
       <c r="AB12" s="1">
-        <v>5894.4</v>
+        <v>0</v>
       </c>
       <c r="AC12" s="1">
-        <v>4948249</v>
+        <v>4927032</v>
       </c>
       <c r="AD12" s="1">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="1">
-        <v>40500</v>
+        <v>116340</v>
       </c>
       <c r="AF12" t="s">
         <v>64</v>
       </c>
       <c r="AH12" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="AI12" s="1">
         <v>0</v>
@@ -22201,25 +22318,25 @@
         <v>0</v>
       </c>
       <c r="AL12" s="1">
-        <v>5894.4</v>
+        <v>0</v>
       </c>
       <c r="AM12" s="1">
         <v>78056</v>
       </c>
       <c r="AN12" s="1">
-        <v>212880</v>
+        <v>106440</v>
       </c>
       <c r="AO12" s="1">
-        <v>247413</v>
+        <v>246352</v>
       </c>
       <c r="AP12" s="1">
-        <v>296830.40000000002</v>
+        <v>184496</v>
       </c>
       <c r="AQ12" s="1">
-        <v>5195662</v>
+        <v>5173384</v>
       </c>
       <c r="AR12" s="1">
-        <v>5252362</v>
+        <v>5289724</v>
       </c>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.35">
@@ -22236,13 +22353,13 @@
         <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="F13" t="s">
-        <v>725</v>
+        <v>708</v>
       </c>
       <c r="G13" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="H13" t="s">
         <v>52</v>
@@ -22254,10 +22371,10 @@
         <v>54</v>
       </c>
       <c r="K13" t="s">
-        <v>727</v>
+        <v>715</v>
       </c>
       <c r="L13" t="s">
-        <v>725</v>
+        <v>708</v>
       </c>
       <c r="M13" t="s">
         <v>56</v>
@@ -22281,16 +22398,16 @@
         <v>61</v>
       </c>
       <c r="T13" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="U13" s="1">
-        <v>3932</v>
+        <v>3912.8</v>
       </c>
       <c r="V13" s="1">
-        <v>3929.5</v>
+        <v>3903.1</v>
       </c>
       <c r="W13" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="X13" s="1">
         <v>0</v>
@@ -22302,25 +22419,25 @@
         <v>1228</v>
       </c>
       <c r="AA13" s="1">
-        <v>4828496</v>
+        <v>4804918.4000000004</v>
       </c>
       <c r="AB13" s="1">
-        <v>0</v>
+        <v>1964.8</v>
       </c>
       <c r="AC13" s="1">
-        <v>5012992</v>
+        <v>4955900</v>
       </c>
       <c r="AD13" s="1">
         <v>0</v>
       </c>
       <c r="AE13" s="1">
-        <v>8550</v>
+        <v>107730</v>
       </c>
       <c r="AF13" t="s">
         <v>64</v>
       </c>
       <c r="AH13" t="s">
-        <v>729</v>
+        <v>717</v>
       </c>
       <c r="AI13" s="1">
         <v>0</v>
@@ -22332,25 +22449,25 @@
         <v>0</v>
       </c>
       <c r="AL13" s="1">
-        <v>0</v>
+        <v>1964.8</v>
       </c>
       <c r="AM13" s="1">
         <v>78056</v>
       </c>
       <c r="AN13" s="1">
-        <v>106440</v>
+        <v>70960</v>
       </c>
       <c r="AO13" s="1">
-        <v>250650</v>
+        <v>247795</v>
       </c>
       <c r="AP13" s="1">
-        <v>184496</v>
+        <v>150980.79999999999</v>
       </c>
       <c r="AQ13" s="1">
-        <v>5263642</v>
+        <v>5203695</v>
       </c>
       <c r="AR13" s="1">
-        <v>5272192</v>
+        <v>5311425</v>
       </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.35">
@@ -22367,13 +22484,13 @@
         <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="F14" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="G14" t="s">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="H14" t="s">
         <v>52</v>
@@ -22385,10 +22502,10 @@
         <v>54</v>
       </c>
       <c r="K14" t="s">
-        <v>733</v>
+        <v>721</v>
       </c>
       <c r="L14" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="M14" t="s">
         <v>56</v>
@@ -22412,16 +22529,16 @@
         <v>61</v>
       </c>
       <c r="T14" t="s">
-        <v>734</v>
+        <v>722</v>
       </c>
       <c r="U14" s="1">
-        <v>3996.8</v>
+        <v>3787.8</v>
       </c>
       <c r="V14" s="1">
-        <v>3992.3</v>
+        <v>3785.3</v>
       </c>
       <c r="W14" s="1">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X14" s="1">
         <v>0</v>
@@ -22433,25 +22550,25 @@
         <v>1228</v>
       </c>
       <c r="AA14" s="1">
-        <v>4908070.4000000004</v>
+        <v>4651418.4000000004</v>
       </c>
       <c r="AB14" s="1">
-        <v>0</v>
+        <v>5894.4</v>
       </c>
       <c r="AC14" s="1">
-        <v>5340927</v>
+        <v>4948249</v>
       </c>
       <c r="AD14" s="1">
-        <v>43500</v>
+        <v>16200</v>
       </c>
       <c r="AE14" s="1">
-        <v>0</v>
+        <v>40500</v>
       </c>
       <c r="AF14" t="s">
         <v>64</v>
       </c>
       <c r="AH14" t="s">
-        <v>735</v>
+        <v>723</v>
       </c>
       <c r="AI14" s="1">
         <v>0</v>
@@ -22463,25 +22580,25 @@
         <v>0</v>
       </c>
       <c r="AL14" s="1">
-        <v>0</v>
+        <v>5894.4</v>
       </c>
       <c r="AM14" s="1">
         <v>78056</v>
       </c>
       <c r="AN14" s="1">
-        <v>354800</v>
+        <v>212880</v>
       </c>
       <c r="AO14" s="1">
-        <v>267047</v>
+        <v>247413</v>
       </c>
       <c r="AP14" s="1">
-        <v>432856</v>
+        <v>296830.40000000002</v>
       </c>
       <c r="AQ14" s="1">
-        <v>5607974</v>
+        <v>5195662</v>
       </c>
       <c r="AR14" s="1">
-        <v>5651474</v>
+        <v>5252362</v>
       </c>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.35">
@@ -22498,13 +22615,13 @@
         <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="F15" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="G15" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
       <c r="H15" t="s">
         <v>52</v>
@@ -22516,10 +22633,10 @@
         <v>54</v>
       </c>
       <c r="K15" t="s">
-        <v>738</v>
+        <v>727</v>
       </c>
       <c r="L15" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="M15" t="s">
         <v>56</v>
@@ -22543,13 +22660,13 @@
         <v>61</v>
       </c>
       <c r="T15" t="s">
-        <v>739</v>
+        <v>728</v>
       </c>
       <c r="U15" s="1">
-        <v>3917.6</v>
+        <v>3932</v>
       </c>
       <c r="V15" s="1">
-        <v>3909.2</v>
+        <v>3929.5</v>
       </c>
       <c r="W15" s="1">
         <v>0</v>
@@ -22564,25 +22681,25 @@
         <v>1228</v>
       </c>
       <c r="AA15" s="1">
-        <v>4810812.8</v>
+        <v>4828496</v>
       </c>
       <c r="AB15" s="1">
         <v>0</v>
       </c>
       <c r="AC15" s="1">
-        <v>4959829</v>
+        <v>5012992</v>
       </c>
       <c r="AD15" s="1">
         <v>0</v>
       </c>
       <c r="AE15" s="1">
-        <v>0</v>
+        <v>8550</v>
       </c>
       <c r="AF15" t="s">
         <v>64</v>
       </c>
       <c r="AH15" t="s">
-        <v>740</v>
+        <v>729</v>
       </c>
       <c r="AI15" s="1">
         <v>0</v>
@@ -22600,19 +22717,19 @@
         <v>78056</v>
       </c>
       <c r="AN15" s="1">
-        <v>70960</v>
+        <v>106440</v>
       </c>
       <c r="AO15" s="1">
-        <v>247992</v>
+        <v>250650</v>
       </c>
       <c r="AP15" s="1">
-        <v>149016</v>
+        <v>184496</v>
       </c>
       <c r="AQ15" s="1">
-        <v>5207821</v>
+        <v>5263642</v>
       </c>
       <c r="AR15" s="1">
-        <v>5207821</v>
+        <v>5272192</v>
       </c>
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.35">
@@ -22629,13 +22746,13 @@
         <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>741</v>
+        <v>730</v>
       </c>
       <c r="F16" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="G16" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="H16" t="s">
         <v>52</v>
@@ -22647,10 +22764,10 @@
         <v>54</v>
       </c>
       <c r="K16" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="L16" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="M16" t="s">
         <v>56</v>
@@ -22674,16 +22791,16 @@
         <v>61</v>
       </c>
       <c r="T16" t="s">
-        <v>745</v>
+        <v>734</v>
       </c>
       <c r="U16" s="1">
-        <v>3783.8</v>
+        <v>3996.8</v>
       </c>
       <c r="V16" s="1">
-        <v>3777.3</v>
+        <v>3992.3</v>
       </c>
       <c r="W16" s="1">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X16" s="1">
         <v>0</v>
@@ -22695,16 +22812,16 @@
         <v>1228</v>
       </c>
       <c r="AA16" s="1">
-        <v>4646506.4000000004</v>
+        <v>4908070.4000000004</v>
       </c>
       <c r="AB16" s="1">
-        <v>4420.8</v>
+        <v>0</v>
       </c>
       <c r="AC16" s="1">
-        <v>4835424</v>
+        <v>5340927</v>
       </c>
       <c r="AD16" s="1">
-        <v>0</v>
+        <v>43500</v>
       </c>
       <c r="AE16" s="1">
         <v>0</v>
@@ -22713,7 +22830,7 @@
         <v>64</v>
       </c>
       <c r="AH16" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="AI16" s="1">
         <v>0</v>
@@ -22725,25 +22842,25 @@
         <v>0</v>
       </c>
       <c r="AL16" s="1">
-        <v>4420.8</v>
+        <v>0</v>
       </c>
       <c r="AM16" s="1">
         <v>78056</v>
       </c>
       <c r="AN16" s="1">
-        <v>106440</v>
+        <v>354800</v>
       </c>
       <c r="AO16" s="1">
-        <v>241772</v>
+        <v>267047</v>
       </c>
       <c r="AP16" s="1">
-        <v>188916.8</v>
+        <v>432856</v>
       </c>
       <c r="AQ16" s="1">
-        <v>5077196</v>
+        <v>5607974</v>
       </c>
       <c r="AR16" s="1">
-        <v>5077196</v>
+        <v>5651474</v>
       </c>
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.35">
@@ -22760,13 +22877,13 @@
         <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="F17" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
       <c r="G17" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
       <c r="H17" t="s">
         <v>52</v>
@@ -22778,10 +22895,10 @@
         <v>54</v>
       </c>
       <c r="K17" t="s">
-        <v>750</v>
+        <v>738</v>
       </c>
       <c r="L17" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="M17" t="s">
         <v>56</v>
@@ -22805,13 +22922,13 @@
         <v>61</v>
       </c>
       <c r="T17" t="s">
-        <v>751</v>
+        <v>739</v>
       </c>
       <c r="U17" s="1">
-        <v>4043.2</v>
+        <v>3917.6</v>
       </c>
       <c r="V17" s="1">
-        <v>4021.7</v>
+        <v>3909.2</v>
       </c>
       <c r="W17" s="1">
         <v>0</v>
@@ -22826,13 +22943,13 @@
         <v>1228</v>
       </c>
       <c r="AA17" s="1">
-        <v>4965049.5999999996</v>
+        <v>4810812.8</v>
       </c>
       <c r="AB17" s="1">
         <v>0</v>
       </c>
       <c r="AC17" s="1">
-        <v>5114066</v>
+        <v>4959829</v>
       </c>
       <c r="AD17" s="1">
         <v>0</v>
@@ -22844,7 +22961,7 @@
         <v>64</v>
       </c>
       <c r="AH17" t="s">
-        <v>752</v>
+        <v>740</v>
       </c>
       <c r="AI17" s="1">
         <v>0</v>
@@ -22865,16 +22982,16 @@
         <v>70960</v>
       </c>
       <c r="AO17" s="1">
-        <v>255704</v>
+        <v>247992</v>
       </c>
       <c r="AP17" s="1">
         <v>149016</v>
       </c>
       <c r="AQ17" s="1">
-        <v>5369770</v>
+        <v>5207821</v>
       </c>
       <c r="AR17" s="1">
-        <v>5369770</v>
+        <v>5207821</v>
       </c>
     </row>
     <row r="18" spans="1:44" x14ac:dyDescent="0.35">
@@ -22891,13 +23008,13 @@
         <v>48</v>
       </c>
       <c r="E18" t="s">
-        <v>753</v>
+        <v>741</v>
       </c>
       <c r="F18" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="G18" t="s">
-        <v>754</v>
+        <v>743</v>
       </c>
       <c r="H18" t="s">
         <v>52</v>
@@ -22909,10 +23026,10 @@
         <v>54</v>
       </c>
       <c r="K18" t="s">
-        <v>755</v>
+        <v>744</v>
       </c>
       <c r="L18" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="M18" t="s">
         <v>56</v>
@@ -22936,16 +23053,16 @@
         <v>61</v>
       </c>
       <c r="T18" t="s">
-        <v>756</v>
+        <v>745</v>
       </c>
       <c r="U18" s="1">
-        <v>4113</v>
+        <v>3783.8</v>
       </c>
       <c r="V18" s="1">
-        <v>4096.6000000000004</v>
+        <v>3777.3</v>
       </c>
       <c r="W18" s="1">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X18" s="1">
         <v>0</v>
@@ -22957,16 +23074,16 @@
         <v>1228</v>
       </c>
       <c r="AA18" s="1">
-        <v>5050764</v>
+        <v>4646506.4000000004</v>
       </c>
       <c r="AB18" s="1">
-        <v>0</v>
+        <v>4420.8</v>
       </c>
       <c r="AC18" s="1">
-        <v>5377180</v>
+        <v>4835424</v>
       </c>
       <c r="AD18" s="1">
-        <v>17700</v>
+        <v>0</v>
       </c>
       <c r="AE18" s="1">
         <v>0</v>
@@ -22975,7 +23092,7 @@
         <v>64</v>
       </c>
       <c r="AH18" t="s">
-        <v>757</v>
+        <v>746</v>
       </c>
       <c r="AI18" s="1">
         <v>0</v>
@@ -22987,25 +23104,25 @@
         <v>0</v>
       </c>
       <c r="AL18" s="1">
-        <v>0</v>
+        <v>4420.8</v>
       </c>
       <c r="AM18" s="1">
         <v>78056</v>
       </c>
       <c r="AN18" s="1">
-        <v>248360</v>
+        <v>106440</v>
       </c>
       <c r="AO18" s="1">
-        <v>268859</v>
+        <v>241772</v>
       </c>
       <c r="AP18" s="1">
-        <v>326416</v>
+        <v>188916.8</v>
       </c>
       <c r="AQ18" s="1">
-        <v>5646039</v>
+        <v>5077196</v>
       </c>
       <c r="AR18" s="1">
-        <v>5663739</v>
+        <v>5077196</v>
       </c>
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.35">
@@ -23022,13 +23139,13 @@
         <v>48</v>
       </c>
       <c r="E19" t="s">
-        <v>758</v>
+        <v>747</v>
       </c>
       <c r="F19" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="G19" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="H19" t="s">
         <v>52</v>
@@ -23040,10 +23157,10 @@
         <v>54</v>
       </c>
       <c r="K19" t="s">
-        <v>761</v>
+        <v>750</v>
       </c>
       <c r="L19" t="s">
-        <v>759</v>
+        <v>742</v>
       </c>
       <c r="M19" t="s">
         <v>56</v>
@@ -23067,16 +23184,16 @@
         <v>61</v>
       </c>
       <c r="T19" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
       <c r="U19" s="1">
-        <v>3591.4</v>
+        <v>4043.2</v>
       </c>
       <c r="V19" s="1">
-        <v>3590</v>
+        <v>4021.7</v>
       </c>
       <c r="W19" s="1">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X19" s="1">
         <v>0</v>
@@ -23088,25 +23205,25 @@
         <v>1228</v>
       </c>
       <c r="AA19" s="1">
-        <v>4410239.2</v>
+        <v>4965049.5999999996</v>
       </c>
       <c r="AB19" s="1">
-        <v>4420.8</v>
+        <v>0</v>
       </c>
       <c r="AC19" s="1">
-        <v>4599156</v>
+        <v>5114066</v>
       </c>
       <c r="AD19" s="1">
         <v>0</v>
       </c>
       <c r="AE19" s="1">
-        <v>72540</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="s">
         <v>64</v>
       </c>
       <c r="AH19" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
       <c r="AI19" s="1">
         <v>0</v>
@@ -23118,25 +23235,25 @@
         <v>0</v>
       </c>
       <c r="AL19" s="1">
-        <v>4420.8</v>
+        <v>0</v>
       </c>
       <c r="AM19" s="1">
         <v>78056</v>
       </c>
       <c r="AN19" s="1">
-        <v>106440</v>
+        <v>70960</v>
       </c>
       <c r="AO19" s="1">
-        <v>229958</v>
+        <v>255704</v>
       </c>
       <c r="AP19" s="1">
-        <v>188916.8</v>
+        <v>149016</v>
       </c>
       <c r="AQ19" s="1">
-        <v>4829114</v>
+        <v>5369770</v>
       </c>
       <c r="AR19" s="1">
-        <v>4901654</v>
+        <v>5369770</v>
       </c>
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.35">
@@ -23153,13 +23270,13 @@
         <v>48</v>
       </c>
       <c r="E20" t="s">
-        <v>764</v>
+        <v>753</v>
       </c>
       <c r="F20" t="s">
-        <v>765</v>
+        <v>748</v>
       </c>
       <c r="G20" t="s">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="H20" t="s">
         <v>52</v>
@@ -23171,10 +23288,10 @@
         <v>54</v>
       </c>
       <c r="K20" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="L20" t="s">
-        <v>765</v>
+        <v>748</v>
       </c>
       <c r="M20" t="s">
         <v>56</v>
@@ -23198,13 +23315,13 @@
         <v>61</v>
       </c>
       <c r="T20" t="s">
-        <v>768</v>
+        <v>756</v>
       </c>
       <c r="U20" s="1">
-        <v>3981.8</v>
+        <v>4113</v>
       </c>
       <c r="V20" s="1">
-        <v>3972.7</v>
+        <v>4096.6000000000004</v>
       </c>
       <c r="W20" s="1">
         <v>0</v>
@@ -23219,25 +23336,25 @@
         <v>1228</v>
       </c>
       <c r="AA20" s="1">
-        <v>4889650.4000000004</v>
+        <v>5050764</v>
       </c>
       <c r="AB20" s="1">
         <v>0</v>
       </c>
       <c r="AC20" s="1">
-        <v>5074147</v>
+        <v>5377180</v>
       </c>
       <c r="AD20" s="1">
-        <v>0</v>
+        <v>17700</v>
       </c>
       <c r="AE20" s="1">
-        <v>26100</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="s">
         <v>64</v>
       </c>
       <c r="AH20" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="AI20" s="1">
         <v>0</v>
@@ -23255,19 +23372,19 @@
         <v>78056</v>
       </c>
       <c r="AN20" s="1">
-        <v>106440</v>
+        <v>248360</v>
       </c>
       <c r="AO20" s="1">
-        <v>253708</v>
+        <v>268859</v>
       </c>
       <c r="AP20" s="1">
-        <v>184496</v>
+        <v>326416</v>
       </c>
       <c r="AQ20" s="1">
-        <v>5327855</v>
+        <v>5646039</v>
       </c>
       <c r="AR20" s="1">
-        <v>5353955</v>
+        <v>5663739</v>
       </c>
     </row>
     <row r="21" spans="1:44" x14ac:dyDescent="0.35">
@@ -23284,13 +23401,13 @@
         <v>48</v>
       </c>
       <c r="E21" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="F21" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="G21" t="s">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="H21" t="s">
         <v>52</v>
@@ -23302,10 +23419,10 @@
         <v>54</v>
       </c>
       <c r="K21" t="s">
-        <v>773</v>
+        <v>761</v>
       </c>
       <c r="L21" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="M21" t="s">
         <v>56</v>
@@ -23329,16 +23446,16 @@
         <v>61</v>
       </c>
       <c r="T21" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="U21" s="1">
-        <v>3922.2</v>
+        <v>3591.4</v>
       </c>
       <c r="V21" s="1">
-        <v>3915.7</v>
+        <v>3590</v>
       </c>
       <c r="W21" s="1">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X21" s="1">
         <v>0</v>
@@ -23350,25 +23467,25 @@
         <v>1228</v>
       </c>
       <c r="AA21" s="1">
-        <v>4816461.5999999996</v>
+        <v>4410239.2</v>
       </c>
       <c r="AB21" s="1">
-        <v>0</v>
+        <v>4420.8</v>
       </c>
       <c r="AC21" s="1">
-        <v>5036438</v>
+        <v>4599156</v>
       </c>
       <c r="AD21" s="1">
-        <v>8550</v>
+        <v>0</v>
       </c>
       <c r="AE21" s="1">
-        <v>107730</v>
+        <v>72540</v>
       </c>
       <c r="AF21" t="s">
         <v>64</v>
       </c>
       <c r="AH21" t="s">
-        <v>775</v>
+        <v>763</v>
       </c>
       <c r="AI21" s="1">
         <v>0</v>
@@ -23380,25 +23497,25 @@
         <v>0</v>
       </c>
       <c r="AL21" s="1">
-        <v>0</v>
+        <v>4420.8</v>
       </c>
       <c r="AM21" s="1">
         <v>78056</v>
       </c>
       <c r="AN21" s="1">
-        <v>141920</v>
+        <v>106440</v>
       </c>
       <c r="AO21" s="1">
-        <v>251822</v>
+        <v>229958</v>
       </c>
       <c r="AP21" s="1">
-        <v>219976</v>
+        <v>188916.8</v>
       </c>
       <c r="AQ21" s="1">
-        <v>5288260</v>
+        <v>4829114</v>
       </c>
       <c r="AR21" s="1">
-        <v>5404540</v>
+        <v>4901654</v>
       </c>
     </row>
     <row r="22" spans="1:44" x14ac:dyDescent="0.35">
@@ -23415,13 +23532,13 @@
         <v>48</v>
       </c>
       <c r="E22" t="s">
-        <v>995</v>
+        <v>764</v>
       </c>
       <c r="F22" t="s">
-        <v>909</v>
+        <v>765</v>
       </c>
       <c r="G22" t="s">
-        <v>996</v>
+        <v>766</v>
       </c>
       <c r="H22" t="s">
         <v>52</v>
@@ -23433,10 +23550,10 @@
         <v>54</v>
       </c>
       <c r="K22" t="s">
-        <v>869</v>
+        <v>767</v>
       </c>
       <c r="L22" t="s">
-        <v>909</v>
+        <v>765</v>
       </c>
       <c r="M22" t="s">
         <v>56</v>
@@ -23460,16 +23577,16 @@
         <v>61</v>
       </c>
       <c r="T22" t="s">
-        <v>997</v>
+        <v>768</v>
       </c>
       <c r="U22" s="1">
-        <v>3703.4</v>
+        <v>3981.8</v>
       </c>
       <c r="V22" s="1">
-        <v>3701.6</v>
+        <v>3972.7</v>
       </c>
       <c r="W22" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X22" s="1">
         <v>0</v>
@@ -23481,55 +23598,55 @@
         <v>1228</v>
       </c>
       <c r="AA22" s="1">
-        <v>4547775.2</v>
+        <v>4889650.4000000004</v>
       </c>
       <c r="AB22" s="1">
-        <v>11052</v>
+        <v>0</v>
       </c>
       <c r="AC22" s="1">
-        <v>4868766</v>
+        <v>5074147</v>
       </c>
       <c r="AD22" s="1">
-        <v>7950</v>
+        <v>0</v>
       </c>
       <c r="AE22" s="1">
-        <v>23850</v>
+        <v>26100</v>
       </c>
       <c r="AF22" t="s">
         <v>64</v>
       </c>
       <c r="AH22" t="s">
-        <v>998</v>
+        <v>769</v>
       </c>
       <c r="AI22" s="1">
-        <v>7950</v>
+        <v>0</v>
       </c>
       <c r="AJ22" s="1">
-        <v>35480</v>
+        <v>0</v>
       </c>
       <c r="AK22" s="1">
-        <v>11052</v>
+        <v>0</v>
       </c>
       <c r="AL22" s="1">
-        <v>11052</v>
+        <v>0</v>
       </c>
       <c r="AM22" s="1">
         <v>78056</v>
       </c>
       <c r="AN22" s="1">
-        <v>177400</v>
+        <v>106440</v>
       </c>
       <c r="AO22" s="1">
-        <v>243439</v>
+        <v>253708</v>
       </c>
       <c r="AP22" s="1">
-        <v>320990</v>
+        <v>184496</v>
       </c>
       <c r="AQ22" s="1">
-        <v>5112205</v>
+        <v>5327855</v>
       </c>
       <c r="AR22" s="1">
-        <v>5144005</v>
+        <v>5353955</v>
       </c>
     </row>
     <row r="23" spans="1:44" x14ac:dyDescent="0.35">
@@ -23546,13 +23663,13 @@
         <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>999</v>
+        <v>770</v>
       </c>
       <c r="F23" t="s">
-        <v>1000</v>
+        <v>771</v>
       </c>
       <c r="G23" t="s">
-        <v>1001</v>
+        <v>772</v>
       </c>
       <c r="H23" t="s">
         <v>52</v>
@@ -23564,10 +23681,10 @@
         <v>54</v>
       </c>
       <c r="K23" t="s">
-        <v>874</v>
+        <v>773</v>
       </c>
       <c r="L23" t="s">
-        <v>1000</v>
+        <v>771</v>
       </c>
       <c r="M23" t="s">
         <v>56</v>
@@ -23591,16 +23708,16 @@
         <v>61</v>
       </c>
       <c r="T23" t="s">
-        <v>1002</v>
+        <v>774</v>
       </c>
       <c r="U23" s="1">
-        <v>3912.2</v>
+        <v>3922.2</v>
       </c>
       <c r="V23" s="1">
-        <v>3910.8</v>
+        <v>3915.7</v>
       </c>
       <c r="W23" s="1">
-        <v>4.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="X23" s="1">
         <v>0</v>
@@ -23612,25 +23729,25 @@
         <v>1228</v>
       </c>
       <c r="AA23" s="1">
-        <v>4804181.5999999996</v>
+        <v>4816461.5999999996</v>
       </c>
       <c r="AB23" s="1">
-        <v>16209.6</v>
+        <v>0</v>
       </c>
       <c r="AC23" s="1">
-        <v>5075848</v>
+        <v>5036438</v>
       </c>
       <c r="AD23" s="1">
-        <v>8400</v>
+        <v>8550</v>
       </c>
       <c r="AE23" s="1">
-        <v>59640</v>
+        <v>107730</v>
       </c>
       <c r="AF23" t="s">
         <v>64</v>
       </c>
       <c r="AH23" t="s">
-        <v>1003</v>
+        <v>775</v>
       </c>
       <c r="AI23" s="1">
         <v>0</v>
@@ -23642,25 +23759,25 @@
         <v>0</v>
       </c>
       <c r="AL23" s="1">
-        <v>16209.6</v>
+        <v>0</v>
       </c>
       <c r="AM23" s="1">
         <v>78056</v>
       </c>
       <c r="AN23" s="1">
-        <v>177400</v>
+        <v>141920</v>
       </c>
       <c r="AO23" s="1">
-        <v>253793</v>
+        <v>251822</v>
       </c>
       <c r="AP23" s="1">
-        <v>271665.59999999998</v>
+        <v>219976</v>
       </c>
       <c r="AQ23" s="1">
-        <v>5329641</v>
+        <v>5288260</v>
       </c>
       <c r="AR23" s="1">
-        <v>5397681</v>
+        <v>5404540</v>
       </c>
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.35">
@@ -23671,19 +23788,19 @@
         <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>357</v>
+        <v>219</v>
       </c>
       <c r="D24" t="s">
         <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>776</v>
+        <v>995</v>
       </c>
       <c r="F24" t="s">
-        <v>664</v>
+        <v>909</v>
       </c>
       <c r="G24" t="s">
-        <v>777</v>
+        <v>996</v>
       </c>
       <c r="H24" t="s">
         <v>52</v>
@@ -23695,13 +23812,13 @@
         <v>54</v>
       </c>
       <c r="K24" t="s">
-        <v>309</v>
+        <v>869</v>
       </c>
       <c r="L24" t="s">
-        <v>664</v>
+        <v>909</v>
       </c>
       <c r="M24" t="s">
-        <v>368</v>
+        <v>56</v>
       </c>
       <c r="N24" t="s">
         <v>57</v>
@@ -23710,28 +23827,28 @@
         <v>58</v>
       </c>
       <c r="P24" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="Q24" t="s">
         <v>60</v>
       </c>
       <c r="R24" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S24" t="s">
         <v>61</v>
       </c>
       <c r="T24" t="s">
-        <v>778</v>
+        <v>997</v>
       </c>
       <c r="U24" s="1">
-        <v>3845.4</v>
+        <v>3703.4</v>
       </c>
       <c r="V24" s="1">
-        <v>3826.8</v>
+        <v>3701.6</v>
       </c>
       <c r="W24" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X24" s="1">
         <v>0</v>
@@ -23743,55 +23860,55 @@
         <v>1228</v>
       </c>
       <c r="AA24" s="1">
-        <v>4722151.2</v>
+        <v>4547775.2</v>
       </c>
       <c r="AB24" s="1">
-        <v>0</v>
+        <v>11052</v>
       </c>
       <c r="AC24" s="1">
-        <v>4907240</v>
+        <v>4868766</v>
       </c>
       <c r="AD24" s="1">
-        <v>25200</v>
+        <v>7950</v>
       </c>
       <c r="AE24" s="1">
-        <v>0</v>
+        <v>23850</v>
       </c>
       <c r="AF24" t="s">
         <v>64</v>
       </c>
       <c r="AH24" t="s">
-        <v>779</v>
+        <v>998</v>
       </c>
       <c r="AI24" s="1">
-        <v>0</v>
+        <v>7950</v>
       </c>
       <c r="AJ24" s="1">
-        <v>0</v>
+        <v>35480</v>
       </c>
       <c r="AK24" s="1">
-        <v>0</v>
+        <v>11052</v>
       </c>
       <c r="AL24" s="1">
-        <v>0</v>
+        <v>11052</v>
       </c>
       <c r="AM24" s="1">
-        <v>78648</v>
+        <v>78056</v>
       </c>
       <c r="AN24" s="1">
-        <v>106440</v>
+        <v>177400</v>
       </c>
       <c r="AO24" s="1">
-        <v>245362</v>
+        <v>243439</v>
       </c>
       <c r="AP24" s="1">
-        <v>185088</v>
+        <v>320990</v>
       </c>
       <c r="AQ24" s="1">
-        <v>5152602</v>
+        <v>5112205</v>
       </c>
       <c r="AR24" s="1">
-        <v>5177802</v>
+        <v>5144005</v>
       </c>
     </row>
     <row r="25" spans="1:44" x14ac:dyDescent="0.35">
@@ -23802,19 +23919,19 @@
         <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>357</v>
+        <v>219</v>
       </c>
       <c r="D25" t="s">
         <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>780</v>
+        <v>999</v>
       </c>
       <c r="F25" t="s">
-        <v>664</v>
+        <v>1000</v>
       </c>
       <c r="G25" t="s">
-        <v>781</v>
+        <v>1001</v>
       </c>
       <c r="H25" t="s">
         <v>52</v>
@@ -23826,13 +23943,13 @@
         <v>54</v>
       </c>
       <c r="K25" t="s">
-        <v>315</v>
+        <v>874</v>
       </c>
       <c r="L25" t="s">
-        <v>664</v>
+        <v>1000</v>
       </c>
       <c r="M25" t="s">
-        <v>368</v>
+        <v>56</v>
       </c>
       <c r="N25" t="s">
         <v>57</v>
@@ -23841,7 +23958,7 @@
         <v>58</v>
       </c>
       <c r="P25" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="Q25" t="s">
         <v>60</v>
@@ -23853,16 +23970,16 @@
         <v>61</v>
       </c>
       <c r="T25" t="s">
-        <v>782</v>
+        <v>1002</v>
       </c>
       <c r="U25" s="1">
-        <v>3784.4</v>
+        <v>3912.2</v>
       </c>
       <c r="V25" s="1">
-        <v>3769.4</v>
+        <v>3910.8</v>
       </c>
       <c r="W25" s="1">
-        <v>0.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="X25" s="1">
         <v>0</v>
@@ -23874,25 +23991,25 @@
         <v>1228</v>
       </c>
       <c r="AA25" s="1">
-        <v>4647243.2</v>
+        <v>4804181.5999999996</v>
       </c>
       <c r="AB25" s="1">
-        <v>491.2</v>
+        <v>16209.6</v>
       </c>
       <c r="AC25" s="1">
-        <v>4736435</v>
+        <v>5075848</v>
       </c>
       <c r="AD25" s="1">
-        <v>16500</v>
+        <v>8400</v>
       </c>
       <c r="AE25" s="1">
-        <v>0</v>
+        <v>59640</v>
       </c>
       <c r="AF25" t="s">
         <v>64</v>
       </c>
       <c r="AH25" t="s">
-        <v>783</v>
+        <v>1003</v>
       </c>
       <c r="AI25" s="1">
         <v>0</v>
@@ -23904,25 +24021,25 @@
         <v>0</v>
       </c>
       <c r="AL25" s="1">
-        <v>491.2</v>
+        <v>16209.6</v>
       </c>
       <c r="AM25" s="1">
-        <v>0</v>
+        <v>78056</v>
       </c>
       <c r="AN25" s="1">
-        <v>88700</v>
+        <v>177400</v>
       </c>
       <c r="AO25" s="1">
-        <v>236822</v>
+        <v>253793</v>
       </c>
       <c r="AP25" s="1">
-        <v>89191.2</v>
+        <v>271665.59999999998</v>
       </c>
       <c r="AQ25" s="1">
-        <v>4973257</v>
+        <v>5329641</v>
       </c>
       <c r="AR25" s="1">
-        <v>4989757</v>
+        <v>5397681</v>
       </c>
     </row>
     <row r="26" spans="1:44" x14ac:dyDescent="0.35">
@@ -23933,19 +24050,19 @@
         <v>46</v>
       </c>
       <c r="C26" t="s">
-        <v>357</v>
+        <v>219</v>
       </c>
       <c r="D26" t="s">
         <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>784</v>
+        <v>1018</v>
       </c>
       <c r="F26" t="s">
-        <v>680</v>
+        <v>1009</v>
       </c>
       <c r="G26" t="s">
-        <v>785</v>
+        <v>1019</v>
       </c>
       <c r="H26" t="s">
         <v>52</v>
@@ -23957,13 +24074,13 @@
         <v>54</v>
       </c>
       <c r="K26" t="s">
-        <v>321</v>
+        <v>879</v>
       </c>
       <c r="L26" t="s">
-        <v>680</v>
+        <v>1009</v>
       </c>
       <c r="M26" t="s">
-        <v>368</v>
+        <v>56</v>
       </c>
       <c r="N26" t="s">
         <v>57</v>
@@ -23972,7 +24089,7 @@
         <v>58</v>
       </c>
       <c r="P26" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="Q26" t="s">
         <v>60</v>
@@ -23984,16 +24101,16 @@
         <v>61</v>
       </c>
       <c r="T26" t="s">
-        <v>786</v>
+        <v>1020</v>
       </c>
       <c r="U26" s="1">
-        <v>4062.6</v>
+        <v>4051</v>
       </c>
       <c r="V26" s="1">
-        <v>4049.8</v>
+        <v>4047.9</v>
       </c>
       <c r="W26" s="1">
-        <v>0</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="X26" s="1">
         <v>0</v>
@@ -24005,25 +24122,25 @@
         <v>1228</v>
       </c>
       <c r="AA26" s="1">
-        <v>4988872.8</v>
+        <v>4974628</v>
       </c>
       <c r="AB26" s="1">
-        <v>0</v>
+        <v>8104.8</v>
       </c>
       <c r="AC26" s="1">
-        <v>5041553</v>
+        <v>5131749</v>
       </c>
       <c r="AD26" s="1">
         <v>0</v>
       </c>
       <c r="AE26" s="1">
-        <v>35400</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="s">
         <v>64</v>
       </c>
       <c r="AH26" t="s">
-        <v>787</v>
+        <v>1021</v>
       </c>
       <c r="AI26" s="1">
         <v>0</v>
@@ -24035,25 +24152,25 @@
         <v>0</v>
       </c>
       <c r="AL26" s="1">
-        <v>0</v>
+        <v>8104.8</v>
       </c>
       <c r="AM26" s="1">
-        <v>0</v>
+        <v>78056</v>
       </c>
       <c r="AN26" s="1">
-        <v>52680</v>
+        <v>70960</v>
       </c>
       <c r="AO26" s="1">
-        <v>252078</v>
+        <v>256588</v>
       </c>
       <c r="AP26" s="1">
-        <v>52680</v>
+        <v>157120.79999999999</v>
       </c>
       <c r="AQ26" s="1">
-        <v>5293631</v>
+        <v>5388337</v>
       </c>
       <c r="AR26" s="1">
-        <v>5329031</v>
+        <v>5388337</v>
       </c>
     </row>
     <row r="27" spans="1:44" x14ac:dyDescent="0.35">
@@ -24070,13 +24187,13 @@
         <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="F27" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="G27" t="s">
-        <v>789</v>
+        <v>777</v>
       </c>
       <c r="H27" t="s">
         <v>52</v>
@@ -24088,10 +24205,10 @@
         <v>54</v>
       </c>
       <c r="K27" t="s">
-        <v>666</v>
+        <v>309</v>
       </c>
       <c r="L27" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="M27" t="s">
         <v>368</v>
@@ -24109,19 +24226,19 @@
         <v>60</v>
       </c>
       <c r="R27" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="S27" t="s">
         <v>61</v>
       </c>
       <c r="T27" t="s">
-        <v>790</v>
+        <v>778</v>
       </c>
       <c r="U27" s="1">
-        <v>4060.4</v>
+        <v>3845.4</v>
       </c>
       <c r="V27" s="1">
-        <v>4044.5</v>
+        <v>3826.8</v>
       </c>
       <c r="W27" s="1">
         <v>0</v>
@@ -24136,25 +24253,25 @@
         <v>1228</v>
       </c>
       <c r="AA27" s="1">
-        <v>4986171.2</v>
+        <v>4722151.2</v>
       </c>
       <c r="AB27" s="1">
         <v>0</v>
       </c>
       <c r="AC27" s="1">
-        <v>5092612</v>
+        <v>4907240</v>
       </c>
       <c r="AD27" s="1">
-        <v>26550</v>
+        <v>25200</v>
       </c>
       <c r="AE27" s="1">
-        <v>26550</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="s">
         <v>64</v>
       </c>
       <c r="AH27" t="s">
-        <v>791</v>
+        <v>779</v>
       </c>
       <c r="AI27" s="1">
         <v>0</v>
@@ -24169,22 +24286,22 @@
         <v>0</v>
       </c>
       <c r="AM27" s="1">
-        <v>0</v>
+        <v>78648</v>
       </c>
       <c r="AN27" s="1">
         <v>106440</v>
       </c>
       <c r="AO27" s="1">
-        <v>254631</v>
+        <v>245362</v>
       </c>
       <c r="AP27" s="1">
-        <v>106440</v>
+        <v>185088</v>
       </c>
       <c r="AQ27" s="1">
-        <v>5347243</v>
+        <v>5152602</v>
       </c>
       <c r="AR27" s="1">
-        <v>5400343</v>
+        <v>5177802</v>
       </c>
     </row>
     <row r="28" spans="1:44" x14ac:dyDescent="0.35">
@@ -24201,13 +24318,13 @@
         <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>792</v>
+        <v>780</v>
       </c>
       <c r="F28" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="G28" t="s">
-        <v>793</v>
+        <v>781</v>
       </c>
       <c r="H28" t="s">
         <v>52</v>
@@ -24219,10 +24336,10 @@
         <v>54</v>
       </c>
       <c r="K28" t="s">
-        <v>671</v>
+        <v>315</v>
       </c>
       <c r="L28" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="M28" t="s">
         <v>368</v>
@@ -24246,16 +24363,16 @@
         <v>61</v>
       </c>
       <c r="T28" t="s">
-        <v>794</v>
+        <v>782</v>
       </c>
       <c r="U28" s="1">
-        <v>3705.2</v>
+        <v>3784.4</v>
       </c>
       <c r="V28" s="1">
-        <v>3684.6</v>
+        <v>3769.4</v>
       </c>
       <c r="W28" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="X28" s="1">
         <v>0</v>
@@ -24267,25 +24384,25 @@
         <v>1228</v>
       </c>
       <c r="AA28" s="1">
-        <v>4549985.5999999996</v>
+        <v>4647243.2</v>
       </c>
       <c r="AB28" s="1">
-        <v>0</v>
+        <v>491.2</v>
       </c>
       <c r="AC28" s="1">
-        <v>4603206</v>
+        <v>4736435</v>
       </c>
       <c r="AD28" s="1">
-        <v>0</v>
+        <v>16500</v>
       </c>
       <c r="AE28" s="1">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="s">
         <v>64</v>
       </c>
       <c r="AH28" t="s">
-        <v>795</v>
+        <v>783</v>
       </c>
       <c r="AI28" s="1">
         <v>0</v>
@@ -24297,25 +24414,25 @@
         <v>0</v>
       </c>
       <c r="AL28" s="1">
-        <v>0</v>
+        <v>491.2</v>
       </c>
       <c r="AM28" s="1">
         <v>0</v>
       </c>
       <c r="AN28" s="1">
-        <v>53220</v>
+        <v>88700</v>
       </c>
       <c r="AO28" s="1">
-        <v>230161</v>
+        <v>236822</v>
       </c>
       <c r="AP28" s="1">
-        <v>53220</v>
+        <v>89191.2</v>
       </c>
       <c r="AQ28" s="1">
-        <v>4833367</v>
+        <v>4973257</v>
       </c>
       <c r="AR28" s="1">
-        <v>4849567</v>
+        <v>4989757</v>
       </c>
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.35">
@@ -24332,13 +24449,13 @@
         <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>796</v>
+        <v>784</v>
       </c>
       <c r="F29" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="G29" t="s">
-        <v>797</v>
+        <v>785</v>
       </c>
       <c r="H29" t="s">
         <v>52</v>
@@ -24350,10 +24467,10 @@
         <v>54</v>
       </c>
       <c r="K29" t="s">
-        <v>676</v>
+        <v>321</v>
       </c>
       <c r="L29" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="M29" t="s">
         <v>368</v>
@@ -24371,19 +24488,19 @@
         <v>60</v>
       </c>
       <c r="R29" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S29" t="s">
         <v>61</v>
       </c>
       <c r="T29" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="U29" s="1">
-        <v>4050.4</v>
+        <v>4062.6</v>
       </c>
       <c r="V29" s="1">
-        <v>4031</v>
+        <v>4049.8</v>
       </c>
       <c r="W29" s="1">
         <v>0</v>
@@ -24398,25 +24515,25 @@
         <v>1228</v>
       </c>
       <c r="AA29" s="1">
-        <v>4973891.2</v>
+        <v>4988872.8</v>
       </c>
       <c r="AB29" s="1">
         <v>0</v>
       </c>
       <c r="AC29" s="1">
-        <v>5027652</v>
+        <v>5041553</v>
       </c>
       <c r="AD29" s="1">
         <v>0</v>
       </c>
       <c r="AE29" s="1">
-        <v>0</v>
+        <v>35400</v>
       </c>
       <c r="AF29" t="s">
         <v>64</v>
       </c>
       <c r="AH29" t="s">
-        <v>799</v>
+        <v>787</v>
       </c>
       <c r="AI29" s="1">
         <v>0</v>
@@ -24425,7 +24542,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="1">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="AL29" s="1">
         <v>0</v>
@@ -24434,19 +24551,19 @@
         <v>0</v>
       </c>
       <c r="AN29" s="1">
-        <v>53220</v>
+        <v>52680</v>
       </c>
       <c r="AO29" s="1">
-        <v>251383</v>
+        <v>252078</v>
       </c>
       <c r="AP29" s="1">
-        <v>53760</v>
+        <v>52680</v>
       </c>
       <c r="AQ29" s="1">
-        <v>5279035</v>
+        <v>5293631</v>
       </c>
       <c r="AR29" s="1">
-        <v>5279035</v>
+        <v>5329031</v>
       </c>
     </row>
     <row r="30" spans="1:44" x14ac:dyDescent="0.35">
@@ -24463,13 +24580,13 @@
         <v>48</v>
       </c>
       <c r="E30" t="s">
-        <v>800</v>
+        <v>788</v>
       </c>
       <c r="F30" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="G30" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="H30" t="s">
         <v>52</v>
@@ -24481,10 +24598,10 @@
         <v>54</v>
       </c>
       <c r="K30" t="s">
-        <v>682</v>
+        <v>666</v>
       </c>
       <c r="L30" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="M30" t="s">
         <v>368</v>
@@ -24502,22 +24619,22 @@
         <v>60</v>
       </c>
       <c r="R30" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S30" t="s">
         <v>61</v>
       </c>
       <c r="T30" t="s">
-        <v>694</v>
+        <v>790</v>
       </c>
       <c r="U30" s="1">
-        <v>3440.8</v>
+        <v>4060.4</v>
       </c>
       <c r="V30" s="1">
-        <v>3429.5</v>
+        <v>4044.5</v>
       </c>
       <c r="W30" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="X30" s="1">
         <v>0</v>
@@ -24529,25 +24646,25 @@
         <v>1228</v>
       </c>
       <c r="AA30" s="1">
-        <v>4225302.4000000004</v>
+        <v>4986171.2</v>
       </c>
       <c r="AB30" s="1">
-        <v>491.2</v>
+        <v>0</v>
       </c>
       <c r="AC30" s="1">
-        <v>4302994</v>
+        <v>5092612</v>
       </c>
       <c r="AD30" s="1">
-        <v>15000</v>
+        <v>26550</v>
       </c>
       <c r="AE30" s="1">
-        <v>0</v>
+        <v>26550</v>
       </c>
       <c r="AF30" t="s">
         <v>64</v>
       </c>
       <c r="AH30" t="s">
-        <v>802</v>
+        <v>791</v>
       </c>
       <c r="AI30" s="1">
         <v>0</v>
@@ -24559,25 +24676,25 @@
         <v>0</v>
       </c>
       <c r="AL30" s="1">
-        <v>491.2</v>
+        <v>0</v>
       </c>
       <c r="AM30" s="1">
         <v>0</v>
       </c>
       <c r="AN30" s="1">
-        <v>77200</v>
+        <v>106440</v>
       </c>
       <c r="AO30" s="1">
-        <v>215150</v>
+        <v>254631</v>
       </c>
       <c r="AP30" s="1">
-        <v>77691.199999999997</v>
+        <v>106440</v>
       </c>
       <c r="AQ30" s="1">
-        <v>4518144</v>
+        <v>5347243</v>
       </c>
       <c r="AR30" s="1">
-        <v>4533144</v>
+        <v>5400343</v>
       </c>
     </row>
     <row r="31" spans="1:44" x14ac:dyDescent="0.35">
@@ -24594,13 +24711,13 @@
         <v>48</v>
       </c>
       <c r="E31" t="s">
-        <v>803</v>
+        <v>792</v>
       </c>
       <c r="F31" t="s">
-        <v>697</v>
+        <v>680</v>
       </c>
       <c r="G31" t="s">
-        <v>804</v>
+        <v>793</v>
       </c>
       <c r="H31" t="s">
         <v>52</v>
@@ -24612,10 +24729,10 @@
         <v>54</v>
       </c>
       <c r="K31" t="s">
-        <v>688</v>
+        <v>671</v>
       </c>
       <c r="L31" t="s">
-        <v>697</v>
+        <v>680</v>
       </c>
       <c r="M31" t="s">
         <v>368</v>
@@ -24639,13 +24756,13 @@
         <v>61</v>
       </c>
       <c r="T31" t="s">
-        <v>805</v>
+        <v>794</v>
       </c>
       <c r="U31" s="1">
-        <v>3916.8</v>
+        <v>3705.2</v>
       </c>
       <c r="V31" s="1">
-        <v>3907.2</v>
+        <v>3684.6</v>
       </c>
       <c r="W31" s="1">
         <v>0</v>
@@ -24660,25 +24777,25 @@
         <v>1228</v>
       </c>
       <c r="AA31" s="1">
-        <v>4809830.4000000004</v>
+        <v>4549985.5999999996</v>
       </c>
       <c r="AB31" s="1">
         <v>0</v>
       </c>
       <c r="AC31" s="1">
-        <v>4987231</v>
+        <v>4603206</v>
       </c>
       <c r="AD31" s="1">
-        <v>60705</v>
+        <v>0</v>
       </c>
       <c r="AE31" s="1">
-        <v>60705</v>
+        <v>16200</v>
       </c>
       <c r="AF31" t="s">
         <v>64</v>
       </c>
       <c r="AH31" t="s">
-        <v>806</v>
+        <v>795</v>
       </c>
       <c r="AI31" s="1">
         <v>0</v>
@@ -24696,19 +24813,19 @@
         <v>0</v>
       </c>
       <c r="AN31" s="1">
-        <v>177400</v>
+        <v>53220</v>
       </c>
       <c r="AO31" s="1">
-        <v>249362</v>
+        <v>230161</v>
       </c>
       <c r="AP31" s="1">
-        <v>177400</v>
+        <v>53220</v>
       </c>
       <c r="AQ31" s="1">
-        <v>5236593</v>
+        <v>4833367</v>
       </c>
       <c r="AR31" s="1">
-        <v>5358003</v>
+        <v>4849567</v>
       </c>
     </row>
     <row r="32" spans="1:44" x14ac:dyDescent="0.35">
@@ -24725,13 +24842,13 @@
         <v>48</v>
       </c>
       <c r="E32" t="s">
-        <v>807</v>
+        <v>796</v>
       </c>
       <c r="F32" t="s">
-        <v>708</v>
+        <v>686</v>
       </c>
       <c r="G32" t="s">
-        <v>808</v>
+        <v>797</v>
       </c>
       <c r="H32" t="s">
         <v>52</v>
@@ -24743,10 +24860,10 @@
         <v>54</v>
       </c>
       <c r="K32" t="s">
-        <v>693</v>
+        <v>676</v>
       </c>
       <c r="L32" t="s">
-        <v>708</v>
+        <v>686</v>
       </c>
       <c r="M32" t="s">
         <v>368</v>
@@ -24764,19 +24881,19 @@
         <v>60</v>
       </c>
       <c r="R32" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="S32" t="s">
         <v>61</v>
       </c>
       <c r="T32" t="s">
-        <v>716</v>
+        <v>798</v>
       </c>
       <c r="U32" s="1">
-        <v>3569.6</v>
+        <v>4050.4</v>
       </c>
       <c r="V32" s="1">
-        <v>3551.4</v>
+        <v>4031</v>
       </c>
       <c r="W32" s="1">
         <v>0</v>
@@ -24791,25 +24908,25 @@
         <v>1228</v>
       </c>
       <c r="AA32" s="1">
-        <v>4383468.8</v>
+        <v>4973891.2</v>
       </c>
       <c r="AB32" s="1">
         <v>0</v>
       </c>
       <c r="AC32" s="1">
-        <v>4596349</v>
+        <v>5027652</v>
       </c>
       <c r="AD32" s="1">
-        <v>81120</v>
+        <v>0</v>
       </c>
       <c r="AE32" s="1">
-        <v>89700</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="s">
         <v>64</v>
       </c>
       <c r="AH32" t="s">
-        <v>809</v>
+        <v>799</v>
       </c>
       <c r="AI32" s="1">
         <v>0</v>
@@ -24818,7 +24935,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="1">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="AL32" s="1">
         <v>0</v>
@@ -24827,19 +24944,19 @@
         <v>0</v>
       </c>
       <c r="AN32" s="1">
-        <v>212880</v>
+        <v>53220</v>
       </c>
       <c r="AO32" s="1">
-        <v>229818</v>
+        <v>251383</v>
       </c>
       <c r="AP32" s="1">
-        <v>212880</v>
+        <v>53760</v>
       </c>
       <c r="AQ32" s="1">
-        <v>4826167</v>
+        <v>5279035</v>
       </c>
       <c r="AR32" s="1">
-        <v>4996987</v>
+        <v>5279035</v>
       </c>
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.35">
@@ -24856,13 +24973,13 @@
         <v>48</v>
       </c>
       <c r="E33" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
       <c r="F33" t="s">
-        <v>719</v>
+        <v>686</v>
       </c>
       <c r="G33" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
       <c r="H33" t="s">
         <v>52</v>
@@ -24874,13 +24991,13 @@
         <v>54</v>
       </c>
       <c r="K33" t="s">
-        <v>699</v>
+        <v>682</v>
       </c>
       <c r="L33" t="s">
-        <v>708</v>
+        <v>686</v>
       </c>
       <c r="M33" t="s">
-        <v>212</v>
+        <v>368</v>
       </c>
       <c r="N33" t="s">
         <v>57</v>
@@ -24895,22 +25012,22 @@
         <v>60</v>
       </c>
       <c r="R33" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="S33" t="s">
         <v>61</v>
       </c>
       <c r="T33" t="s">
-        <v>812</v>
+        <v>694</v>
       </c>
       <c r="U33" s="1">
-        <v>3854.8</v>
+        <v>3440.8</v>
       </c>
       <c r="V33" s="1">
-        <v>3841.9</v>
+        <v>3429.5</v>
       </c>
       <c r="W33" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="X33" s="1">
         <v>0</v>
@@ -24922,25 +25039,25 @@
         <v>1228</v>
       </c>
       <c r="AA33" s="1">
-        <v>4733694.4000000004</v>
+        <v>4225302.4000000004</v>
       </c>
       <c r="AB33" s="1">
-        <v>0</v>
+        <v>491.2</v>
       </c>
       <c r="AC33" s="1">
-        <v>4875615</v>
+        <v>4302994</v>
       </c>
       <c r="AD33" s="1">
-        <v>50400</v>
+        <v>15000</v>
       </c>
       <c r="AE33" s="1">
-        <v>87360</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="s">
         <v>64</v>
       </c>
       <c r="AH33" t="s">
-        <v>813</v>
+        <v>802</v>
       </c>
       <c r="AI33" s="1">
         <v>0</v>
@@ -24952,25 +25069,25 @@
         <v>0</v>
       </c>
       <c r="AL33" s="1">
-        <v>0</v>
+        <v>491.2</v>
       </c>
       <c r="AM33" s="1">
         <v>0</v>
       </c>
       <c r="AN33" s="1">
-        <v>141920</v>
+        <v>77200</v>
       </c>
       <c r="AO33" s="1">
-        <v>243781</v>
+        <v>215150</v>
       </c>
       <c r="AP33" s="1">
-        <v>141920</v>
+        <v>77691.199999999997</v>
       </c>
       <c r="AQ33" s="1">
-        <v>5119396</v>
+        <v>4518144</v>
       </c>
       <c r="AR33" s="1">
-        <v>5257156</v>
+        <v>4533144</v>
       </c>
     </row>
     <row r="34" spans="1:44" x14ac:dyDescent="0.35">
@@ -24987,13 +25104,13 @@
         <v>48</v>
       </c>
       <c r="E34" t="s">
-        <v>814</v>
+        <v>803</v>
       </c>
       <c r="F34" t="s">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="G34" t="s">
-        <v>815</v>
+        <v>804</v>
       </c>
       <c r="H34" t="s">
         <v>52</v>
@@ -25005,10 +25122,10 @@
         <v>54</v>
       </c>
       <c r="K34" t="s">
-        <v>704</v>
+        <v>688</v>
       </c>
       <c r="L34" t="s">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="M34" t="s">
         <v>368</v>
@@ -25032,13 +25149,13 @@
         <v>61</v>
       </c>
       <c r="T34" t="s">
-        <v>816</v>
+        <v>805</v>
       </c>
       <c r="U34" s="1">
-        <v>3990.4</v>
+        <v>3916.8</v>
       </c>
       <c r="V34" s="1">
-        <v>3973.8</v>
+        <v>3907.2</v>
       </c>
       <c r="W34" s="1">
         <v>0</v>
@@ -25053,25 +25170,25 @@
         <v>1228</v>
       </c>
       <c r="AA34" s="1">
-        <v>4900211.2</v>
+        <v>4809830.4000000004</v>
       </c>
       <c r="AB34" s="1">
         <v>0</v>
       </c>
       <c r="AC34" s="1">
-        <v>5042132</v>
+        <v>4987231</v>
       </c>
       <c r="AD34" s="1">
-        <v>43500</v>
+        <v>60705</v>
       </c>
       <c r="AE34" s="1">
-        <v>26100</v>
+        <v>60705</v>
       </c>
       <c r="AF34" t="s">
         <v>64</v>
       </c>
       <c r="AH34" t="s">
-        <v>817</v>
+        <v>806</v>
       </c>
       <c r="AI34" s="1">
         <v>0</v>
@@ -25089,19 +25206,19 @@
         <v>0</v>
       </c>
       <c r="AN34" s="1">
-        <v>141920</v>
+        <v>177400</v>
       </c>
       <c r="AO34" s="1">
-        <v>252107</v>
+        <v>249362</v>
       </c>
       <c r="AP34" s="1">
-        <v>141920</v>
+        <v>177400</v>
       </c>
       <c r="AQ34" s="1">
-        <v>5294239</v>
+        <v>5236593</v>
       </c>
       <c r="AR34" s="1">
-        <v>5363839</v>
+        <v>5358003</v>
       </c>
     </row>
     <row r="35" spans="1:44" x14ac:dyDescent="0.35">
@@ -25118,13 +25235,13 @@
         <v>48</v>
       </c>
       <c r="E35" t="s">
-        <v>818</v>
+        <v>807</v>
       </c>
       <c r="F35" t="s">
-        <v>725</v>
+        <v>708</v>
       </c>
       <c r="G35" t="s">
-        <v>819</v>
+        <v>808</v>
       </c>
       <c r="H35" t="s">
         <v>52</v>
@@ -25136,10 +25253,10 @@
         <v>54</v>
       </c>
       <c r="K35" t="s">
-        <v>710</v>
+        <v>693</v>
       </c>
       <c r="L35" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="M35" t="s">
         <v>368</v>
@@ -25163,13 +25280,13 @@
         <v>61</v>
       </c>
       <c r="T35" t="s">
-        <v>820</v>
+        <v>716</v>
       </c>
       <c r="U35" s="1">
-        <v>3711</v>
+        <v>3569.6</v>
       </c>
       <c r="V35" s="1">
-        <v>3692.5</v>
+        <v>3551.4</v>
       </c>
       <c r="W35" s="1">
         <v>0</v>
@@ -25184,25 +25301,25 @@
         <v>1228</v>
       </c>
       <c r="AA35" s="1">
-        <v>4557108</v>
+        <v>4383468.8</v>
       </c>
       <c r="AB35" s="1">
         <v>0</v>
       </c>
       <c r="AC35" s="1">
-        <v>4628068</v>
+        <v>4596349</v>
       </c>
       <c r="AD35" s="1">
-        <v>8100</v>
+        <v>81120</v>
       </c>
       <c r="AE35" s="1">
-        <v>8100</v>
+        <v>89700</v>
       </c>
       <c r="AF35" t="s">
         <v>64</v>
       </c>
       <c r="AH35" t="s">
-        <v>821</v>
+        <v>809</v>
       </c>
       <c r="AI35" s="1">
         <v>0</v>
@@ -25220,19 +25337,19 @@
         <v>0</v>
       </c>
       <c r="AN35" s="1">
-        <v>70960</v>
+        <v>212880</v>
       </c>
       <c r="AO35" s="1">
-        <v>231404</v>
+        <v>229818</v>
       </c>
       <c r="AP35" s="1">
-        <v>70960</v>
+        <v>212880</v>
       </c>
       <c r="AQ35" s="1">
-        <v>4859472</v>
+        <v>4826167</v>
       </c>
       <c r="AR35" s="1">
-        <v>4875672</v>
+        <v>4996987</v>
       </c>
     </row>
     <row r="36" spans="1:44" x14ac:dyDescent="0.35">
@@ -25249,13 +25366,13 @@
         <v>48</v>
       </c>
       <c r="E36" t="s">
-        <v>822</v>
+        <v>810</v>
       </c>
       <c r="F36" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="G36" t="s">
-        <v>823</v>
+        <v>811</v>
       </c>
       <c r="H36" t="s">
         <v>52</v>
@@ -25267,13 +25384,13 @@
         <v>54</v>
       </c>
       <c r="K36" t="s">
-        <v>715</v>
+        <v>699</v>
       </c>
       <c r="L36" t="s">
-        <v>725</v>
+        <v>708</v>
       </c>
       <c r="M36" t="s">
-        <v>368</v>
+        <v>212</v>
       </c>
       <c r="N36" t="s">
         <v>57</v>
@@ -25294,13 +25411,13 @@
         <v>61</v>
       </c>
       <c r="T36" t="s">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="U36" s="1">
-        <v>3904.6</v>
+        <v>3854.8</v>
       </c>
       <c r="V36" s="1">
-        <v>3874.6</v>
+        <v>3841.9</v>
       </c>
       <c r="W36" s="1">
         <v>0</v>
@@ -25315,25 +25432,25 @@
         <v>1228</v>
       </c>
       <c r="AA36" s="1">
-        <v>4794848.8</v>
+        <v>4733694.4000000004</v>
       </c>
       <c r="AB36" s="1">
         <v>0</v>
       </c>
       <c r="AC36" s="1">
-        <v>4848069</v>
+        <v>4875615</v>
       </c>
       <c r="AD36" s="1">
-        <v>0</v>
+        <v>50400</v>
       </c>
       <c r="AE36" s="1">
-        <v>8550</v>
+        <v>87360</v>
       </c>
       <c r="AF36" t="s">
         <v>64</v>
       </c>
       <c r="AH36" t="s">
-        <v>825</v>
+        <v>813</v>
       </c>
       <c r="AI36" s="1">
         <v>0</v>
@@ -25351,19 +25468,19 @@
         <v>0</v>
       </c>
       <c r="AN36" s="1">
-        <v>53220</v>
+        <v>141920</v>
       </c>
       <c r="AO36" s="1">
-        <v>242404</v>
+        <v>243781</v>
       </c>
       <c r="AP36" s="1">
-        <v>53220</v>
+        <v>141920</v>
       </c>
       <c r="AQ36" s="1">
-        <v>5090473</v>
+        <v>5119396</v>
       </c>
       <c r="AR36" s="1">
-        <v>5099023</v>
+        <v>5257156</v>
       </c>
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.35">
@@ -25380,13 +25497,13 @@
         <v>48</v>
       </c>
       <c r="E37" t="s">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="F37" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="G37" t="s">
-        <v>827</v>
+        <v>815</v>
       </c>
       <c r="H37" t="s">
         <v>52</v>
@@ -25398,10 +25515,10 @@
         <v>54</v>
       </c>
       <c r="K37" t="s">
-        <v>721</v>
+        <v>704</v>
       </c>
       <c r="L37" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="M37" t="s">
         <v>368</v>
@@ -25425,13 +25542,13 @@
         <v>61</v>
       </c>
       <c r="T37" t="s">
-        <v>828</v>
+        <v>816</v>
       </c>
       <c r="U37" s="1">
-        <v>3840.8</v>
+        <v>3990.4</v>
       </c>
       <c r="V37" s="1">
-        <v>3818.8</v>
+        <v>3973.8</v>
       </c>
       <c r="W37" s="1">
         <v>0</v>
@@ -25446,25 +25563,25 @@
         <v>1228</v>
       </c>
       <c r="AA37" s="1">
-        <v>4716502.4000000004</v>
+        <v>4900211.2</v>
       </c>
       <c r="AB37" s="1">
         <v>0</v>
       </c>
       <c r="AC37" s="1">
-        <v>4769723</v>
+        <v>5042132</v>
       </c>
       <c r="AD37" s="1">
-        <v>0</v>
+        <v>43500</v>
       </c>
       <c r="AE37" s="1">
-        <v>8400</v>
+        <v>26100</v>
       </c>
       <c r="AF37" t="s">
         <v>64</v>
       </c>
       <c r="AH37" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="AI37" s="1">
         <v>0</v>
@@ -25482,19 +25599,19 @@
         <v>0</v>
       </c>
       <c r="AN37" s="1">
-        <v>53220</v>
+        <v>141920</v>
       </c>
       <c r="AO37" s="1">
-        <v>238487</v>
+        <v>252107</v>
       </c>
       <c r="AP37" s="1">
-        <v>53220</v>
+        <v>141920</v>
       </c>
       <c r="AQ37" s="1">
-        <v>5008210</v>
+        <v>5294239</v>
       </c>
       <c r="AR37" s="1">
-        <v>5016610</v>
+        <v>5363839</v>
       </c>
     </row>
     <row r="38" spans="1:44" x14ac:dyDescent="0.35">
@@ -25511,13 +25628,13 @@
         <v>48</v>
       </c>
       <c r="E38" t="s">
-        <v>830</v>
+        <v>818</v>
       </c>
       <c r="F38" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="G38" t="s">
-        <v>831</v>
+        <v>819</v>
       </c>
       <c r="H38" t="s">
         <v>52</v>
@@ -25529,10 +25646,10 @@
         <v>54</v>
       </c>
       <c r="K38" t="s">
-        <v>727</v>
+        <v>710</v>
       </c>
       <c r="L38" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="M38" t="s">
         <v>368</v>
@@ -25556,13 +25673,13 @@
         <v>61</v>
       </c>
       <c r="T38" t="s">
-        <v>832</v>
+        <v>820</v>
       </c>
       <c r="U38" s="1">
-        <v>3841.8</v>
+        <v>3711</v>
       </c>
       <c r="V38" s="1">
-        <v>3817.2</v>
+        <v>3692.5</v>
       </c>
       <c r="W38" s="1">
         <v>0</v>
@@ -25577,25 +25694,25 @@
         <v>1228</v>
       </c>
       <c r="AA38" s="1">
-        <v>4717730.4000000004</v>
+        <v>4557108</v>
       </c>
       <c r="AB38" s="1">
         <v>0</v>
       </c>
       <c r="AC38" s="1">
-        <v>4770951</v>
+        <v>4628068</v>
       </c>
       <c r="AD38" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="AE38" s="1">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="AF38" t="s">
         <v>64</v>
       </c>
       <c r="AH38" t="s">
-        <v>833</v>
+        <v>821</v>
       </c>
       <c r="AI38" s="1">
         <v>0</v>
@@ -25613,19 +25730,19 @@
         <v>0</v>
       </c>
       <c r="AN38" s="1">
-        <v>53220</v>
+        <v>70960</v>
       </c>
       <c r="AO38" s="1">
-        <v>238548</v>
+        <v>231404</v>
       </c>
       <c r="AP38" s="1">
-        <v>53220</v>
+        <v>70960</v>
       </c>
       <c r="AQ38" s="1">
-        <v>5009499</v>
+        <v>4859472</v>
       </c>
       <c r="AR38" s="1">
-        <v>5009499</v>
+        <v>4875672</v>
       </c>
     </row>
     <row r="39" spans="1:44" x14ac:dyDescent="0.35">
@@ -25642,13 +25759,13 @@
         <v>48</v>
       </c>
       <c r="E39" t="s">
-        <v>834</v>
+        <v>822</v>
       </c>
       <c r="F39" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="G39" t="s">
-        <v>835</v>
+        <v>823</v>
       </c>
       <c r="H39" t="s">
         <v>52</v>
@@ -25660,10 +25777,10 @@
         <v>54</v>
       </c>
       <c r="K39" t="s">
-        <v>733</v>
+        <v>715</v>
       </c>
       <c r="L39" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="M39" t="s">
         <v>368</v>
@@ -25687,13 +25804,13 @@
         <v>61</v>
       </c>
       <c r="T39" t="s">
-        <v>836</v>
+        <v>824</v>
       </c>
       <c r="U39" s="1">
-        <v>3978.2</v>
+        <v>3904.6</v>
       </c>
       <c r="V39" s="1">
-        <v>3953.4</v>
+        <v>3874.6</v>
       </c>
       <c r="W39" s="1">
         <v>0</v>
@@ -25708,25 +25825,25 @@
         <v>1228</v>
       </c>
       <c r="AA39" s="1">
-        <v>4885229.5999999996</v>
+        <v>4794848.8</v>
       </c>
       <c r="AB39" s="1">
         <v>0</v>
       </c>
       <c r="AC39" s="1">
-        <v>4938450</v>
+        <v>4848069</v>
       </c>
       <c r="AD39" s="1">
         <v>0</v>
       </c>
       <c r="AE39" s="1">
-        <v>26100</v>
+        <v>8550</v>
       </c>
       <c r="AF39" t="s">
         <v>64</v>
       </c>
       <c r="AH39" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
       <c r="AI39" s="1">
         <v>0</v>
@@ -25747,16 +25864,16 @@
         <v>53220</v>
       </c>
       <c r="AO39" s="1">
-        <v>246923</v>
+        <v>242404</v>
       </c>
       <c r="AP39" s="1">
         <v>53220</v>
       </c>
       <c r="AQ39" s="1">
-        <v>5185373</v>
+        <v>5090473</v>
       </c>
       <c r="AR39" s="1">
-        <v>5211473</v>
+        <v>5099023</v>
       </c>
     </row>
     <row r="40" spans="1:44" x14ac:dyDescent="0.35">
@@ -25773,13 +25890,13 @@
         <v>48</v>
       </c>
       <c r="E40" t="s">
-        <v>838</v>
+        <v>826</v>
       </c>
       <c r="F40" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="G40" t="s">
-        <v>839</v>
+        <v>827</v>
       </c>
       <c r="H40" t="s">
         <v>52</v>
@@ -25791,10 +25908,10 @@
         <v>54</v>
       </c>
       <c r="K40" t="s">
-        <v>738</v>
+        <v>721</v>
       </c>
       <c r="L40" t="s">
-        <v>742</v>
+        <v>725</v>
       </c>
       <c r="M40" t="s">
         <v>368</v>
@@ -25818,13 +25935,13 @@
         <v>61</v>
       </c>
       <c r="T40" t="s">
-        <v>840</v>
+        <v>828</v>
       </c>
       <c r="U40" s="1">
-        <v>3923.4</v>
+        <v>3840.8</v>
       </c>
       <c r="V40" s="1">
-        <v>3912.4</v>
+        <v>3818.8</v>
       </c>
       <c r="W40" s="1">
         <v>0</v>
@@ -25839,25 +25956,25 @@
         <v>1228</v>
       </c>
       <c r="AA40" s="1">
-        <v>4817935.2</v>
+        <v>4716502.4000000004</v>
       </c>
       <c r="AB40" s="1">
         <v>0</v>
       </c>
       <c r="AC40" s="1">
-        <v>4871156</v>
+        <v>4769723</v>
       </c>
       <c r="AD40" s="1">
         <v>0</v>
       </c>
       <c r="AE40" s="1">
-        <v>25650</v>
+        <v>8400</v>
       </c>
       <c r="AF40" t="s">
         <v>64</v>
       </c>
       <c r="AH40" t="s">
-        <v>841</v>
+        <v>829</v>
       </c>
       <c r="AI40" s="1">
         <v>0</v>
@@ -25878,16 +25995,16 @@
         <v>53220</v>
       </c>
       <c r="AO40" s="1">
-        <v>243558</v>
+        <v>238487</v>
       </c>
       <c r="AP40" s="1">
         <v>53220</v>
       </c>
       <c r="AQ40" s="1">
-        <v>5114714</v>
+        <v>5008210</v>
       </c>
       <c r="AR40" s="1">
-        <v>5140364</v>
+        <v>5016610</v>
       </c>
     </row>
     <row r="41" spans="1:44" x14ac:dyDescent="0.35">
@@ -25904,13 +26021,13 @@
         <v>48</v>
       </c>
       <c r="E41" t="s">
-        <v>842</v>
+        <v>830</v>
       </c>
       <c r="F41" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="G41" t="s">
-        <v>843</v>
+        <v>831</v>
       </c>
       <c r="H41" t="s">
         <v>52</v>
@@ -25922,10 +26039,10 @@
         <v>54</v>
       </c>
       <c r="K41" t="s">
-        <v>744</v>
+        <v>727</v>
       </c>
       <c r="L41" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="M41" t="s">
         <v>368</v>
@@ -25949,13 +26066,13 @@
         <v>61</v>
       </c>
       <c r="T41" t="s">
-        <v>844</v>
+        <v>832</v>
       </c>
       <c r="U41" s="1">
-        <v>3901.2</v>
+        <v>3841.8</v>
       </c>
       <c r="V41" s="1">
-        <v>3870.4</v>
+        <v>3817.2</v>
       </c>
       <c r="W41" s="1">
         <v>0</v>
@@ -25970,13 +26087,13 @@
         <v>1228</v>
       </c>
       <c r="AA41" s="1">
-        <v>4790673.5999999996</v>
+        <v>4717730.4000000004</v>
       </c>
       <c r="AB41" s="1">
         <v>0</v>
       </c>
       <c r="AC41" s="1">
-        <v>4843894</v>
+        <v>4770951</v>
       </c>
       <c r="AD41" s="1">
         <v>0</v>
@@ -25988,7 +26105,7 @@
         <v>64</v>
       </c>
       <c r="AH41" t="s">
-        <v>845</v>
+        <v>833</v>
       </c>
       <c r="AI41" s="1">
         <v>0</v>
@@ -26009,16 +26126,16 @@
         <v>53220</v>
       </c>
       <c r="AO41" s="1">
-        <v>242195</v>
+        <v>238548</v>
       </c>
       <c r="AP41" s="1">
         <v>53220</v>
       </c>
       <c r="AQ41" s="1">
-        <v>5086089</v>
+        <v>5009499</v>
       </c>
       <c r="AR41" s="1">
-        <v>5086089</v>
+        <v>5009499</v>
       </c>
     </row>
     <row r="42" spans="1:44" x14ac:dyDescent="0.35">
@@ -26035,13 +26152,13 @@
         <v>48</v>
       </c>
       <c r="E42" t="s">
-        <v>846</v>
+        <v>834</v>
       </c>
       <c r="F42" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
       <c r="G42" t="s">
-        <v>847</v>
+        <v>835</v>
       </c>
       <c r="H42" t="s">
         <v>52</v>
@@ -26053,13 +26170,13 @@
         <v>54</v>
       </c>
       <c r="K42" t="s">
-        <v>750</v>
+        <v>733</v>
       </c>
       <c r="L42" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
       <c r="M42" t="s">
-        <v>212</v>
+        <v>368</v>
       </c>
       <c r="N42" t="s">
         <v>57</v>
@@ -26080,13 +26197,13 @@
         <v>61</v>
       </c>
       <c r="T42" t="s">
-        <v>756</v>
+        <v>836</v>
       </c>
       <c r="U42" s="1">
-        <v>3918.2</v>
+        <v>3978.2</v>
       </c>
       <c r="V42" s="1">
-        <v>3902.7</v>
+        <v>3953.4</v>
       </c>
       <c r="W42" s="1">
         <v>0</v>
@@ -26101,25 +26218,25 @@
         <v>1228</v>
       </c>
       <c r="AA42" s="1">
-        <v>4811549.5999999996</v>
+        <v>4885229.5999999996</v>
       </c>
       <c r="AB42" s="1">
         <v>0</v>
       </c>
       <c r="AC42" s="1">
-        <v>4864770</v>
+        <v>4938450</v>
       </c>
       <c r="AD42" s="1">
         <v>0</v>
       </c>
       <c r="AE42" s="1">
-        <v>0</v>
+        <v>26100</v>
       </c>
       <c r="AF42" t="s">
         <v>64</v>
       </c>
       <c r="AH42" t="s">
-        <v>848</v>
+        <v>837</v>
       </c>
       <c r="AI42" s="1">
         <v>0</v>
@@ -26140,16 +26257,16 @@
         <v>53220</v>
       </c>
       <c r="AO42" s="1">
-        <v>243239</v>
+        <v>246923</v>
       </c>
       <c r="AP42" s="1">
         <v>53220</v>
       </c>
       <c r="AQ42" s="1">
-        <v>5108009</v>
+        <v>5185373</v>
       </c>
       <c r="AR42" s="1">
-        <v>5108009</v>
+        <v>5211473</v>
       </c>
     </row>
     <row r="43" spans="1:44" x14ac:dyDescent="0.35">
@@ -26166,13 +26283,13 @@
         <v>48</v>
       </c>
       <c r="E43" t="s">
-        <v>849</v>
+        <v>838</v>
       </c>
       <c r="F43" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="G43" t="s">
-        <v>850</v>
+        <v>839</v>
       </c>
       <c r="H43" t="s">
         <v>52</v>
@@ -26184,10 +26301,10 @@
         <v>54</v>
       </c>
       <c r="K43" t="s">
-        <v>755</v>
+        <v>738</v>
       </c>
       <c r="L43" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="M43" t="s">
         <v>368</v>
@@ -26211,13 +26328,13 @@
         <v>61</v>
       </c>
       <c r="T43" t="s">
-        <v>851</v>
+        <v>840</v>
       </c>
       <c r="U43" s="1">
-        <v>4118</v>
+        <v>3923.4</v>
       </c>
       <c r="V43" s="1">
-        <v>4117.8</v>
+        <v>3912.4</v>
       </c>
       <c r="W43" s="1">
         <v>0</v>
@@ -26232,25 +26349,25 @@
         <v>1228</v>
       </c>
       <c r="AA43" s="1">
-        <v>5056904</v>
+        <v>4817935.2</v>
       </c>
       <c r="AB43" s="1">
         <v>0</v>
       </c>
       <c r="AC43" s="1">
-        <v>5118664</v>
+        <v>4871156</v>
       </c>
       <c r="AD43" s="1">
-        <v>8850</v>
+        <v>0</v>
       </c>
       <c r="AE43" s="1">
-        <v>17700</v>
+        <v>25650</v>
       </c>
       <c r="AF43" t="s">
         <v>64</v>
       </c>
       <c r="AH43" t="s">
-        <v>852</v>
+        <v>841</v>
       </c>
       <c r="AI43" s="1">
         <v>0</v>
@@ -26268,19 +26385,19 @@
         <v>0</v>
       </c>
       <c r="AN43" s="1">
-        <v>61760</v>
+        <v>53220</v>
       </c>
       <c r="AO43" s="1">
-        <v>255934</v>
+        <v>243558</v>
       </c>
       <c r="AP43" s="1">
-        <v>61760</v>
+        <v>53220</v>
       </c>
       <c r="AQ43" s="1">
-        <v>5374598</v>
+        <v>5114714</v>
       </c>
       <c r="AR43" s="1">
-        <v>5401148</v>
+        <v>5140364</v>
       </c>
     </row>
     <row r="44" spans="1:44" x14ac:dyDescent="0.35">
@@ -26297,13 +26414,13 @@
         <v>48</v>
       </c>
       <c r="E44" t="s">
-        <v>853</v>
+        <v>842</v>
       </c>
       <c r="F44" t="s">
-        <v>854</v>
+        <v>742</v>
       </c>
       <c r="G44" t="s">
-        <v>855</v>
+        <v>843</v>
       </c>
       <c r="H44" t="s">
         <v>52</v>
@@ -26315,13 +26432,13 @@
         <v>54</v>
       </c>
       <c r="K44" t="s">
-        <v>761</v>
+        <v>744</v>
       </c>
       <c r="L44" t="s">
-        <v>854</v>
+        <v>742</v>
       </c>
       <c r="M44" t="s">
-        <v>212</v>
+        <v>368</v>
       </c>
       <c r="N44" t="s">
         <v>57</v>
@@ -26336,19 +26453,19 @@
         <v>60</v>
       </c>
       <c r="R44" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S44" t="s">
         <v>61</v>
       </c>
       <c r="T44" t="s">
-        <v>856</v>
+        <v>844</v>
       </c>
       <c r="U44" s="1">
-        <v>3792.2</v>
+        <v>3901.2</v>
       </c>
       <c r="V44" s="1">
-        <v>3785.7</v>
+        <v>3870.4</v>
       </c>
       <c r="W44" s="1">
         <v>0</v>
@@ -26363,25 +26480,25 @@
         <v>1228</v>
       </c>
       <c r="AA44" s="1">
-        <v>4656821.5999999996</v>
+        <v>4790673.5999999996</v>
       </c>
       <c r="AB44" s="1">
         <v>0</v>
       </c>
       <c r="AC44" s="1">
-        <v>4710042</v>
+        <v>4843894</v>
       </c>
       <c r="AD44" s="1">
         <v>0</v>
       </c>
       <c r="AE44" s="1">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="s">
         <v>64</v>
       </c>
       <c r="AH44" t="s">
-        <v>857</v>
+        <v>845</v>
       </c>
       <c r="AI44" s="1">
         <v>0</v>
@@ -26402,16 +26519,16 @@
         <v>53220</v>
       </c>
       <c r="AO44" s="1">
-        <v>235503</v>
+        <v>242195</v>
       </c>
       <c r="AP44" s="1">
         <v>53220</v>
       </c>
       <c r="AQ44" s="1">
-        <v>4945545</v>
+        <v>5086089</v>
       </c>
       <c r="AR44" s="1">
-        <v>4978545</v>
+        <v>5086089</v>
       </c>
     </row>
     <row r="45" spans="1:44" x14ac:dyDescent="0.35">
@@ -26428,13 +26545,13 @@
         <v>48</v>
       </c>
       <c r="E45" t="s">
-        <v>858</v>
+        <v>846</v>
       </c>
       <c r="F45" t="s">
-        <v>854</v>
+        <v>748</v>
       </c>
       <c r="G45" t="s">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="H45" t="s">
         <v>52</v>
@@ -26446,13 +26563,13 @@
         <v>54</v>
       </c>
       <c r="K45" t="s">
-        <v>767</v>
+        <v>750</v>
       </c>
       <c r="L45" t="s">
-        <v>854</v>
+        <v>748</v>
       </c>
       <c r="M45" t="s">
-        <v>368</v>
+        <v>212</v>
       </c>
       <c r="N45" t="s">
         <v>57</v>
@@ -26467,19 +26584,19 @@
         <v>60</v>
       </c>
       <c r="R45" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S45" t="s">
         <v>61</v>
       </c>
       <c r="T45" t="s">
-        <v>860</v>
+        <v>756</v>
       </c>
       <c r="U45" s="1">
-        <v>3916</v>
+        <v>3918.2</v>
       </c>
       <c r="V45" s="1">
-        <v>3896.8</v>
+        <v>3902.7</v>
       </c>
       <c r="W45" s="1">
         <v>0</v>
@@ -26494,25 +26611,25 @@
         <v>1228</v>
       </c>
       <c r="AA45" s="1">
-        <v>4808848</v>
+        <v>4811549.5999999996</v>
       </c>
       <c r="AB45" s="1">
         <v>0</v>
       </c>
       <c r="AC45" s="1">
-        <v>4862068</v>
+        <v>4864770</v>
       </c>
       <c r="AD45" s="1">
         <v>0</v>
       </c>
       <c r="AE45" s="1">
-        <v>42750</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="s">
         <v>64</v>
       </c>
       <c r="AH45" t="s">
-        <v>861</v>
+        <v>848</v>
       </c>
       <c r="AI45" s="1">
         <v>0</v>
@@ -26533,16 +26650,16 @@
         <v>53220</v>
       </c>
       <c r="AO45" s="1">
-        <v>243104</v>
+        <v>243239</v>
       </c>
       <c r="AP45" s="1">
         <v>53220</v>
       </c>
       <c r="AQ45" s="1">
-        <v>5105172</v>
+        <v>5108009</v>
       </c>
       <c r="AR45" s="1">
-        <v>5147922</v>
+        <v>5108009</v>
       </c>
     </row>
     <row r="46" spans="1:44" x14ac:dyDescent="0.35">
@@ -26559,13 +26676,13 @@
         <v>48</v>
       </c>
       <c r="E46" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="F46" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="G46" t="s">
-        <v>863</v>
+        <v>850</v>
       </c>
       <c r="H46" t="s">
         <v>52</v>
@@ -26577,10 +26694,10 @@
         <v>54</v>
       </c>
       <c r="K46" t="s">
-        <v>773</v>
+        <v>755</v>
       </c>
       <c r="L46" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="M46" t="s">
         <v>368</v>
@@ -26604,13 +26721,13 @@
         <v>61</v>
       </c>
       <c r="T46" t="s">
-        <v>864</v>
+        <v>851</v>
       </c>
       <c r="U46" s="1">
-        <v>3994.8</v>
+        <v>4118</v>
       </c>
       <c r="V46" s="1">
-        <v>3985.6</v>
+        <v>4117.8</v>
       </c>
       <c r="W46" s="1">
         <v>0</v>
@@ -26625,25 +26742,25 @@
         <v>1228</v>
       </c>
       <c r="AA46" s="1">
-        <v>4905614.4000000004</v>
+        <v>5056904</v>
       </c>
       <c r="AB46" s="1">
         <v>0</v>
       </c>
       <c r="AC46" s="1">
-        <v>4958835</v>
+        <v>5118664</v>
       </c>
       <c r="AD46" s="1">
-        <v>0</v>
+        <v>8850</v>
       </c>
       <c r="AE46" s="1">
-        <v>71340</v>
+        <v>17700</v>
       </c>
       <c r="AF46" t="s">
         <v>64</v>
       </c>
       <c r="AH46" t="s">
-        <v>865</v>
+        <v>852</v>
       </c>
       <c r="AI46" s="1">
         <v>0</v>
@@ -26661,19 +26778,19 @@
         <v>0</v>
       </c>
       <c r="AN46" s="1">
-        <v>53220</v>
+        <v>61760</v>
       </c>
       <c r="AO46" s="1">
-        <v>247942</v>
+        <v>255934</v>
       </c>
       <c r="AP46" s="1">
-        <v>53220</v>
+        <v>61760</v>
       </c>
       <c r="AQ46" s="1">
-        <v>5206777</v>
+        <v>5374598</v>
       </c>
       <c r="AR46" s="1">
-        <v>5278117</v>
+        <v>5401148</v>
       </c>
     </row>
     <row r="47" spans="1:44" x14ac:dyDescent="0.35">
@@ -26690,13 +26807,13 @@
         <v>48</v>
       </c>
       <c r="E47" t="s">
-        <v>866</v>
+        <v>853</v>
       </c>
       <c r="F47" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
       <c r="G47" t="s">
-        <v>868</v>
+        <v>855</v>
       </c>
       <c r="H47" t="s">
         <v>52</v>
@@ -26708,13 +26825,13 @@
         <v>54</v>
       </c>
       <c r="K47" t="s">
-        <v>869</v>
+        <v>761</v>
       </c>
       <c r="L47" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
       <c r="M47" t="s">
-        <v>368</v>
+        <v>212</v>
       </c>
       <c r="N47" t="s">
         <v>57</v>
@@ -26729,19 +26846,19 @@
         <v>60</v>
       </c>
       <c r="R47" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="S47" t="s">
         <v>61</v>
       </c>
       <c r="T47" t="s">
-        <v>870</v>
+        <v>856</v>
       </c>
       <c r="U47" s="1">
-        <v>3697.2</v>
+        <v>3792.2</v>
       </c>
       <c r="V47" s="1">
-        <v>3667.5</v>
+        <v>3785.7</v>
       </c>
       <c r="W47" s="1">
         <v>0</v>
@@ -26756,25 +26873,25 @@
         <v>1228</v>
       </c>
       <c r="AA47" s="1">
-        <v>4540161.5999999996</v>
+        <v>4656821.5999999996</v>
       </c>
       <c r="AB47" s="1">
         <v>0</v>
       </c>
       <c r="AC47" s="1">
-        <v>4628862</v>
+        <v>4710042</v>
       </c>
       <c r="AD47" s="1">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="AE47" s="1">
-        <v>40500</v>
+        <v>33000</v>
       </c>
       <c r="AF47" t="s">
         <v>64</v>
       </c>
       <c r="AH47" t="s">
-        <v>871</v>
+        <v>857</v>
       </c>
       <c r="AI47" s="1">
         <v>0</v>
@@ -26792,19 +26909,19 @@
         <v>0</v>
       </c>
       <c r="AN47" s="1">
-        <v>88700</v>
+        <v>53220</v>
       </c>
       <c r="AO47" s="1">
-        <v>231444</v>
+        <v>235503</v>
       </c>
       <c r="AP47" s="1">
-        <v>88700</v>
+        <v>53220</v>
       </c>
       <c r="AQ47" s="1">
-        <v>4860306</v>
+        <v>4945545</v>
       </c>
       <c r="AR47" s="1">
-        <v>4917006</v>
+        <v>4978545</v>
       </c>
     </row>
     <row r="48" spans="1:44" x14ac:dyDescent="0.35">
@@ -26821,13 +26938,13 @@
         <v>48</v>
       </c>
       <c r="E48" t="s">
-        <v>872</v>
+        <v>858</v>
       </c>
       <c r="F48" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
       <c r="G48" t="s">
-        <v>873</v>
+        <v>859</v>
       </c>
       <c r="H48" t="s">
         <v>52</v>
@@ -26839,10 +26956,10 @@
         <v>54</v>
       </c>
       <c r="K48" t="s">
-        <v>874</v>
+        <v>767</v>
       </c>
       <c r="L48" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
       <c r="M48" t="s">
         <v>368</v>
@@ -26860,19 +26977,19 @@
         <v>60</v>
       </c>
       <c r="R48" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="S48" t="s">
         <v>61</v>
       </c>
       <c r="T48" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="U48" s="1">
-        <v>3585</v>
+        <v>3916</v>
       </c>
       <c r="V48" s="1">
-        <v>3576.4</v>
+        <v>3896.8</v>
       </c>
       <c r="W48" s="1">
         <v>0</v>
@@ -26887,25 +27004,25 @@
         <v>1228</v>
       </c>
       <c r="AA48" s="1">
-        <v>4402380</v>
+        <v>4808848</v>
       </c>
       <c r="AB48" s="1">
         <v>0</v>
       </c>
       <c r="AC48" s="1">
-        <v>4455600</v>
+        <v>4862068</v>
       </c>
       <c r="AD48" s="1">
         <v>0</v>
       </c>
       <c r="AE48" s="1">
-        <v>15600</v>
+        <v>42750</v>
       </c>
       <c r="AF48" t="s">
         <v>64</v>
       </c>
       <c r="AH48" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="AI48" s="1">
         <v>0</v>
@@ -26926,16 +27043,16 @@
         <v>53220</v>
       </c>
       <c r="AO48" s="1">
-        <v>222780</v>
+        <v>243104</v>
       </c>
       <c r="AP48" s="1">
         <v>53220</v>
       </c>
       <c r="AQ48" s="1">
-        <v>4678380</v>
+        <v>5105172</v>
       </c>
       <c r="AR48" s="1">
-        <v>4693980</v>
+        <v>5147922</v>
       </c>
     </row>
     <row r="49" spans="1:44" x14ac:dyDescent="0.35">
@@ -26952,13 +27069,13 @@
         <v>48</v>
       </c>
       <c r="E49" t="s">
-        <v>877</v>
+        <v>862</v>
       </c>
       <c r="F49" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="G49" t="s">
-        <v>878</v>
+        <v>863</v>
       </c>
       <c r="H49" t="s">
         <v>52</v>
@@ -26970,10 +27087,10 @@
         <v>54</v>
       </c>
       <c r="K49" t="s">
-        <v>879</v>
+        <v>773</v>
       </c>
       <c r="L49" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="M49" t="s">
         <v>368</v>
@@ -26997,13 +27114,13 @@
         <v>61</v>
       </c>
       <c r="T49" t="s">
-        <v>880</v>
+        <v>864</v>
       </c>
       <c r="U49" s="1">
-        <v>3780.2</v>
+        <v>3994.8</v>
       </c>
       <c r="V49" s="1">
-        <v>3765.2</v>
+        <v>3985.6</v>
       </c>
       <c r="W49" s="1">
         <v>0</v>
@@ -27018,25 +27135,25 @@
         <v>1228</v>
       </c>
       <c r="AA49" s="1">
-        <v>4642085.5999999996</v>
+        <v>4905614.4000000004</v>
       </c>
       <c r="AB49" s="1">
         <v>0</v>
       </c>
       <c r="AC49" s="1">
-        <v>4695306</v>
+        <v>4958835</v>
       </c>
       <c r="AD49" s="1">
         <v>0</v>
       </c>
       <c r="AE49" s="1">
-        <v>41250</v>
+        <v>71340</v>
       </c>
       <c r="AF49" t="s">
         <v>64</v>
       </c>
       <c r="AH49" t="s">
-        <v>881</v>
+        <v>865</v>
       </c>
       <c r="AI49" s="1">
         <v>0</v>
@@ -27057,16 +27174,16 @@
         <v>53220</v>
       </c>
       <c r="AO49" s="1">
-        <v>234766</v>
+        <v>247942</v>
       </c>
       <c r="AP49" s="1">
         <v>53220</v>
       </c>
       <c r="AQ49" s="1">
-        <v>4930072</v>
+        <v>5206777</v>
       </c>
       <c r="AR49" s="1">
-        <v>4971322</v>
+        <v>5278117</v>
       </c>
     </row>
     <row r="50" spans="1:44" x14ac:dyDescent="0.35">
@@ -27083,13 +27200,13 @@
         <v>48</v>
       </c>
       <c r="E50" t="s">
-        <v>882</v>
+        <v>866</v>
       </c>
       <c r="F50" t="s">
-        <v>765</v>
+        <v>867</v>
       </c>
       <c r="G50" t="s">
-        <v>883</v>
+        <v>868</v>
       </c>
       <c r="H50" t="s">
         <v>52</v>
@@ -27101,10 +27218,10 @@
         <v>54</v>
       </c>
       <c r="K50" t="s">
-        <v>884</v>
+        <v>869</v>
       </c>
       <c r="L50" t="s">
-        <v>765</v>
+        <v>867</v>
       </c>
       <c r="M50" t="s">
         <v>368</v>
@@ -27128,13 +27245,13 @@
         <v>61</v>
       </c>
       <c r="T50" t="s">
-        <v>768</v>
+        <v>870</v>
       </c>
       <c r="U50" s="1">
-        <v>3515.2</v>
+        <v>3697.2</v>
       </c>
       <c r="V50" s="1">
-        <v>3502.2</v>
+        <v>3667.5</v>
       </c>
       <c r="W50" s="1">
         <v>0</v>
@@ -27149,25 +27266,25 @@
         <v>1228</v>
       </c>
       <c r="AA50" s="1">
-        <v>4316665.5999999996</v>
+        <v>4540161.5999999996</v>
       </c>
       <c r="AB50" s="1">
         <v>0</v>
       </c>
       <c r="AC50" s="1">
-        <v>4369886</v>
+        <v>4628862</v>
       </c>
       <c r="AD50" s="1">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="AE50" s="1">
-        <v>45900</v>
+        <v>40500</v>
       </c>
       <c r="AF50" t="s">
         <v>64</v>
       </c>
       <c r="AH50" t="s">
-        <v>885</v>
+        <v>871</v>
       </c>
       <c r="AI50" s="1">
         <v>0</v>
@@ -27185,19 +27302,19 @@
         <v>0</v>
       </c>
       <c r="AN50" s="1">
-        <v>53220</v>
+        <v>88700</v>
       </c>
       <c r="AO50" s="1">
-        <v>218495</v>
+        <v>231444</v>
       </c>
       <c r="AP50" s="1">
-        <v>53220</v>
+        <v>88700</v>
       </c>
       <c r="AQ50" s="1">
-        <v>4588381</v>
+        <v>4860306</v>
       </c>
       <c r="AR50" s="1">
-        <v>4634281</v>
+        <v>4917006</v>
       </c>
     </row>
     <row r="51" spans="1:44" x14ac:dyDescent="0.35">
@@ -27214,13 +27331,13 @@
         <v>48</v>
       </c>
       <c r="E51" t="s">
-        <v>886</v>
+        <v>872</v>
       </c>
       <c r="F51" t="s">
-        <v>771</v>
+        <v>867</v>
       </c>
       <c r="G51" t="s">
-        <v>887</v>
+        <v>873</v>
       </c>
       <c r="H51" t="s">
         <v>52</v>
@@ -27232,10 +27349,10 @@
         <v>54</v>
       </c>
       <c r="K51" t="s">
-        <v>888</v>
+        <v>874</v>
       </c>
       <c r="L51" t="s">
-        <v>771</v>
+        <v>867</v>
       </c>
       <c r="M51" t="s">
         <v>368</v>
@@ -27259,13 +27376,13 @@
         <v>61</v>
       </c>
       <c r="T51" t="s">
-        <v>889</v>
+        <v>875</v>
       </c>
       <c r="U51" s="1">
-        <v>3708.2</v>
+        <v>3585</v>
       </c>
       <c r="V51" s="1">
-        <v>3691</v>
+        <v>3576.4</v>
       </c>
       <c r="W51" s="1">
         <v>0</v>
@@ -27280,25 +27397,25 @@
         <v>1228</v>
       </c>
       <c r="AA51" s="1">
-        <v>4553669.5999999996</v>
+        <v>4402380</v>
       </c>
       <c r="AB51" s="1">
         <v>0</v>
       </c>
       <c r="AC51" s="1">
-        <v>4606890</v>
+        <v>4455600</v>
       </c>
       <c r="AD51" s="1">
         <v>0</v>
       </c>
       <c r="AE51" s="1">
-        <v>0</v>
+        <v>15600</v>
       </c>
       <c r="AF51" t="s">
         <v>64</v>
       </c>
       <c r="AH51" t="s">
-        <v>890</v>
+        <v>876</v>
       </c>
       <c r="AI51" s="1">
         <v>0</v>
@@ -27319,16 +27436,16 @@
         <v>53220</v>
       </c>
       <c r="AO51" s="1">
-        <v>230345</v>
+        <v>222780</v>
       </c>
       <c r="AP51" s="1">
         <v>53220</v>
       </c>
       <c r="AQ51" s="1">
-        <v>4837235</v>
+        <v>4678380</v>
       </c>
       <c r="AR51" s="1">
-        <v>4837235</v>
+        <v>4693980</v>
       </c>
     </row>
     <row r="52" spans="1:44" x14ac:dyDescent="0.35">
@@ -27345,13 +27462,13 @@
         <v>48</v>
       </c>
       <c r="E52" t="s">
-        <v>891</v>
+        <v>877</v>
       </c>
       <c r="F52" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="G52" t="s">
-        <v>892</v>
+        <v>878</v>
       </c>
       <c r="H52" t="s">
         <v>52</v>
@@ -27363,13 +27480,13 @@
         <v>54</v>
       </c>
       <c r="K52" t="s">
-        <v>893</v>
+        <v>879</v>
       </c>
       <c r="L52" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="M52" t="s">
-        <v>56</v>
+        <v>368</v>
       </c>
       <c r="N52" t="s">
         <v>57</v>
@@ -27390,13 +27507,13 @@
         <v>61</v>
       </c>
       <c r="T52" t="s">
-        <v>894</v>
+        <v>880</v>
       </c>
       <c r="U52" s="1">
-        <v>3922.2</v>
+        <v>3780.2</v>
       </c>
       <c r="V52" s="1">
-        <v>3906</v>
+        <v>3765.2</v>
       </c>
       <c r="W52" s="1">
         <v>0</v>
@@ -27411,25 +27528,25 @@
         <v>1228</v>
       </c>
       <c r="AA52" s="1">
-        <v>4816461.5999999996</v>
+        <v>4642085.5999999996</v>
       </c>
       <c r="AB52" s="1">
         <v>0</v>
       </c>
       <c r="AC52" s="1">
-        <v>4905162</v>
+        <v>4695306</v>
       </c>
       <c r="AD52" s="1">
-        <v>17100</v>
+        <v>0</v>
       </c>
       <c r="AE52" s="1">
-        <v>129105</v>
+        <v>41250</v>
       </c>
       <c r="AF52" t="s">
         <v>64</v>
       </c>
       <c r="AH52" t="s">
-        <v>895</v>
+        <v>881</v>
       </c>
       <c r="AI52" s="1">
         <v>0</v>
@@ -27447,19 +27564,19 @@
         <v>0</v>
       </c>
       <c r="AN52" s="1">
-        <v>88700</v>
+        <v>53220</v>
       </c>
       <c r="AO52" s="1">
-        <v>245259</v>
+        <v>234766</v>
       </c>
       <c r="AP52" s="1">
-        <v>88700</v>
+        <v>53220</v>
       </c>
       <c r="AQ52" s="1">
-        <v>5150421</v>
+        <v>4930072</v>
       </c>
       <c r="AR52" s="1">
-        <v>5296626</v>
+        <v>4971322</v>
       </c>
     </row>
     <row r="53" spans="1:44" x14ac:dyDescent="0.35">
@@ -27476,13 +27593,13 @@
         <v>48</v>
       </c>
       <c r="E53" t="s">
-        <v>896</v>
+        <v>882</v>
       </c>
       <c r="F53" t="s">
-        <v>897</v>
+        <v>765</v>
       </c>
       <c r="G53" t="s">
-        <v>898</v>
+        <v>883</v>
       </c>
       <c r="H53" t="s">
         <v>52</v>
@@ -27494,13 +27611,13 @@
         <v>54</v>
       </c>
       <c r="K53" t="s">
-        <v>899</v>
+        <v>884</v>
       </c>
       <c r="L53" t="s">
-        <v>897</v>
+        <v>765</v>
       </c>
       <c r="M53" t="s">
-        <v>56</v>
+        <v>368</v>
       </c>
       <c r="N53" t="s">
         <v>57</v>
@@ -27521,13 +27638,13 @@
         <v>61</v>
       </c>
       <c r="T53" t="s">
-        <v>900</v>
+        <v>768</v>
       </c>
       <c r="U53" s="1">
-        <v>3899.8</v>
+        <v>3515.2</v>
       </c>
       <c r="V53" s="1">
-        <v>3879.3</v>
+        <v>3502.2</v>
       </c>
       <c r="W53" s="1">
         <v>0</v>
@@ -27542,25 +27659,25 @@
         <v>1228</v>
       </c>
       <c r="AA53" s="1">
-        <v>4788954.4000000004</v>
+        <v>4316665.5999999996</v>
       </c>
       <c r="AB53" s="1">
         <v>0</v>
       </c>
       <c r="AC53" s="1">
-        <v>4895395</v>
+        <v>4369886</v>
       </c>
       <c r="AD53" s="1">
-        <v>25200</v>
+        <v>0</v>
       </c>
       <c r="AE53" s="1">
-        <v>33600</v>
+        <v>45900</v>
       </c>
       <c r="AF53" t="s">
         <v>64</v>
       </c>
       <c r="AH53" t="s">
-        <v>901</v>
+        <v>885</v>
       </c>
       <c r="AI53" s="1">
         <v>0</v>
@@ -27578,19 +27695,19 @@
         <v>0</v>
       </c>
       <c r="AN53" s="1">
-        <v>106440</v>
+        <v>53220</v>
       </c>
       <c r="AO53" s="1">
-        <v>244770</v>
+        <v>218495</v>
       </c>
       <c r="AP53" s="1">
-        <v>106440</v>
+        <v>53220</v>
       </c>
       <c r="AQ53" s="1">
-        <v>5140165</v>
+        <v>4588381</v>
       </c>
       <c r="AR53" s="1">
-        <v>5198965</v>
+        <v>4634281</v>
       </c>
     </row>
     <row r="54" spans="1:44" x14ac:dyDescent="0.35">
@@ -27607,13 +27724,13 @@
         <v>48</v>
       </c>
       <c r="E54" t="s">
-        <v>902</v>
+        <v>886</v>
       </c>
       <c r="F54" t="s">
-        <v>903</v>
+        <v>771</v>
       </c>
       <c r="G54" t="s">
-        <v>904</v>
+        <v>887</v>
       </c>
       <c r="H54" t="s">
         <v>52</v>
@@ -27625,13 +27742,13 @@
         <v>54</v>
       </c>
       <c r="K54" t="s">
-        <v>905</v>
+        <v>888</v>
       </c>
       <c r="L54" t="s">
-        <v>903</v>
+        <v>771</v>
       </c>
       <c r="M54" t="s">
-        <v>56</v>
+        <v>368</v>
       </c>
       <c r="N54" t="s">
         <v>57</v>
@@ -27652,13 +27769,13 @@
         <v>61</v>
       </c>
       <c r="T54" t="s">
-        <v>906</v>
+        <v>889</v>
       </c>
       <c r="U54" s="1">
-        <v>4118.8</v>
+        <v>3708.2</v>
       </c>
       <c r="V54" s="1">
-        <v>4105.3</v>
+        <v>3691</v>
       </c>
       <c r="W54" s="1">
         <v>0</v>
@@ -27673,25 +27790,25 @@
         <v>1228</v>
       </c>
       <c r="AA54" s="1">
-        <v>5057886.4000000004</v>
+        <v>4553669.5999999996</v>
       </c>
       <c r="AB54" s="1">
         <v>0</v>
       </c>
       <c r="AC54" s="1">
-        <v>5253027</v>
+        <v>4606890</v>
       </c>
       <c r="AD54" s="1">
-        <v>72570</v>
+        <v>0</v>
       </c>
       <c r="AE54" s="1">
-        <v>26550</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="s">
         <v>64</v>
       </c>
       <c r="AH54" t="s">
-        <v>907</v>
+        <v>890</v>
       </c>
       <c r="AI54" s="1">
         <v>0</v>
@@ -27709,19 +27826,19 @@
         <v>0</v>
       </c>
       <c r="AN54" s="1">
-        <v>195140</v>
+        <v>53220</v>
       </c>
       <c r="AO54" s="1">
-        <v>262652</v>
+        <v>230345</v>
       </c>
       <c r="AP54" s="1">
-        <v>195140</v>
+        <v>53220</v>
       </c>
       <c r="AQ54" s="1">
-        <v>5515679</v>
+        <v>4837235</v>
       </c>
       <c r="AR54" s="1">
-        <v>5614799</v>
+        <v>4837235</v>
       </c>
     </row>
     <row r="55" spans="1:44" x14ac:dyDescent="0.35">
@@ -27738,13 +27855,13 @@
         <v>48</v>
       </c>
       <c r="E55" t="s">
-        <v>908</v>
+        <v>891</v>
       </c>
       <c r="F55" t="s">
-        <v>909</v>
+        <v>771</v>
       </c>
       <c r="G55" t="s">
-        <v>910</v>
+        <v>892</v>
       </c>
       <c r="H55" t="s">
         <v>52</v>
@@ -27756,10 +27873,10 @@
         <v>54</v>
       </c>
       <c r="K55" t="s">
-        <v>911</v>
+        <v>893</v>
       </c>
       <c r="L55" t="s">
-        <v>909</v>
+        <v>771</v>
       </c>
       <c r="M55" t="s">
         <v>56</v>
@@ -27783,13 +27900,13 @@
         <v>61</v>
       </c>
       <c r="T55" t="s">
-        <v>912</v>
+        <v>894</v>
       </c>
       <c r="U55" s="1">
-        <v>3908.8</v>
+        <v>3922.2</v>
       </c>
       <c r="V55" s="1">
-        <v>3894.4</v>
+        <v>3906</v>
       </c>
       <c r="W55" s="1">
         <v>0</v>
@@ -27804,25 +27921,25 @@
         <v>1228</v>
       </c>
       <c r="AA55" s="1">
-        <v>4800006.4000000004</v>
+        <v>4816461.5999999996</v>
       </c>
       <c r="AB55" s="1">
         <v>0</v>
       </c>
       <c r="AC55" s="1">
-        <v>4870967</v>
+        <v>4905162</v>
       </c>
       <c r="AD55" s="1">
-        <v>0</v>
+        <v>17100</v>
       </c>
       <c r="AE55" s="1">
-        <v>59640</v>
+        <v>129105</v>
       </c>
       <c r="AF55" t="s">
         <v>64</v>
       </c>
       <c r="AH55" t="s">
-        <v>913</v>
+        <v>895</v>
       </c>
       <c r="AI55" s="1">
         <v>0</v>
@@ -27840,19 +27957,19 @@
         <v>0</v>
       </c>
       <c r="AN55" s="1">
-        <v>70960</v>
+        <v>88700</v>
       </c>
       <c r="AO55" s="1">
-        <v>243549</v>
+        <v>245259</v>
       </c>
       <c r="AP55" s="1">
-        <v>70960</v>
+        <v>88700</v>
       </c>
       <c r="AQ55" s="1">
-        <v>5114516</v>
+        <v>5150421</v>
       </c>
       <c r="AR55" s="1">
-        <v>5174156</v>
+        <v>5296626</v>
       </c>
     </row>
     <row r="56" spans="1:44" x14ac:dyDescent="0.35">
@@ -27863,19 +27980,19 @@
         <v>46</v>
       </c>
       <c r="C56" t="s">
-        <v>506</v>
+        <v>357</v>
       </c>
       <c r="D56" t="s">
         <v>48</v>
       </c>
       <c r="E56" t="s">
-        <v>914</v>
+        <v>896</v>
       </c>
       <c r="F56" t="s">
-        <v>680</v>
+        <v>897</v>
       </c>
       <c r="G56" t="s">
-        <v>915</v>
+        <v>898</v>
       </c>
       <c r="H56" t="s">
         <v>52</v>
@@ -27887,10 +28004,10 @@
         <v>54</v>
       </c>
       <c r="K56" t="s">
-        <v>222</v>
+        <v>899</v>
       </c>
       <c r="L56" t="s">
-        <v>680</v>
+        <v>897</v>
       </c>
       <c r="M56" t="s">
         <v>56</v>
@@ -27902,28 +28019,28 @@
         <v>58</v>
       </c>
       <c r="P56" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="Q56" t="s">
         <v>60</v>
       </c>
       <c r="R56" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S56" t="s">
         <v>61</v>
       </c>
       <c r="T56" t="s">
-        <v>916</v>
+        <v>900</v>
       </c>
       <c r="U56" s="1">
-        <v>3803.8</v>
+        <v>3899.8</v>
       </c>
       <c r="V56" s="1">
-        <v>3754.2</v>
+        <v>3879.3</v>
       </c>
       <c r="W56" s="1">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="X56" s="1">
         <v>0</v>
@@ -27935,55 +28052,55 @@
         <v>1228</v>
       </c>
       <c r="AA56" s="1">
-        <v>4671066.4000000004</v>
+        <v>4788954.4000000004</v>
       </c>
       <c r="AB56" s="1">
-        <v>15227.2</v>
+        <v>0</v>
       </c>
       <c r="AC56" s="1">
-        <v>4807354</v>
+        <v>4895395</v>
       </c>
       <c r="AD56" s="1">
-        <v>24750</v>
+        <v>25200</v>
       </c>
       <c r="AE56" s="1">
-        <v>0</v>
+        <v>33600</v>
       </c>
       <c r="AF56" t="s">
         <v>64</v>
       </c>
       <c r="AH56" t="s">
-        <v>917</v>
+        <v>901</v>
       </c>
       <c r="AI56" s="1">
-        <v>16500</v>
+        <v>0</v>
       </c>
       <c r="AJ56" s="1">
-        <v>30880</v>
+        <v>0</v>
       </c>
       <c r="AK56" s="1">
-        <v>73680</v>
+        <v>0</v>
       </c>
       <c r="AL56" s="1">
-        <v>15227.2</v>
+        <v>0</v>
       </c>
       <c r="AM56" s="1">
         <v>0</v>
       </c>
       <c r="AN56" s="1">
-        <v>0</v>
+        <v>106440</v>
       </c>
       <c r="AO56" s="1">
-        <v>240368</v>
+        <v>244770</v>
       </c>
       <c r="AP56" s="1">
-        <v>136287.20000000001</v>
+        <v>106440</v>
       </c>
       <c r="AQ56" s="1">
-        <v>5047722</v>
+        <v>5140165</v>
       </c>
       <c r="AR56" s="1">
-        <v>5072472</v>
+        <v>5198965</v>
       </c>
     </row>
     <row r="57" spans="1:44" x14ac:dyDescent="0.35">
@@ -27994,19 +28111,19 @@
         <v>46</v>
       </c>
       <c r="C57" t="s">
-        <v>506</v>
+        <v>357</v>
       </c>
       <c r="D57" t="s">
         <v>48</v>
       </c>
       <c r="E57" t="s">
-        <v>918</v>
+        <v>902</v>
       </c>
       <c r="F57" t="s">
-        <v>686</v>
+        <v>903</v>
       </c>
       <c r="G57" t="s">
-        <v>919</v>
+        <v>904</v>
       </c>
       <c r="H57" t="s">
         <v>52</v>
@@ -28018,13 +28135,13 @@
         <v>54</v>
       </c>
       <c r="K57" t="s">
-        <v>227</v>
+        <v>905</v>
       </c>
       <c r="L57" t="s">
-        <v>686</v>
+        <v>903</v>
       </c>
       <c r="M57" t="s">
-        <v>212</v>
+        <v>56</v>
       </c>
       <c r="N57" t="s">
         <v>57</v>
@@ -28033,7 +28150,7 @@
         <v>58</v>
       </c>
       <c r="P57" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="Q57" t="s">
         <v>60</v>
@@ -28045,16 +28162,16 @@
         <v>61</v>
       </c>
       <c r="T57" t="s">
-        <v>920</v>
+        <v>906</v>
       </c>
       <c r="U57" s="1">
-        <v>3999.2</v>
+        <v>4118.8</v>
       </c>
       <c r="V57" s="1">
-        <v>3885</v>
+        <v>4105.3</v>
       </c>
       <c r="W57" s="1">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="X57" s="1">
         <v>0</v>
@@ -28066,55 +28183,55 @@
         <v>1228</v>
       </c>
       <c r="AA57" s="1">
-        <v>4911017.5999999996</v>
+        <v>5057886.4000000004</v>
       </c>
       <c r="AB57" s="1">
-        <v>13753.6</v>
+        <v>0</v>
       </c>
       <c r="AC57" s="1">
-        <v>5007136</v>
+        <v>5253027</v>
       </c>
       <c r="AD57" s="1">
-        <v>8550</v>
+        <v>72570</v>
       </c>
       <c r="AE57" s="1">
-        <v>42750</v>
+        <v>26550</v>
       </c>
       <c r="AF57" t="s">
         <v>64</v>
       </c>
       <c r="AH57" t="s">
-        <v>921</v>
+        <v>907</v>
       </c>
       <c r="AI57" s="1">
-        <v>17100</v>
+        <v>0</v>
       </c>
       <c r="AJ57" s="1">
-        <v>30880</v>
+        <v>0</v>
       </c>
       <c r="AK57" s="1">
-        <v>34384</v>
+        <v>0</v>
       </c>
       <c r="AL57" s="1">
-        <v>13753.6</v>
+        <v>0</v>
       </c>
       <c r="AM57" s="1">
         <v>0</v>
       </c>
       <c r="AN57" s="1">
-        <v>0</v>
+        <v>195140</v>
       </c>
       <c r="AO57" s="1">
-        <v>250357</v>
+        <v>262652</v>
       </c>
       <c r="AP57" s="1">
-        <v>96117.6</v>
+        <v>195140</v>
       </c>
       <c r="AQ57" s="1">
-        <v>5257493</v>
+        <v>5515679</v>
       </c>
       <c r="AR57" s="1">
-        <v>5308793</v>
+        <v>5614799</v>
       </c>
     </row>
     <row r="58" spans="1:44" x14ac:dyDescent="0.35">
@@ -28125,19 +28242,19 @@
         <v>46</v>
       </c>
       <c r="C58" t="s">
-        <v>506</v>
+        <v>357</v>
       </c>
       <c r="D58" t="s">
         <v>48</v>
       </c>
       <c r="E58" t="s">
-        <v>922</v>
+        <v>908</v>
       </c>
       <c r="F58" t="s">
-        <v>708</v>
+        <v>909</v>
       </c>
       <c r="G58" t="s">
-        <v>923</v>
+        <v>910</v>
       </c>
       <c r="H58" t="s">
         <v>52</v>
@@ -28149,13 +28266,13 @@
         <v>54</v>
       </c>
       <c r="K58" t="s">
-        <v>232</v>
+        <v>911</v>
       </c>
       <c r="L58" t="s">
-        <v>708</v>
+        <v>909</v>
       </c>
       <c r="M58" t="s">
-        <v>212</v>
+        <v>56</v>
       </c>
       <c r="N58" t="s">
         <v>57</v>
@@ -28164,7 +28281,7 @@
         <v>58</v>
       </c>
       <c r="P58" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="Q58" t="s">
         <v>60</v>
@@ -28176,16 +28293,16 @@
         <v>61</v>
       </c>
       <c r="T58" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
       <c r="U58" s="1">
-        <v>3957.4</v>
+        <v>3908.8</v>
       </c>
       <c r="V58" s="1">
-        <v>3934</v>
+        <v>3894.4</v>
       </c>
       <c r="W58" s="1">
-        <v>17.8</v>
+        <v>0</v>
       </c>
       <c r="X58" s="1">
         <v>0</v>
@@ -28197,55 +28314,55 @@
         <v>1228</v>
       </c>
       <c r="AA58" s="1">
-        <v>4859687.2</v>
+        <v>4800006.4000000004</v>
       </c>
       <c r="AB58" s="1">
-        <v>65575.199999999997</v>
+        <v>0</v>
       </c>
       <c r="AC58" s="1">
-        <v>5269371</v>
+        <v>4870967</v>
       </c>
       <c r="AD58" s="1">
-        <v>17100</v>
+        <v>0</v>
       </c>
       <c r="AE58" s="1">
-        <v>79515</v>
+        <v>59640</v>
       </c>
       <c r="AF58" t="s">
         <v>64</v>
       </c>
       <c r="AH58" t="s">
-        <v>925</v>
+        <v>913</v>
       </c>
       <c r="AI58" s="1">
-        <v>17100</v>
+        <v>0</v>
       </c>
       <c r="AJ58" s="1">
-        <v>61760</v>
+        <v>0</v>
       </c>
       <c r="AK58" s="1">
-        <v>265248</v>
+        <v>0</v>
       </c>
       <c r="AL58" s="1">
-        <v>65575.199999999997</v>
+        <v>0</v>
       </c>
       <c r="AM58" s="1">
         <v>0</v>
       </c>
       <c r="AN58" s="1">
-        <v>0</v>
+        <v>70960</v>
       </c>
       <c r="AO58" s="1">
-        <v>263469</v>
+        <v>243549</v>
       </c>
       <c r="AP58" s="1">
-        <v>409683.20000000001</v>
+        <v>70960</v>
       </c>
       <c r="AQ58" s="1">
-        <v>5532840</v>
+        <v>5114516</v>
       </c>
       <c r="AR58" s="1">
-        <v>5629455</v>
+        <v>5174156</v>
       </c>
     </row>
     <row r="59" spans="1:44" x14ac:dyDescent="0.35">
@@ -28256,19 +28373,19 @@
         <v>46</v>
       </c>
       <c r="C59" t="s">
-        <v>506</v>
+        <v>357</v>
       </c>
       <c r="D59" t="s">
         <v>48</v>
       </c>
       <c r="E59" t="s">
-        <v>926</v>
+        <v>1022</v>
       </c>
       <c r="F59" t="s">
-        <v>719</v>
+        <v>1023</v>
       </c>
       <c r="G59" t="s">
-        <v>927</v>
+        <v>1024</v>
       </c>
       <c r="H59" t="s">
         <v>52</v>
@@ -28280,13 +28397,13 @@
         <v>54</v>
       </c>
       <c r="K59" t="s">
-        <v>237</v>
+        <v>1025</v>
       </c>
       <c r="L59" t="s">
-        <v>719</v>
+        <v>1023</v>
       </c>
       <c r="M59" t="s">
-        <v>212</v>
+        <v>368</v>
       </c>
       <c r="N59" t="s">
         <v>57</v>
@@ -28295,7 +28412,7 @@
         <v>58</v>
       </c>
       <c r="P59" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="Q59" t="s">
         <v>60</v>
@@ -28307,16 +28424,16 @@
         <v>61</v>
       </c>
       <c r="T59" t="s">
-        <v>928</v>
+        <v>1026</v>
       </c>
       <c r="U59" s="1">
-        <v>3753.6</v>
+        <v>3973.4</v>
       </c>
       <c r="V59" s="1">
-        <v>3737.7</v>
+        <v>3952.4</v>
       </c>
       <c r="W59" s="1">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="X59" s="1">
         <v>0</v>
@@ -28328,55 +28445,55 @@
         <v>1228</v>
       </c>
       <c r="AA59" s="1">
-        <v>4609420.8</v>
+        <v>4879335.2</v>
       </c>
       <c r="AB59" s="1">
-        <v>95784</v>
+        <v>0</v>
       </c>
       <c r="AC59" s="1">
-        <v>4884909</v>
+        <v>5003516</v>
       </c>
       <c r="AD59" s="1">
-        <v>40500</v>
+        <v>34200</v>
       </c>
       <c r="AE59" s="1">
-        <v>24300</v>
+        <v>214605</v>
       </c>
       <c r="AF59" t="s">
         <v>64</v>
       </c>
       <c r="AH59" t="s">
-        <v>929</v>
+        <v>1027</v>
       </c>
       <c r="AI59" s="1">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="AJ59" s="1">
-        <v>30880</v>
+        <v>0</v>
       </c>
       <c r="AK59" s="1">
-        <v>132624</v>
+        <v>0</v>
       </c>
       <c r="AL59" s="1">
-        <v>95784</v>
+        <v>0</v>
       </c>
       <c r="AM59" s="1">
         <v>0</v>
       </c>
       <c r="AN59" s="1">
-        <v>0</v>
+        <v>124180</v>
       </c>
       <c r="AO59" s="1">
-        <v>244246</v>
+        <v>250176</v>
       </c>
       <c r="AP59" s="1">
-        <v>275488</v>
+        <v>124180</v>
       </c>
       <c r="AQ59" s="1">
-        <v>5129155</v>
+        <v>5253692</v>
       </c>
       <c r="AR59" s="1">
-        <v>5193955</v>
+        <v>5502497</v>
       </c>
     </row>
     <row r="60" spans="1:44" x14ac:dyDescent="0.35">
@@ -28387,19 +28504,19 @@
         <v>46</v>
       </c>
       <c r="C60" t="s">
-        <v>506</v>
+        <v>357</v>
       </c>
       <c r="D60" t="s">
         <v>48</v>
       </c>
       <c r="E60" t="s">
-        <v>930</v>
+        <v>1028</v>
       </c>
       <c r="F60" t="s">
-        <v>725</v>
+        <v>1014</v>
       </c>
       <c r="G60" t="s">
-        <v>931</v>
+        <v>1029</v>
       </c>
       <c r="H60" t="s">
         <v>52</v>
@@ -28411,13 +28528,13 @@
         <v>54</v>
       </c>
       <c r="K60" t="s">
-        <v>242</v>
+        <v>1030</v>
       </c>
       <c r="L60" t="s">
-        <v>725</v>
+        <v>1014</v>
       </c>
       <c r="M60" t="s">
-        <v>212</v>
+        <v>368</v>
       </c>
       <c r="N60" t="s">
         <v>57</v>
@@ -28426,7 +28543,7 @@
         <v>58</v>
       </c>
       <c r="P60" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="Q60" t="s">
         <v>60</v>
@@ -28438,16 +28555,16 @@
         <v>61</v>
       </c>
       <c r="T60" t="s">
-        <v>932</v>
+        <v>1031</v>
       </c>
       <c r="U60" s="1">
-        <v>3788.4</v>
+        <v>3768.4</v>
       </c>
       <c r="V60" s="1">
-        <v>3738.9</v>
+        <v>3754.9</v>
       </c>
       <c r="W60" s="1">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="X60" s="1">
         <v>0</v>
@@ -28459,16 +28576,16 @@
         <v>1228</v>
       </c>
       <c r="AA60" s="1">
-        <v>4652155.2</v>
+        <v>4627595.2</v>
       </c>
       <c r="AB60" s="1">
-        <v>27998.400000000001</v>
+        <v>0</v>
       </c>
       <c r="AC60" s="1">
-        <v>4766830</v>
+        <v>4787256</v>
       </c>
       <c r="AD60" s="1">
-        <v>33000</v>
+        <v>48600</v>
       </c>
       <c r="AE60" s="1">
         <v>0</v>
@@ -28477,37 +28594,37 @@
         <v>64</v>
       </c>
       <c r="AH60" t="s">
-        <v>933</v>
+        <v>1032</v>
       </c>
       <c r="AI60" s="1">
-        <v>16500</v>
+        <v>0</v>
       </c>
       <c r="AJ60" s="1">
-        <v>30880</v>
+        <v>0</v>
       </c>
       <c r="AK60" s="1">
-        <v>39296</v>
+        <v>0</v>
       </c>
       <c r="AL60" s="1">
-        <v>27998.400000000001</v>
+        <v>0</v>
       </c>
       <c r="AM60" s="1">
         <v>0</v>
       </c>
       <c r="AN60" s="1">
-        <v>0</v>
+        <v>159660</v>
       </c>
       <c r="AO60" s="1">
-        <v>238342</v>
+        <v>239363</v>
       </c>
       <c r="AP60" s="1">
-        <v>114674.4</v>
+        <v>159660</v>
       </c>
       <c r="AQ60" s="1">
-        <v>5005172</v>
+        <v>5026619</v>
       </c>
       <c r="AR60" s="1">
-        <v>5038172</v>
+        <v>5075219</v>
       </c>
     </row>
     <row r="61" spans="1:44" x14ac:dyDescent="0.35">
@@ -28518,19 +28635,19 @@
         <v>46</v>
       </c>
       <c r="C61" t="s">
-        <v>506</v>
+        <v>357</v>
       </c>
       <c r="D61" t="s">
         <v>48</v>
       </c>
       <c r="E61" t="s">
-        <v>934</v>
+        <v>1033</v>
       </c>
       <c r="F61" t="s">
-        <v>731</v>
+        <v>1034</v>
       </c>
       <c r="G61" t="s">
-        <v>935</v>
+        <v>1035</v>
       </c>
       <c r="H61" t="s">
         <v>52</v>
@@ -28542,13 +28659,13 @@
         <v>54</v>
       </c>
       <c r="K61" t="s">
-        <v>247</v>
+        <v>1036</v>
       </c>
       <c r="L61" t="s">
-        <v>731</v>
+        <v>1014</v>
       </c>
       <c r="M61" t="s">
-        <v>212</v>
+        <v>368</v>
       </c>
       <c r="N61" t="s">
         <v>57</v>
@@ -28557,7 +28674,7 @@
         <v>58</v>
       </c>
       <c r="P61" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="Q61" t="s">
         <v>60</v>
@@ -28569,16 +28686,16 @@
         <v>61</v>
       </c>
       <c r="T61" t="s">
-        <v>936</v>
+        <v>1037</v>
       </c>
       <c r="U61" s="1">
-        <v>4032.2</v>
+        <v>4117.3999999999996</v>
       </c>
       <c r="V61" s="1">
-        <v>3959.3</v>
+        <v>4100.8</v>
       </c>
       <c r="W61" s="1">
-        <v>9.8000000000000007</v>
+        <v>0</v>
       </c>
       <c r="X61" s="1">
         <v>0</v>
@@ -28590,55 +28707,55 @@
         <v>1228</v>
       </c>
       <c r="AA61" s="1">
-        <v>4951541.5999999996</v>
+        <v>5056167.2</v>
       </c>
       <c r="AB61" s="1">
-        <v>24068.799999999999</v>
+        <v>0</v>
       </c>
       <c r="AC61" s="1">
-        <v>5077923</v>
+        <v>5162608</v>
       </c>
       <c r="AD61" s="1">
-        <v>17400</v>
+        <v>26550</v>
       </c>
       <c r="AE61" s="1">
-        <v>17400</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="s">
         <v>64</v>
       </c>
       <c r="AH61" t="s">
-        <v>937</v>
+        <v>1038</v>
       </c>
       <c r="AI61" s="1">
-        <v>17400</v>
+        <v>0</v>
       </c>
       <c r="AJ61" s="1">
-        <v>30880</v>
+        <v>0</v>
       </c>
       <c r="AK61" s="1">
-        <v>54032</v>
+        <v>0</v>
       </c>
       <c r="AL61" s="1">
-        <v>24068.799999999999</v>
+        <v>0</v>
       </c>
       <c r="AM61" s="1">
         <v>0</v>
       </c>
       <c r="AN61" s="1">
-        <v>0</v>
+        <v>106440</v>
       </c>
       <c r="AO61" s="1">
-        <v>253897</v>
+        <v>258131</v>
       </c>
       <c r="AP61" s="1">
-        <v>126380.8</v>
+        <v>106440</v>
       </c>
       <c r="AQ61" s="1">
-        <v>5331820</v>
+        <v>5420739</v>
       </c>
       <c r="AR61" s="1">
-        <v>5366620</v>
+        <v>5447289</v>
       </c>
     </row>
     <row r="62" spans="1:44" x14ac:dyDescent="0.35">
@@ -28655,13 +28772,13 @@
         <v>48</v>
       </c>
       <c r="E62" t="s">
-        <v>938</v>
+        <v>914</v>
       </c>
       <c r="F62" t="s">
-        <v>742</v>
+        <v>680</v>
       </c>
       <c r="G62" t="s">
-        <v>939</v>
+        <v>915</v>
       </c>
       <c r="H62" t="s">
         <v>52</v>
@@ -28673,13 +28790,13 @@
         <v>54</v>
       </c>
       <c r="K62" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="L62" t="s">
-        <v>742</v>
+        <v>680</v>
       </c>
       <c r="M62" t="s">
-        <v>212</v>
+        <v>56</v>
       </c>
       <c r="N62" t="s">
         <v>57</v>
@@ -28694,22 +28811,22 @@
         <v>60</v>
       </c>
       <c r="R62" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="S62" t="s">
         <v>61</v>
       </c>
       <c r="T62" t="s">
-        <v>940</v>
+        <v>916</v>
       </c>
       <c r="U62" s="1">
-        <v>3595</v>
+        <v>3803.8</v>
       </c>
       <c r="V62" s="1">
-        <v>3496.1</v>
+        <v>3754.2</v>
       </c>
       <c r="W62" s="1">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="X62" s="1">
         <v>0</v>
@@ -28721,16 +28838,16 @@
         <v>1228</v>
       </c>
       <c r="AA62" s="1">
-        <v>4414660</v>
+        <v>4671066.4000000004</v>
       </c>
       <c r="AB62" s="1">
-        <v>10315.200000000001</v>
+        <v>15227.2</v>
       </c>
       <c r="AC62" s="1">
-        <v>4500928</v>
+        <v>4807354</v>
       </c>
       <c r="AD62" s="1">
-        <v>15600</v>
+        <v>24750</v>
       </c>
       <c r="AE62" s="1">
         <v>0</v>
@@ -28739,19 +28856,19 @@
         <v>64</v>
       </c>
       <c r="AH62" t="s">
-        <v>941</v>
+        <v>917</v>
       </c>
       <c r="AI62" s="1">
-        <v>15600</v>
+        <v>16500</v>
       </c>
       <c r="AJ62" s="1">
         <v>30880</v>
       </c>
       <c r="AK62" s="1">
-        <v>29472</v>
+        <v>73680</v>
       </c>
       <c r="AL62" s="1">
-        <v>10315.200000000001</v>
+        <v>15227.2</v>
       </c>
       <c r="AM62" s="1">
         <v>0</v>
@@ -28760,16 +28877,16 @@
         <v>0</v>
       </c>
       <c r="AO62" s="1">
-        <v>225047</v>
+        <v>240368</v>
       </c>
       <c r="AP62" s="1">
-        <v>86267.199999999997</v>
+        <v>136287.20000000001</v>
       </c>
       <c r="AQ62" s="1">
-        <v>4725975</v>
+        <v>5047722</v>
       </c>
       <c r="AR62" s="1">
-        <v>4741575</v>
+        <v>5072472</v>
       </c>
     </row>
     <row r="63" spans="1:44" x14ac:dyDescent="0.35">
@@ -28786,13 +28903,13 @@
         <v>48</v>
       </c>
       <c r="E63" t="s">
-        <v>942</v>
+        <v>918</v>
       </c>
       <c r="F63" t="s">
-        <v>748</v>
+        <v>686</v>
       </c>
       <c r="G63" t="s">
-        <v>943</v>
+        <v>919</v>
       </c>
       <c r="H63" t="s">
         <v>52</v>
@@ -28804,10 +28921,10 @@
         <v>54</v>
       </c>
       <c r="K63" t="s">
-        <v>259</v>
+        <v>227</v>
       </c>
       <c r="L63" t="s">
-        <v>748</v>
+        <v>686</v>
       </c>
       <c r="M63" t="s">
         <v>212</v>
@@ -28831,16 +28948,16 @@
         <v>61</v>
       </c>
       <c r="T63" t="s">
-        <v>944</v>
+        <v>920</v>
       </c>
       <c r="U63" s="1">
-        <v>4075</v>
+        <v>3999.2</v>
       </c>
       <c r="V63" s="1">
-        <v>4008.6</v>
+        <v>3885</v>
       </c>
       <c r="W63" s="1">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="X63" s="1">
         <v>0</v>
@@ -28852,37 +28969,37 @@
         <v>1228</v>
       </c>
       <c r="AA63" s="1">
-        <v>5004100</v>
+        <v>4911017.5999999996</v>
       </c>
       <c r="AB63" s="1">
-        <v>18174.400000000001</v>
+        <v>13753.6</v>
       </c>
       <c r="AC63" s="1">
-        <v>5250855</v>
+        <v>5007136</v>
       </c>
       <c r="AD63" s="1">
-        <v>17700</v>
+        <v>8550</v>
       </c>
       <c r="AE63" s="1">
-        <v>0</v>
+        <v>42750</v>
       </c>
       <c r="AF63" t="s">
         <v>64</v>
       </c>
       <c r="AH63" t="s">
-        <v>945</v>
+        <v>921</v>
       </c>
       <c r="AI63" s="1">
-        <v>17700</v>
+        <v>17100</v>
       </c>
       <c r="AJ63" s="1">
-        <v>61760</v>
+        <v>30880</v>
       </c>
       <c r="AK63" s="1">
-        <v>149120</v>
+        <v>34384</v>
       </c>
       <c r="AL63" s="1">
-        <v>18174.400000000001</v>
+        <v>13753.6</v>
       </c>
       <c r="AM63" s="1">
         <v>0</v>
@@ -28891,16 +29008,16 @@
         <v>0</v>
       </c>
       <c r="AO63" s="1">
-        <v>262543</v>
+        <v>250357</v>
       </c>
       <c r="AP63" s="1">
-        <v>246754.4</v>
+        <v>96117.6</v>
       </c>
       <c r="AQ63" s="1">
-        <v>5513398</v>
+        <v>5257493</v>
       </c>
       <c r="AR63" s="1">
-        <v>5531098</v>
+        <v>5308793</v>
       </c>
     </row>
     <row r="64" spans="1:44" x14ac:dyDescent="0.35">
@@ -28917,13 +29034,13 @@
         <v>48</v>
       </c>
       <c r="E64" t="s">
-        <v>946</v>
+        <v>922</v>
       </c>
       <c r="F64" t="s">
-        <v>854</v>
+        <v>708</v>
       </c>
       <c r="G64" t="s">
-        <v>947</v>
+        <v>923</v>
       </c>
       <c r="H64" t="s">
         <v>52</v>
@@ -28935,13 +29052,13 @@
         <v>54</v>
       </c>
       <c r="K64" t="s">
-        <v>264</v>
+        <v>232</v>
       </c>
       <c r="L64" t="s">
-        <v>854</v>
+        <v>708</v>
       </c>
       <c r="M64" t="s">
-        <v>56</v>
+        <v>212</v>
       </c>
       <c r="N64" t="s">
         <v>57</v>
@@ -28962,16 +29079,16 @@
         <v>61</v>
       </c>
       <c r="T64" t="s">
-        <v>948</v>
+        <v>924</v>
       </c>
       <c r="U64" s="1">
-        <v>3831.4</v>
+        <v>3957.4</v>
       </c>
       <c r="V64" s="1">
-        <v>3667.1</v>
+        <v>3934</v>
       </c>
       <c r="W64" s="1">
-        <v>5</v>
+        <v>17.8</v>
       </c>
       <c r="X64" s="1">
         <v>0</v>
@@ -28983,37 +29100,37 @@
         <v>1228</v>
       </c>
       <c r="AA64" s="1">
-        <v>4704959.2</v>
+        <v>4859687.2</v>
       </c>
       <c r="AB64" s="1">
-        <v>12280</v>
+        <v>65575.199999999997</v>
       </c>
       <c r="AC64" s="1">
-        <v>4871256</v>
+        <v>5269371</v>
       </c>
       <c r="AD64" s="1">
-        <v>25200</v>
+        <v>17100</v>
       </c>
       <c r="AE64" s="1">
-        <v>0</v>
+        <v>79515</v>
       </c>
       <c r="AF64" t="s">
         <v>64</v>
       </c>
       <c r="AH64" t="s">
-        <v>949</v>
+        <v>925</v>
       </c>
       <c r="AI64" s="1">
-        <v>8400</v>
+        <v>17100</v>
       </c>
       <c r="AJ64" s="1">
-        <v>30880</v>
+        <v>61760</v>
       </c>
       <c r="AK64" s="1">
-        <v>114736</v>
+        <v>265248</v>
       </c>
       <c r="AL64" s="1">
-        <v>12280</v>
+        <v>65575.199999999997</v>
       </c>
       <c r="AM64" s="1">
         <v>0</v>
@@ -29022,16 +29139,16 @@
         <v>0</v>
       </c>
       <c r="AO64" s="1">
-        <v>243563</v>
+        <v>263469</v>
       </c>
       <c r="AP64" s="1">
-        <v>166296</v>
+        <v>409683.20000000001</v>
       </c>
       <c r="AQ64" s="1">
-        <v>5114819</v>
+        <v>5532840</v>
       </c>
       <c r="AR64" s="1">
-        <v>5140019</v>
+        <v>5629455</v>
       </c>
     </row>
     <row r="65" spans="1:44" x14ac:dyDescent="0.35">
@@ -29048,13 +29165,13 @@
         <v>48</v>
       </c>
       <c r="E65" t="s">
-        <v>950</v>
+        <v>926</v>
       </c>
       <c r="F65" t="s">
-        <v>759</v>
+        <v>719</v>
       </c>
       <c r="G65" t="s">
-        <v>951</v>
+        <v>927</v>
       </c>
       <c r="H65" t="s">
         <v>52</v>
@@ -29066,10 +29183,10 @@
         <v>54</v>
       </c>
       <c r="K65" t="s">
-        <v>269</v>
+        <v>237</v>
       </c>
       <c r="L65" t="s">
-        <v>854</v>
+        <v>719</v>
       </c>
       <c r="M65" t="s">
         <v>212</v>
@@ -29093,16 +29210,16 @@
         <v>61</v>
       </c>
       <c r="T65" t="s">
-        <v>952</v>
+        <v>928</v>
       </c>
       <c r="U65" s="1">
-        <v>3953.4</v>
+        <v>3753.6</v>
       </c>
       <c r="V65" s="1">
-        <v>3916</v>
+        <v>3737.7</v>
       </c>
       <c r="W65" s="1">
-        <v>13.6</v>
+        <v>26</v>
       </c>
       <c r="X65" s="1">
         <v>0</v>
@@ -29114,37 +29231,37 @@
         <v>1228</v>
       </c>
       <c r="AA65" s="1">
-        <v>4854775.2</v>
+        <v>4609420.8</v>
       </c>
       <c r="AB65" s="1">
-        <v>33401.599999999999</v>
+        <v>95784</v>
       </c>
       <c r="AC65" s="1">
-        <v>4965629</v>
+        <v>4884909</v>
       </c>
       <c r="AD65" s="1">
-        <v>17100</v>
+        <v>40500</v>
       </c>
       <c r="AE65" s="1">
-        <v>139792.5</v>
+        <v>24300</v>
       </c>
       <c r="AF65" t="s">
         <v>64</v>
       </c>
       <c r="AH65" t="s">
-        <v>953</v>
+        <v>929</v>
       </c>
       <c r="AI65" s="1">
-        <v>17100</v>
+        <v>16200</v>
       </c>
       <c r="AJ65" s="1">
         <v>30880</v>
       </c>
       <c r="AK65" s="1">
-        <v>29472</v>
+        <v>132624</v>
       </c>
       <c r="AL65" s="1">
-        <v>33401.599999999999</v>
+        <v>95784</v>
       </c>
       <c r="AM65" s="1">
         <v>0</v>
@@ -29153,16 +29270,16 @@
         <v>0</v>
       </c>
       <c r="AO65" s="1">
-        <v>248282</v>
+        <v>244246</v>
       </c>
       <c r="AP65" s="1">
-        <v>110853.6</v>
+        <v>275488</v>
       </c>
       <c r="AQ65" s="1">
-        <v>5213911</v>
+        <v>5129155</v>
       </c>
       <c r="AR65" s="1">
-        <v>5370803.5</v>
+        <v>5193955</v>
       </c>
     </row>
     <row r="66" spans="1:44" x14ac:dyDescent="0.35">
@@ -29179,13 +29296,13 @@
         <v>48</v>
       </c>
       <c r="E66" t="s">
-        <v>954</v>
+        <v>930</v>
       </c>
       <c r="F66" t="s">
-        <v>759</v>
+        <v>725</v>
       </c>
       <c r="G66" t="s">
-        <v>955</v>
+        <v>931</v>
       </c>
       <c r="H66" t="s">
         <v>52</v>
@@ -29197,13 +29314,13 @@
         <v>54</v>
       </c>
       <c r="K66" t="s">
-        <v>275</v>
+        <v>242</v>
       </c>
       <c r="L66" t="s">
-        <v>759</v>
+        <v>725</v>
       </c>
       <c r="M66" t="s">
-        <v>56</v>
+        <v>212</v>
       </c>
       <c r="N66" t="s">
         <v>57</v>
@@ -29218,22 +29335,22 @@
         <v>60</v>
       </c>
       <c r="R66" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S66" t="s">
         <v>61</v>
       </c>
       <c r="T66" t="s">
-        <v>956</v>
+        <v>932</v>
       </c>
       <c r="U66" s="1">
-        <v>4076.4</v>
+        <v>3788.4</v>
       </c>
       <c r="V66" s="1">
-        <v>4057</v>
+        <v>3738.9</v>
       </c>
       <c r="W66" s="1">
-        <v>22.6</v>
+        <v>11.4</v>
       </c>
       <c r="X66" s="1">
         <v>0</v>
@@ -29245,37 +29362,37 @@
         <v>1228</v>
       </c>
       <c r="AA66" s="1">
-        <v>5005819.2</v>
+        <v>4652155.2</v>
       </c>
       <c r="AB66" s="1">
-        <v>83258.399999999994</v>
+        <v>27998.400000000001</v>
       </c>
       <c r="AC66" s="1">
-        <v>5433786</v>
+        <v>4766830</v>
       </c>
       <c r="AD66" s="1">
-        <v>17700</v>
+        <v>33000</v>
       </c>
       <c r="AE66" s="1">
-        <v>26550</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="s">
         <v>64</v>
       </c>
       <c r="AH66" t="s">
-        <v>957</v>
+        <v>933</v>
       </c>
       <c r="AI66" s="1">
-        <v>17700</v>
+        <v>16500</v>
       </c>
       <c r="AJ66" s="1">
-        <v>61760</v>
+        <v>30880</v>
       </c>
       <c r="AK66" s="1">
-        <v>265248</v>
+        <v>39296</v>
       </c>
       <c r="AL66" s="1">
-        <v>83258.399999999994</v>
+        <v>27998.400000000001</v>
       </c>
       <c r="AM66" s="1">
         <v>0</v>
@@ -29284,16 +29401,16 @@
         <v>0</v>
       </c>
       <c r="AO66" s="1">
-        <v>271690</v>
+        <v>238342</v>
       </c>
       <c r="AP66" s="1">
-        <v>427966.4</v>
+        <v>114674.4</v>
       </c>
       <c r="AQ66" s="1">
-        <v>5705476</v>
+        <v>5005172</v>
       </c>
       <c r="AR66" s="1">
-        <v>5749726</v>
+        <v>5038172</v>
       </c>
     </row>
     <row r="67" spans="1:44" x14ac:dyDescent="0.35">
@@ -29310,13 +29427,13 @@
         <v>48</v>
       </c>
       <c r="E67" t="s">
-        <v>958</v>
+        <v>934</v>
       </c>
       <c r="F67" t="s">
-        <v>867</v>
+        <v>731</v>
       </c>
       <c r="G67" t="s">
-        <v>959</v>
+        <v>935</v>
       </c>
       <c r="H67" t="s">
         <v>52</v>
@@ -29328,13 +29445,13 @@
         <v>54</v>
       </c>
       <c r="K67" t="s">
-        <v>281</v>
+        <v>247</v>
       </c>
       <c r="L67" t="s">
-        <v>867</v>
+        <v>731</v>
       </c>
       <c r="M67" t="s">
-        <v>56</v>
+        <v>212</v>
       </c>
       <c r="N67" t="s">
         <v>57</v>
@@ -29349,22 +29466,22 @@
         <v>60</v>
       </c>
       <c r="R67" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S67" t="s">
         <v>61</v>
       </c>
       <c r="T67" t="s">
-        <v>960</v>
+        <v>936</v>
       </c>
       <c r="U67" s="1">
-        <v>3942.2</v>
+        <v>4032.2</v>
       </c>
       <c r="V67" s="1">
-        <v>3927.6</v>
+        <v>3959.3</v>
       </c>
       <c r="W67" s="1">
-        <v>25.6</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="X67" s="1">
         <v>0</v>
@@ -29376,37 +29493,37 @@
         <v>1228</v>
       </c>
       <c r="AA67" s="1">
-        <v>4841021.5999999996</v>
+        <v>4951541.5999999996</v>
       </c>
       <c r="AB67" s="1">
-        <v>94310.399999999994</v>
+        <v>24068.799999999999</v>
       </c>
       <c r="AC67" s="1">
-        <v>5171196</v>
+        <v>5077923</v>
       </c>
       <c r="AD67" s="1">
-        <v>25650</v>
+        <v>17400</v>
       </c>
       <c r="AE67" s="1">
-        <v>51300</v>
+        <v>17400</v>
       </c>
       <c r="AF67" t="s">
         <v>64</v>
       </c>
       <c r="AH67" t="s">
-        <v>961</v>
+        <v>937</v>
       </c>
       <c r="AI67" s="1">
-        <v>17100</v>
+        <v>17400</v>
       </c>
       <c r="AJ67" s="1">
         <v>30880</v>
       </c>
       <c r="AK67" s="1">
-        <v>187884</v>
+        <v>54032</v>
       </c>
       <c r="AL67" s="1">
-        <v>94310.399999999994</v>
+        <v>24068.799999999999</v>
       </c>
       <c r="AM67" s="1">
         <v>0</v>
@@ -29415,16 +29532,16 @@
         <v>0</v>
       </c>
       <c r="AO67" s="1">
-        <v>258560</v>
+        <v>253897</v>
       </c>
       <c r="AP67" s="1">
-        <v>330174.40000000002</v>
+        <v>126380.8</v>
       </c>
       <c r="AQ67" s="1">
-        <v>5429756</v>
+        <v>5331820</v>
       </c>
       <c r="AR67" s="1">
-        <v>5506706</v>
+        <v>5366620</v>
       </c>
     </row>
     <row r="68" spans="1:44" x14ac:dyDescent="0.35">
@@ -29441,13 +29558,13 @@
         <v>48</v>
       </c>
       <c r="E68" t="s">
-        <v>962</v>
+        <v>938</v>
       </c>
       <c r="F68" t="s">
-        <v>867</v>
+        <v>742</v>
       </c>
       <c r="G68" t="s">
-        <v>963</v>
+        <v>939</v>
       </c>
       <c r="H68" t="s">
         <v>52</v>
@@ -29459,10 +29576,10 @@
         <v>54</v>
       </c>
       <c r="K68" t="s">
-        <v>287</v>
+        <v>253</v>
       </c>
       <c r="L68" t="s">
-        <v>867</v>
+        <v>742</v>
       </c>
       <c r="M68" t="s">
         <v>212</v>
@@ -29486,16 +29603,16 @@
         <v>61</v>
       </c>
       <c r="T68" t="s">
-        <v>964</v>
+        <v>940</v>
       </c>
       <c r="U68" s="1">
-        <v>3893</v>
+        <v>3595</v>
       </c>
       <c r="V68" s="1">
-        <v>3866.9</v>
+        <v>3496.1</v>
       </c>
       <c r="W68" s="1">
-        <v>16</v>
+        <v>4.2</v>
       </c>
       <c r="X68" s="1">
         <v>0</v>
@@ -29507,37 +29624,37 @@
         <v>1228</v>
       </c>
       <c r="AA68" s="1">
-        <v>4780604</v>
+        <v>4414660</v>
       </c>
       <c r="AB68" s="1">
-        <v>58944</v>
+        <v>10315.200000000001</v>
       </c>
       <c r="AC68" s="1">
-        <v>5076778</v>
+        <v>4500928</v>
       </c>
       <c r="AD68" s="1">
-        <v>25200</v>
+        <v>15600</v>
       </c>
       <c r="AE68" s="1">
-        <v>87360</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="s">
         <v>64</v>
       </c>
       <c r="AH68" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="AI68" s="1">
-        <v>16800</v>
+        <v>15600</v>
       </c>
       <c r="AJ68" s="1">
-        <v>61760</v>
+        <v>30880</v>
       </c>
       <c r="AK68" s="1">
-        <v>158670</v>
+        <v>29472</v>
       </c>
       <c r="AL68" s="1">
-        <v>58944</v>
+        <v>10315.200000000001</v>
       </c>
       <c r="AM68" s="1">
         <v>0</v>
@@ -29546,16 +29663,16 @@
         <v>0</v>
       </c>
       <c r="AO68" s="1">
-        <v>253839</v>
+        <v>225047</v>
       </c>
       <c r="AP68" s="1">
-        <v>296174</v>
+        <v>86267.199999999997</v>
       </c>
       <c r="AQ68" s="1">
-        <v>5330617</v>
+        <v>4725975</v>
       </c>
       <c r="AR68" s="1">
-        <v>5443177</v>
+        <v>4741575</v>
       </c>
     </row>
     <row r="69" spans="1:44" x14ac:dyDescent="0.35">
@@ -29572,13 +29689,13 @@
         <v>48</v>
       </c>
       <c r="E69" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="F69" t="s">
-        <v>765</v>
+        <v>748</v>
       </c>
       <c r="G69" t="s">
-        <v>967</v>
+        <v>943</v>
       </c>
       <c r="H69" t="s">
         <v>52</v>
@@ -29590,10 +29707,10 @@
         <v>54</v>
       </c>
       <c r="K69" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="L69" t="s">
-        <v>765</v>
+        <v>748</v>
       </c>
       <c r="M69" t="s">
         <v>212</v>
@@ -29617,16 +29734,16 @@
         <v>61</v>
       </c>
       <c r="T69" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="U69" s="1">
-        <v>3817.8</v>
+        <v>4075</v>
       </c>
       <c r="V69" s="1">
-        <v>3804.9</v>
+        <v>4008.6</v>
       </c>
       <c r="W69" s="1">
-        <v>23.2</v>
+        <v>7.4</v>
       </c>
       <c r="X69" s="1">
         <v>0</v>
@@ -29638,37 +29755,37 @@
         <v>1228</v>
       </c>
       <c r="AA69" s="1">
-        <v>4688258.4000000004</v>
+        <v>5004100</v>
       </c>
       <c r="AB69" s="1">
-        <v>85468.800000000003</v>
+        <v>18174.400000000001</v>
       </c>
       <c r="AC69" s="1">
-        <v>5183548</v>
+        <v>5250855</v>
       </c>
       <c r="AD69" s="1">
-        <v>49500</v>
+        <v>17700</v>
       </c>
       <c r="AE69" s="1">
-        <v>58575</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="s">
         <v>64</v>
       </c>
       <c r="AH69" t="s">
-        <v>969</v>
+        <v>945</v>
       </c>
       <c r="AI69" s="1">
-        <v>16500</v>
+        <v>17700</v>
       </c>
       <c r="AJ69" s="1">
         <v>61760</v>
       </c>
       <c r="AK69" s="1">
-        <v>331560</v>
+        <v>149120</v>
       </c>
       <c r="AL69" s="1">
-        <v>85468.800000000003</v>
+        <v>18174.400000000001</v>
       </c>
       <c r="AM69" s="1">
         <v>0</v>
@@ -29677,16 +29794,16 @@
         <v>0</v>
       </c>
       <c r="AO69" s="1">
-        <v>259178</v>
+        <v>262543</v>
       </c>
       <c r="AP69" s="1">
-        <v>495288.8</v>
+        <v>246754.4</v>
       </c>
       <c r="AQ69" s="1">
-        <v>5442726</v>
+        <v>5513398</v>
       </c>
       <c r="AR69" s="1">
-        <v>5550801</v>
+        <v>5531098</v>
       </c>
     </row>
     <row r="70" spans="1:44" x14ac:dyDescent="0.35">
@@ -29703,13 +29820,13 @@
         <v>48</v>
       </c>
       <c r="E70" t="s">
-        <v>970</v>
+        <v>946</v>
       </c>
       <c r="F70" t="s">
-        <v>771</v>
+        <v>854</v>
       </c>
       <c r="G70" t="s">
-        <v>971</v>
+        <v>947</v>
       </c>
       <c r="H70" t="s">
         <v>52</v>
@@ -29721,10 +29838,10 @@
         <v>54</v>
       </c>
       <c r="K70" t="s">
-        <v>298</v>
+        <v>264</v>
       </c>
       <c r="L70" t="s">
-        <v>771</v>
+        <v>854</v>
       </c>
       <c r="M70" t="s">
         <v>56</v>
@@ -29748,16 +29865,16 @@
         <v>61</v>
       </c>
       <c r="T70" t="s">
-        <v>972</v>
+        <v>948</v>
       </c>
       <c r="U70" s="1">
-        <v>3744.6</v>
+        <v>3831.4</v>
       </c>
       <c r="V70" s="1">
-        <v>3728.9</v>
+        <v>3667.1</v>
       </c>
       <c r="W70" s="1">
-        <v>23.2</v>
+        <v>5</v>
       </c>
       <c r="X70" s="1">
         <v>0</v>
@@ -29769,37 +29886,37 @@
         <v>1228</v>
       </c>
       <c r="AA70" s="1">
-        <v>4598368.8</v>
+        <v>4704959.2</v>
       </c>
       <c r="AB70" s="1">
-        <v>85468.800000000003</v>
+        <v>12280</v>
       </c>
       <c r="AC70" s="1">
-        <v>5038098</v>
+        <v>4871256</v>
       </c>
       <c r="AD70" s="1">
-        <v>24300</v>
+        <v>25200</v>
       </c>
       <c r="AE70" s="1">
-        <v>122310</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="s">
         <v>64</v>
       </c>
       <c r="AH70" t="s">
-        <v>973</v>
+        <v>949</v>
       </c>
       <c r="AI70" s="1">
-        <v>16200</v>
+        <v>8400</v>
       </c>
       <c r="AJ70" s="1">
-        <v>61760</v>
+        <v>30880</v>
       </c>
       <c r="AK70" s="1">
-        <v>276300</v>
+        <v>114736</v>
       </c>
       <c r="AL70" s="1">
-        <v>85468.800000000003</v>
+        <v>12280</v>
       </c>
       <c r="AM70" s="1">
         <v>0</v>
@@ -29808,16 +29925,16 @@
         <v>0</v>
       </c>
       <c r="AO70" s="1">
-        <v>251905</v>
+        <v>243563</v>
       </c>
       <c r="AP70" s="1">
-        <v>439728.8</v>
+        <v>166296</v>
       </c>
       <c r="AQ70" s="1">
-        <v>5290003</v>
+        <v>5114819</v>
       </c>
       <c r="AR70" s="1">
-        <v>5436613</v>
+        <v>5140019</v>
       </c>
     </row>
     <row r="71" spans="1:44" x14ac:dyDescent="0.35">
@@ -29834,13 +29951,13 @@
         <v>48</v>
       </c>
       <c r="E71" t="s">
-        <v>974</v>
+        <v>950</v>
       </c>
       <c r="F71" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="G71" t="s">
-        <v>975</v>
+        <v>951</v>
       </c>
       <c r="H71" t="s">
         <v>52</v>
@@ -29852,10 +29969,10 @@
         <v>54</v>
       </c>
       <c r="K71" t="s">
-        <v>303</v>
+        <v>269</v>
       </c>
       <c r="L71" t="s">
-        <v>771</v>
+        <v>854</v>
       </c>
       <c r="M71" t="s">
         <v>212</v>
@@ -29879,16 +29996,16 @@
         <v>61</v>
       </c>
       <c r="T71" t="s">
-        <v>976</v>
+        <v>952</v>
       </c>
       <c r="U71" s="1">
-        <v>3870.4</v>
+        <v>3953.4</v>
       </c>
       <c r="V71" s="1">
-        <v>3795</v>
+        <v>3916</v>
       </c>
       <c r="W71" s="1">
-        <v>10.4</v>
+        <v>13.6</v>
       </c>
       <c r="X71" s="1">
         <v>0</v>
@@ -29900,28 +30017,28 @@
         <v>1228</v>
       </c>
       <c r="AA71" s="1">
-        <v>4752851.2</v>
+        <v>4854775.2</v>
       </c>
       <c r="AB71" s="1">
-        <v>25542.400000000001</v>
+        <v>33401.599999999999</v>
       </c>
       <c r="AC71" s="1">
-        <v>4855546</v>
+        <v>4965629</v>
       </c>
       <c r="AD71" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
       <c r="AE71" s="1">
-        <v>147840</v>
+        <v>139792.5</v>
       </c>
       <c r="AF71" t="s">
         <v>64</v>
       </c>
       <c r="AH71" t="s">
-        <v>977</v>
+        <v>953</v>
       </c>
       <c r="AI71" s="1">
-        <v>16800</v>
+        <v>17100</v>
       </c>
       <c r="AJ71" s="1">
         <v>30880</v>
@@ -29930,7 +30047,7 @@
         <v>29472</v>
       </c>
       <c r="AL71" s="1">
-        <v>25542.400000000001</v>
+        <v>33401.599999999999</v>
       </c>
       <c r="AM71" s="1">
         <v>0</v>
@@ -29939,16 +30056,16 @@
         <v>0</v>
       </c>
       <c r="AO71" s="1">
-        <v>242778</v>
+        <v>248282</v>
       </c>
       <c r="AP71" s="1">
-        <v>102694.39999999999</v>
+        <v>110853.6</v>
       </c>
       <c r="AQ71" s="1">
-        <v>5098324</v>
+        <v>5213911</v>
       </c>
       <c r="AR71" s="1">
-        <v>5262964</v>
+        <v>5370803.5</v>
       </c>
     </row>
     <row r="72" spans="1:44" x14ac:dyDescent="0.35">
@@ -29965,13 +30082,13 @@
         <v>48</v>
       </c>
       <c r="E72" t="s">
-        <v>978</v>
+        <v>954</v>
       </c>
       <c r="F72" t="s">
-        <v>903</v>
+        <v>759</v>
       </c>
       <c r="G72" t="s">
-        <v>979</v>
+        <v>955</v>
       </c>
       <c r="H72" t="s">
         <v>52</v>
@@ -29983,13 +30100,13 @@
         <v>54</v>
       </c>
       <c r="K72" t="s">
-        <v>309</v>
+        <v>275</v>
       </c>
       <c r="L72" t="s">
-        <v>897</v>
+        <v>759</v>
       </c>
       <c r="M72" t="s">
-        <v>212</v>
+        <v>56</v>
       </c>
       <c r="N72" t="s">
         <v>57</v>
@@ -30004,22 +30121,22 @@
         <v>60</v>
       </c>
       <c r="R72" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="S72" t="s">
         <v>61</v>
       </c>
       <c r="T72" t="s">
-        <v>980</v>
+        <v>956</v>
       </c>
       <c r="U72" s="1">
-        <v>3226.4</v>
+        <v>4076.4</v>
       </c>
       <c r="V72" s="1">
-        <v>3162.6</v>
+        <v>4057</v>
       </c>
       <c r="W72" s="1">
-        <v>3.4</v>
+        <v>22.6</v>
       </c>
       <c r="X72" s="1">
         <v>0</v>
@@ -30031,37 +30148,37 @@
         <v>1228</v>
       </c>
       <c r="AA72" s="1">
-        <v>3962019.2</v>
+        <v>5005819.2</v>
       </c>
       <c r="AB72" s="1">
-        <v>8350.4</v>
+        <v>83258.399999999994</v>
       </c>
       <c r="AC72" s="1">
-        <v>4069082</v>
+        <v>5433786</v>
       </c>
       <c r="AD72" s="1">
-        <v>27600</v>
+        <v>17700</v>
       </c>
       <c r="AE72" s="1">
-        <v>0</v>
+        <v>26550</v>
       </c>
       <c r="AF72" t="s">
         <v>64</v>
       </c>
       <c r="AH72" t="s">
-        <v>981</v>
+        <v>957</v>
       </c>
       <c r="AI72" s="1">
-        <v>13800</v>
+        <v>17700</v>
       </c>
       <c r="AJ72" s="1">
-        <v>30880</v>
+        <v>61760</v>
       </c>
       <c r="AK72" s="1">
-        <v>54032</v>
+        <v>265248</v>
       </c>
       <c r="AL72" s="1">
-        <v>8350.4</v>
+        <v>83258.399999999994</v>
       </c>
       <c r="AM72" s="1">
         <v>0</v>
@@ -30070,16 +30187,16 @@
         <v>0</v>
       </c>
       <c r="AO72" s="1">
-        <v>203455</v>
+        <v>271690</v>
       </c>
       <c r="AP72" s="1">
-        <v>107062.39999999999</v>
+        <v>427966.4</v>
       </c>
       <c r="AQ72" s="1">
-        <v>4272537</v>
+        <v>5705476</v>
       </c>
       <c r="AR72" s="1">
-        <v>4300137</v>
+        <v>5749726</v>
       </c>
     </row>
     <row r="73" spans="1:44" x14ac:dyDescent="0.35">
@@ -30096,13 +30213,13 @@
         <v>48</v>
       </c>
       <c r="E73" t="s">
-        <v>982</v>
+        <v>958</v>
       </c>
       <c r="F73" t="s">
-        <v>983</v>
+        <v>867</v>
       </c>
       <c r="G73" t="s">
-        <v>984</v>
+        <v>959</v>
       </c>
       <c r="H73" t="s">
         <v>52</v>
@@ -30114,13 +30231,13 @@
         <v>54</v>
       </c>
       <c r="K73" t="s">
-        <v>315</v>
+        <v>281</v>
       </c>
       <c r="L73" t="s">
-        <v>903</v>
+        <v>867</v>
       </c>
       <c r="M73" t="s">
-        <v>212</v>
+        <v>56</v>
       </c>
       <c r="N73" t="s">
         <v>57</v>
@@ -30135,22 +30252,22 @@
         <v>60</v>
       </c>
       <c r="R73" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="S73" t="s">
         <v>61</v>
       </c>
       <c r="T73" t="s">
-        <v>985</v>
+        <v>960</v>
       </c>
       <c r="U73" s="1">
-        <v>4155.8</v>
+        <v>3942.2</v>
       </c>
       <c r="V73" s="1">
-        <v>4131.3</v>
+        <v>3927.6</v>
       </c>
       <c r="W73" s="1">
-        <v>20.6</v>
+        <v>25.6</v>
       </c>
       <c r="X73" s="1">
         <v>0</v>
@@ -30162,37 +30279,37 @@
         <v>1228</v>
       </c>
       <c r="AA73" s="1">
-        <v>5103322.4000000004</v>
+        <v>4841021.5999999996</v>
       </c>
       <c r="AB73" s="1">
-        <v>75890.399999999994</v>
+        <v>94310.399999999994</v>
       </c>
       <c r="AC73" s="1">
-        <v>5404625</v>
+        <v>5171196</v>
       </c>
       <c r="AD73" s="1">
-        <v>44250</v>
+        <v>25650</v>
       </c>
       <c r="AE73" s="1">
-        <v>17700</v>
+        <v>51300</v>
       </c>
       <c r="AF73" t="s">
         <v>64</v>
       </c>
       <c r="AH73" t="s">
-        <v>986</v>
+        <v>961</v>
       </c>
       <c r="AI73" s="1">
-        <v>17700</v>
+        <v>17100</v>
       </c>
       <c r="AJ73" s="1">
         <v>30880</v>
       </c>
       <c r="AK73" s="1">
-        <v>176832</v>
+        <v>187884</v>
       </c>
       <c r="AL73" s="1">
-        <v>75890.399999999994</v>
+        <v>94310.399999999994</v>
       </c>
       <c r="AM73" s="1">
         <v>0</v>
@@ -30201,16 +30318,16 @@
         <v>0</v>
       </c>
       <c r="AO73" s="1">
-        <v>270232</v>
+        <v>258560</v>
       </c>
       <c r="AP73" s="1">
-        <v>301302.40000000002</v>
+        <v>330174.40000000002</v>
       </c>
       <c r="AQ73" s="1">
-        <v>5674857</v>
+        <v>5429756</v>
       </c>
       <c r="AR73" s="1">
-        <v>5736807</v>
+        <v>5506706</v>
       </c>
     </row>
     <row r="74" spans="1:44" x14ac:dyDescent="0.35">
@@ -30227,13 +30344,13 @@
         <v>48</v>
       </c>
       <c r="E74" t="s">
-        <v>1004</v>
+        <v>962</v>
       </c>
       <c r="F74" t="s">
-        <v>1000</v>
+        <v>867</v>
       </c>
       <c r="G74" t="s">
-        <v>1005</v>
+        <v>963</v>
       </c>
       <c r="H74" t="s">
         <v>52</v>
@@ -30245,10 +30362,10 @@
         <v>54</v>
       </c>
       <c r="K74" t="s">
-        <v>321</v>
+        <v>287</v>
       </c>
       <c r="L74" t="s">
-        <v>1000</v>
+        <v>867</v>
       </c>
       <c r="M74" t="s">
         <v>212</v>
@@ -30272,16 +30389,16 @@
         <v>61</v>
       </c>
       <c r="T74" t="s">
-        <v>1006</v>
+        <v>964</v>
       </c>
       <c r="U74" s="1">
-        <v>4010.2</v>
+        <v>3893</v>
       </c>
       <c r="V74" s="1">
-        <v>3984.5</v>
+        <v>3866.9</v>
       </c>
       <c r="W74" s="1">
-        <v>17.600000000000001</v>
+        <v>16</v>
       </c>
       <c r="X74" s="1">
         <v>0</v>
@@ -30293,37 +30410,37 @@
         <v>1228</v>
       </c>
       <c r="AA74" s="1">
-        <v>4924525.5999999996</v>
+        <v>4780604</v>
       </c>
       <c r="AB74" s="1">
-        <v>64838.400000000001</v>
+        <v>58944</v>
       </c>
       <c r="AC74" s="1">
-        <v>5214176</v>
+        <v>5076778</v>
       </c>
       <c r="AD74" s="1">
-        <v>17100</v>
+        <v>25200</v>
       </c>
       <c r="AE74" s="1">
-        <v>0</v>
+        <v>87360</v>
       </c>
       <c r="AF74" t="s">
         <v>64</v>
       </c>
       <c r="AH74" t="s">
-        <v>1007</v>
+        <v>965</v>
       </c>
       <c r="AI74" s="1">
-        <v>17100</v>
+        <v>16800</v>
       </c>
       <c r="AJ74" s="1">
-        <v>30880</v>
+        <v>61760</v>
       </c>
       <c r="AK74" s="1">
-        <v>176832</v>
+        <v>158670</v>
       </c>
       <c r="AL74" s="1">
-        <v>64838.400000000001</v>
+        <v>58944</v>
       </c>
       <c r="AM74" s="1">
         <v>0</v>
@@ -30332,16 +30449,16 @@
         <v>0</v>
       </c>
       <c r="AO74" s="1">
-        <v>260709</v>
+        <v>253839</v>
       </c>
       <c r="AP74" s="1">
-        <v>289650.40000000002</v>
+        <v>296174</v>
       </c>
       <c r="AQ74" s="1">
-        <v>5474885</v>
+        <v>5330617</v>
       </c>
       <c r="AR74" s="1">
-        <v>5491985</v>
+        <v>5443177</v>
       </c>
     </row>
     <row r="75" spans="1:44" x14ac:dyDescent="0.35">
@@ -30358,13 +30475,13 @@
         <v>48</v>
       </c>
       <c r="E75" t="s">
-        <v>987</v>
+        <v>966</v>
       </c>
       <c r="F75" t="s">
-        <v>664</v>
+        <v>765</v>
       </c>
       <c r="G75" t="s">
-        <v>988</v>
+        <v>967</v>
       </c>
       <c r="H75" t="s">
         <v>52</v>
@@ -30376,13 +30493,13 @@
         <v>54</v>
       </c>
       <c r="K75" t="s">
-        <v>350</v>
+        <v>293</v>
       </c>
       <c r="L75" t="s">
-        <v>664</v>
+        <v>765</v>
       </c>
       <c r="M75" t="s">
-        <v>56</v>
+        <v>212</v>
       </c>
       <c r="N75" t="s">
         <v>57</v>
@@ -30397,22 +30514,22 @@
         <v>60</v>
       </c>
       <c r="R75" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S75" t="s">
         <v>61</v>
       </c>
       <c r="T75" t="s">
-        <v>989</v>
+        <v>968</v>
       </c>
       <c r="U75" s="1">
-        <v>3989.6</v>
+        <v>3817.8</v>
       </c>
       <c r="V75" s="1">
-        <v>3759.2</v>
+        <v>3804.9</v>
       </c>
       <c r="W75" s="1">
-        <v>1.2</v>
+        <v>23.2</v>
       </c>
       <c r="X75" s="1">
         <v>0</v>
@@ -30424,37 +30541,37 @@
         <v>1228</v>
       </c>
       <c r="AA75" s="1">
-        <v>4899228.8</v>
+        <v>4688258.4000000004</v>
       </c>
       <c r="AB75" s="1">
-        <v>2947.2</v>
+        <v>85468.800000000003</v>
       </c>
       <c r="AC75" s="1">
-        <v>4970104</v>
+        <v>5183548</v>
       </c>
       <c r="AD75" s="1">
-        <v>8700</v>
+        <v>49500</v>
       </c>
       <c r="AE75" s="1">
-        <v>0</v>
+        <v>58575</v>
       </c>
       <c r="AF75" t="s">
         <v>64</v>
       </c>
       <c r="AH75" t="s">
-        <v>990</v>
+        <v>969</v>
       </c>
       <c r="AI75" s="1">
-        <v>17400</v>
+        <v>16500</v>
       </c>
       <c r="AJ75" s="1">
-        <v>30880</v>
+        <v>61760</v>
       </c>
       <c r="AK75" s="1">
-        <v>19648</v>
+        <v>331560</v>
       </c>
       <c r="AL75" s="1">
-        <v>2947.2</v>
+        <v>85468.800000000003</v>
       </c>
       <c r="AM75" s="1">
         <v>0</v>
@@ -30463,16 +30580,16 @@
         <v>0</v>
       </c>
       <c r="AO75" s="1">
-        <v>248506</v>
+        <v>259178</v>
       </c>
       <c r="AP75" s="1">
-        <v>70875.199999999997</v>
+        <v>495288.8</v>
       </c>
       <c r="AQ75" s="1">
-        <v>5218610</v>
+        <v>5442726</v>
       </c>
       <c r="AR75" s="1">
-        <v>5227310</v>
+        <v>5550801</v>
       </c>
     </row>
     <row r="76" spans="1:44" x14ac:dyDescent="0.35">
@@ -30489,13 +30606,13 @@
         <v>48</v>
       </c>
       <c r="E76" t="s">
-        <v>991</v>
+        <v>970</v>
       </c>
       <c r="F76" t="s">
-        <v>664</v>
+        <v>771</v>
       </c>
       <c r="G76" t="s">
-        <v>992</v>
+        <v>971</v>
       </c>
       <c r="H76" t="s">
         <v>52</v>
@@ -30507,13 +30624,13 @@
         <v>54</v>
       </c>
       <c r="K76" t="s">
-        <v>355</v>
+        <v>298</v>
       </c>
       <c r="L76" t="s">
-        <v>664</v>
+        <v>771</v>
       </c>
       <c r="M76" t="s">
-        <v>212</v>
+        <v>56</v>
       </c>
       <c r="N76" t="s">
         <v>57</v>
@@ -30528,22 +30645,22 @@
         <v>60</v>
       </c>
       <c r="R76" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="S76" t="s">
         <v>61</v>
       </c>
       <c r="T76" t="s">
-        <v>993</v>
+        <v>972</v>
       </c>
       <c r="U76" s="1">
-        <v>3822.4</v>
+        <v>3744.6</v>
       </c>
       <c r="V76" s="1">
-        <v>3799.7</v>
+        <v>3728.9</v>
       </c>
       <c r="W76" s="1">
-        <v>20.399999999999999</v>
+        <v>23.2</v>
       </c>
       <c r="X76" s="1">
         <v>0</v>
@@ -30555,59 +30672,1106 @@
         <v>1228</v>
       </c>
       <c r="AA76" s="1">
-        <v>4693907.2</v>
+        <v>4598368.8</v>
       </c>
       <c r="AB76" s="1">
-        <v>75153.600000000006</v>
+        <v>85468.800000000003</v>
       </c>
       <c r="AC76" s="1">
-        <v>5035205</v>
+        <v>5038098</v>
       </c>
       <c r="AD76" s="1">
-        <v>24750</v>
+        <v>24300</v>
       </c>
       <c r="AE76" s="1">
-        <v>0</v>
+        <v>122310</v>
       </c>
       <c r="AF76" t="s">
         <v>64</v>
       </c>
       <c r="AH76" t="s">
-        <v>994</v>
+        <v>973</v>
       </c>
       <c r="AI76" s="1">
-        <v>16500</v>
+        <v>16200</v>
       </c>
       <c r="AJ76" s="1">
         <v>61760</v>
       </c>
       <c r="AK76" s="1">
+        <v>276300</v>
+      </c>
+      <c r="AL76" s="1">
+        <v>85468.800000000003</v>
+      </c>
+      <c r="AM76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="1">
+        <v>251905</v>
+      </c>
+      <c r="AP76" s="1">
+        <v>439728.8</v>
+      </c>
+      <c r="AQ76" s="1">
+        <v>5290003</v>
+      </c>
+      <c r="AR76" s="1">
+        <v>5436613</v>
+      </c>
+    </row>
+    <row r="77" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>45</v>
+      </c>
+      <c r="B77" t="s">
+        <v>46</v>
+      </c>
+      <c r="C77" t="s">
+        <v>506</v>
+      </c>
+      <c r="D77" t="s">
+        <v>48</v>
+      </c>
+      <c r="E77" t="s">
+        <v>974</v>
+      </c>
+      <c r="F77" t="s">
+        <v>771</v>
+      </c>
+      <c r="G77" t="s">
+        <v>975</v>
+      </c>
+      <c r="H77" t="s">
+        <v>52</v>
+      </c>
+      <c r="I77" t="s">
+        <v>53</v>
+      </c>
+      <c r="J77" t="s">
+        <v>54</v>
+      </c>
+      <c r="K77" t="s">
+        <v>303</v>
+      </c>
+      <c r="L77" t="s">
+        <v>771</v>
+      </c>
+      <c r="M77" t="s">
+        <v>212</v>
+      </c>
+      <c r="N77" t="s">
+        <v>57</v>
+      </c>
+      <c r="O77" t="s">
+        <v>58</v>
+      </c>
+      <c r="P77" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>60</v>
+      </c>
+      <c r="R77" t="s">
+        <v>88</v>
+      </c>
+      <c r="S77" t="s">
+        <v>61</v>
+      </c>
+      <c r="T77" t="s">
+        <v>976</v>
+      </c>
+      <c r="U77" s="1">
+        <v>3870.4</v>
+      </c>
+      <c r="V77" s="1">
+        <v>3795</v>
+      </c>
+      <c r="W77" s="1">
+        <v>10.4</v>
+      </c>
+      <c r="X77" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z77" s="1">
+        <v>1228</v>
+      </c>
+      <c r="AA77" s="1">
+        <v>4752851.2</v>
+      </c>
+      <c r="AB77" s="1">
+        <v>25542.400000000001</v>
+      </c>
+      <c r="AC77" s="1">
+        <v>4855546</v>
+      </c>
+      <c r="AD77" s="1">
+        <v>16800</v>
+      </c>
+      <c r="AE77" s="1">
+        <v>147840</v>
+      </c>
+      <c r="AF77" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH77" t="s">
+        <v>977</v>
+      </c>
+      <c r="AI77" s="1">
+        <v>16800</v>
+      </c>
+      <c r="AJ77" s="1">
+        <v>30880</v>
+      </c>
+      <c r="AK77" s="1">
+        <v>29472</v>
+      </c>
+      <c r="AL77" s="1">
+        <v>25542.400000000001</v>
+      </c>
+      <c r="AM77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="1">
+        <v>242778</v>
+      </c>
+      <c r="AP77" s="1">
+        <v>102694.39999999999</v>
+      </c>
+      <c r="AQ77" s="1">
+        <v>5098324</v>
+      </c>
+      <c r="AR77" s="1">
+        <v>5262964</v>
+      </c>
+    </row>
+    <row r="78" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>45</v>
+      </c>
+      <c r="B78" t="s">
+        <v>46</v>
+      </c>
+      <c r="C78" t="s">
+        <v>506</v>
+      </c>
+      <c r="D78" t="s">
+        <v>48</v>
+      </c>
+      <c r="E78" t="s">
+        <v>978</v>
+      </c>
+      <c r="F78" t="s">
+        <v>903</v>
+      </c>
+      <c r="G78" t="s">
+        <v>979</v>
+      </c>
+      <c r="H78" t="s">
+        <v>52</v>
+      </c>
+      <c r="I78" t="s">
+        <v>53</v>
+      </c>
+      <c r="J78" t="s">
+        <v>54</v>
+      </c>
+      <c r="K78" t="s">
+        <v>309</v>
+      </c>
+      <c r="L78" t="s">
+        <v>897</v>
+      </c>
+      <c r="M78" t="s">
+        <v>212</v>
+      </c>
+      <c r="N78" t="s">
+        <v>57</v>
+      </c>
+      <c r="O78" t="s">
+        <v>58</v>
+      </c>
+      <c r="P78" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>60</v>
+      </c>
+      <c r="R78" t="s">
+        <v>88</v>
+      </c>
+      <c r="S78" t="s">
+        <v>61</v>
+      </c>
+      <c r="T78" t="s">
+        <v>980</v>
+      </c>
+      <c r="U78" s="1">
+        <v>3226.4</v>
+      </c>
+      <c r="V78" s="1">
+        <v>3162.6</v>
+      </c>
+      <c r="W78" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="X78" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z78" s="1">
+        <v>1228</v>
+      </c>
+      <c r="AA78" s="1">
+        <v>3962019.2</v>
+      </c>
+      <c r="AB78" s="1">
+        <v>8350.4</v>
+      </c>
+      <c r="AC78" s="1">
+        <v>4069082</v>
+      </c>
+      <c r="AD78" s="1">
+        <v>27600</v>
+      </c>
+      <c r="AE78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH78" t="s">
+        <v>981</v>
+      </c>
+      <c r="AI78" s="1">
+        <v>13800</v>
+      </c>
+      <c r="AJ78" s="1">
+        <v>30880</v>
+      </c>
+      <c r="AK78" s="1">
+        <v>54032</v>
+      </c>
+      <c r="AL78" s="1">
+        <v>8350.4</v>
+      </c>
+      <c r="AM78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO78" s="1">
+        <v>203455</v>
+      </c>
+      <c r="AP78" s="1">
+        <v>107062.39999999999</v>
+      </c>
+      <c r="AQ78" s="1">
+        <v>4272537</v>
+      </c>
+      <c r="AR78" s="1">
+        <v>4300137</v>
+      </c>
+    </row>
+    <row r="79" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>45</v>
+      </c>
+      <c r="B79" t="s">
+        <v>46</v>
+      </c>
+      <c r="C79" t="s">
+        <v>506</v>
+      </c>
+      <c r="D79" t="s">
+        <v>48</v>
+      </c>
+      <c r="E79" t="s">
+        <v>982</v>
+      </c>
+      <c r="F79" t="s">
+        <v>983</v>
+      </c>
+      <c r="G79" t="s">
+        <v>984</v>
+      </c>
+      <c r="H79" t="s">
+        <v>52</v>
+      </c>
+      <c r="I79" t="s">
+        <v>53</v>
+      </c>
+      <c r="J79" t="s">
+        <v>54</v>
+      </c>
+      <c r="K79" t="s">
+        <v>315</v>
+      </c>
+      <c r="L79" t="s">
+        <v>903</v>
+      </c>
+      <c r="M79" t="s">
+        <v>212</v>
+      </c>
+      <c r="N79" t="s">
+        <v>57</v>
+      </c>
+      <c r="O79" t="s">
+        <v>58</v>
+      </c>
+      <c r="P79" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>60</v>
+      </c>
+      <c r="R79" t="s">
+        <v>88</v>
+      </c>
+      <c r="S79" t="s">
+        <v>61</v>
+      </c>
+      <c r="T79" t="s">
+        <v>985</v>
+      </c>
+      <c r="U79" s="1">
+        <v>4155.8</v>
+      </c>
+      <c r="V79" s="1">
+        <v>4131.3</v>
+      </c>
+      <c r="W79" s="1">
+        <v>20.6</v>
+      </c>
+      <c r="X79" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z79" s="1">
+        <v>1228</v>
+      </c>
+      <c r="AA79" s="1">
+        <v>5103322.4000000004</v>
+      </c>
+      <c r="AB79" s="1">
+        <v>75890.399999999994</v>
+      </c>
+      <c r="AC79" s="1">
+        <v>5404625</v>
+      </c>
+      <c r="AD79" s="1">
+        <v>44250</v>
+      </c>
+      <c r="AE79" s="1">
+        <v>17700</v>
+      </c>
+      <c r="AF79" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH79" t="s">
+        <v>986</v>
+      </c>
+      <c r="AI79" s="1">
+        <v>17700</v>
+      </c>
+      <c r="AJ79" s="1">
+        <v>30880</v>
+      </c>
+      <c r="AK79" s="1">
+        <v>176832</v>
+      </c>
+      <c r="AL79" s="1">
+        <v>75890.399999999994</v>
+      </c>
+      <c r="AM79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO79" s="1">
+        <v>270232</v>
+      </c>
+      <c r="AP79" s="1">
+        <v>301302.40000000002</v>
+      </c>
+      <c r="AQ79" s="1">
+        <v>5674857</v>
+      </c>
+      <c r="AR79" s="1">
+        <v>5736807</v>
+      </c>
+    </row>
+    <row r="80" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>45</v>
+      </c>
+      <c r="B80" t="s">
+        <v>46</v>
+      </c>
+      <c r="C80" t="s">
+        <v>506</v>
+      </c>
+      <c r="D80" t="s">
+        <v>48</v>
+      </c>
+      <c r="E80" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F80" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G80" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H80" t="s">
+        <v>52</v>
+      </c>
+      <c r="I80" t="s">
+        <v>53</v>
+      </c>
+      <c r="J80" t="s">
+        <v>54</v>
+      </c>
+      <c r="K80" t="s">
+        <v>321</v>
+      </c>
+      <c r="L80" t="s">
+        <v>1000</v>
+      </c>
+      <c r="M80" t="s">
+        <v>212</v>
+      </c>
+      <c r="N80" t="s">
+        <v>57</v>
+      </c>
+      <c r="O80" t="s">
+        <v>58</v>
+      </c>
+      <c r="P80" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>60</v>
+      </c>
+      <c r="R80" t="s">
+        <v>88</v>
+      </c>
+      <c r="S80" t="s">
+        <v>61</v>
+      </c>
+      <c r="T80" t="s">
+        <v>1006</v>
+      </c>
+      <c r="U80" s="1">
+        <v>4010.2</v>
+      </c>
+      <c r="V80" s="1">
+        <v>3984.5</v>
+      </c>
+      <c r="W80" s="1">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="X80" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z80" s="1">
+        <v>1228</v>
+      </c>
+      <c r="AA80" s="1">
+        <v>4924525.5999999996</v>
+      </c>
+      <c r="AB80" s="1">
+        <v>64838.400000000001</v>
+      </c>
+      <c r="AC80" s="1">
+        <v>5214176</v>
+      </c>
+      <c r="AD80" s="1">
+        <v>17100</v>
+      </c>
+      <c r="AE80" s="1">
+        <v>225292.5</v>
+      </c>
+      <c r="AF80" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH80" t="s">
+        <v>1007</v>
+      </c>
+      <c r="AI80" s="1">
+        <v>17100</v>
+      </c>
+      <c r="AJ80" s="1">
+        <v>30880</v>
+      </c>
+      <c r="AK80" s="1">
+        <v>176832</v>
+      </c>
+      <c r="AL80" s="1">
+        <v>64838.400000000001</v>
+      </c>
+      <c r="AM80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO80" s="1">
+        <v>260709</v>
+      </c>
+      <c r="AP80" s="1">
+        <v>289650.40000000002</v>
+      </c>
+      <c r="AQ80" s="1">
+        <v>5474885</v>
+      </c>
+      <c r="AR80" s="1">
+        <v>5717277.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>45</v>
+      </c>
+      <c r="B81" t="s">
+        <v>46</v>
+      </c>
+      <c r="C81" t="s">
+        <v>506</v>
+      </c>
+      <c r="D81" t="s">
+        <v>48</v>
+      </c>
+      <c r="E81" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F81" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G81" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H81" t="s">
+        <v>52</v>
+      </c>
+      <c r="I81" t="s">
+        <v>53</v>
+      </c>
+      <c r="J81" t="s">
+        <v>54</v>
+      </c>
+      <c r="K81" t="s">
+        <v>666</v>
+      </c>
+      <c r="L81" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M81" t="s">
+        <v>56</v>
+      </c>
+      <c r="N81" t="s">
+        <v>57</v>
+      </c>
+      <c r="O81" t="s">
+        <v>58</v>
+      </c>
+      <c r="P81" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>60</v>
+      </c>
+      <c r="R81" t="s">
+        <v>88</v>
+      </c>
+      <c r="S81" t="s">
+        <v>61</v>
+      </c>
+      <c r="T81" t="s">
+        <v>1041</v>
+      </c>
+      <c r="U81" s="1">
+        <v>3965.6</v>
+      </c>
+      <c r="V81" s="1">
+        <v>3787.7</v>
+      </c>
+      <c r="W81" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="X81" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z81" s="1">
+        <v>1228</v>
+      </c>
+      <c r="AA81" s="1">
+        <v>4869756.8</v>
+      </c>
+      <c r="AB81" s="1">
+        <v>982.4</v>
+      </c>
+      <c r="AC81" s="1">
+        <v>4943280</v>
+      </c>
+      <c r="AD81" s="1">
+        <v>17100</v>
+      </c>
+      <c r="AE81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH81" t="s">
+        <v>1042</v>
+      </c>
+      <c r="AI81" s="1">
+        <v>17100</v>
+      </c>
+      <c r="AJ81" s="1">
+        <v>30880</v>
+      </c>
+      <c r="AK81" s="1">
+        <v>24560</v>
+      </c>
+      <c r="AL81" s="1">
+        <v>982.4</v>
+      </c>
+      <c r="AM81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO81" s="1">
+        <v>247164</v>
+      </c>
+      <c r="AP81" s="1">
+        <v>73522.399999999994</v>
+      </c>
+      <c r="AQ81" s="1">
+        <v>5190444</v>
+      </c>
+      <c r="AR81" s="1">
+        <v>5207544</v>
+      </c>
+    </row>
+    <row r="82" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>45</v>
+      </c>
+      <c r="B82" t="s">
+        <v>46</v>
+      </c>
+      <c r="C82" t="s">
+        <v>506</v>
+      </c>
+      <c r="D82" t="s">
+        <v>48</v>
+      </c>
+      <c r="E82" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F82" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G82" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H82" t="s">
+        <v>52</v>
+      </c>
+      <c r="I82" t="s">
+        <v>53</v>
+      </c>
+      <c r="J82" t="s">
+        <v>54</v>
+      </c>
+      <c r="K82" t="s">
+        <v>671</v>
+      </c>
+      <c r="L82" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M82" t="s">
+        <v>212</v>
+      </c>
+      <c r="N82" t="s">
+        <v>57</v>
+      </c>
+      <c r="O82" t="s">
+        <v>58</v>
+      </c>
+      <c r="P82" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>60</v>
+      </c>
+      <c r="R82" t="s">
+        <v>88</v>
+      </c>
+      <c r="S82" t="s">
+        <v>61</v>
+      </c>
+      <c r="T82" t="s">
+        <v>1045</v>
+      </c>
+      <c r="U82" s="1">
+        <v>4074.2</v>
+      </c>
+      <c r="V82" s="1">
+        <v>4042.2</v>
+      </c>
+      <c r="W82" s="1">
+        <v>20.2</v>
+      </c>
+      <c r="X82" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z82" s="1">
+        <v>1228</v>
+      </c>
+      <c r="AA82" s="1">
+        <v>5003117.5999999996</v>
+      </c>
+      <c r="AB82" s="1">
+        <v>74416.800000000003</v>
+      </c>
+      <c r="AC82" s="1">
+        <v>5322475</v>
+      </c>
+      <c r="AD82" s="1">
+        <v>26100</v>
+      </c>
+      <c r="AE82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH82" t="s">
+        <v>1046</v>
+      </c>
+      <c r="AI82" s="1">
+        <v>17400</v>
+      </c>
+      <c r="AJ82" s="1">
+        <v>61760</v>
+      </c>
+      <c r="AK82" s="1">
+        <v>165780</v>
+      </c>
+      <c r="AL82" s="1">
+        <v>74416.800000000003</v>
+      </c>
+      <c r="AM82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO82" s="1">
+        <v>266124</v>
+      </c>
+      <c r="AP82" s="1">
+        <v>319356.79999999999</v>
+      </c>
+      <c r="AQ82" s="1">
+        <v>5588599</v>
+      </c>
+      <c r="AR82" s="1">
+        <v>5614699</v>
+      </c>
+    </row>
+    <row r="83" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>45</v>
+      </c>
+      <c r="B83" t="s">
+        <v>46</v>
+      </c>
+      <c r="C83" t="s">
+        <v>506</v>
+      </c>
+      <c r="D83" t="s">
+        <v>48</v>
+      </c>
+      <c r="E83" t="s">
+        <v>987</v>
+      </c>
+      <c r="F83" t="s">
+        <v>664</v>
+      </c>
+      <c r="G83" t="s">
+        <v>988</v>
+      </c>
+      <c r="H83" t="s">
+        <v>52</v>
+      </c>
+      <c r="I83" t="s">
+        <v>53</v>
+      </c>
+      <c r="J83" t="s">
+        <v>54</v>
+      </c>
+      <c r="K83" t="s">
+        <v>350</v>
+      </c>
+      <c r="L83" t="s">
+        <v>664</v>
+      </c>
+      <c r="M83" t="s">
+        <v>56</v>
+      </c>
+      <c r="N83" t="s">
+        <v>57</v>
+      </c>
+      <c r="O83" t="s">
+        <v>58</v>
+      </c>
+      <c r="P83" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>60</v>
+      </c>
+      <c r="R83" t="s">
+        <v>48</v>
+      </c>
+      <c r="S83" t="s">
+        <v>61</v>
+      </c>
+      <c r="T83" t="s">
+        <v>989</v>
+      </c>
+      <c r="U83" s="1">
+        <v>3989.6</v>
+      </c>
+      <c r="V83" s="1">
+        <v>3759.2</v>
+      </c>
+      <c r="W83" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="X83" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z83" s="1">
+        <v>1228</v>
+      </c>
+      <c r="AA83" s="1">
+        <v>4899228.8</v>
+      </c>
+      <c r="AB83" s="1">
+        <v>2947.2</v>
+      </c>
+      <c r="AC83" s="1">
+        <v>4970104</v>
+      </c>
+      <c r="AD83" s="1">
+        <v>8700</v>
+      </c>
+      <c r="AE83" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH83" t="s">
+        <v>990</v>
+      </c>
+      <c r="AI83" s="1">
+        <v>17400</v>
+      </c>
+      <c r="AJ83" s="1">
+        <v>30880</v>
+      </c>
+      <c r="AK83" s="1">
+        <v>19648</v>
+      </c>
+      <c r="AL83" s="1">
+        <v>2947.2</v>
+      </c>
+      <c r="AM83" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN83" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO83" s="1">
+        <v>248506</v>
+      </c>
+      <c r="AP83" s="1">
+        <v>70875.199999999997</v>
+      </c>
+      <c r="AQ83" s="1">
+        <v>5218610</v>
+      </c>
+      <c r="AR83" s="1">
+        <v>5227310</v>
+      </c>
+    </row>
+    <row r="84" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>45</v>
+      </c>
+      <c r="B84" t="s">
+        <v>46</v>
+      </c>
+      <c r="C84" t="s">
+        <v>506</v>
+      </c>
+      <c r="D84" t="s">
+        <v>48</v>
+      </c>
+      <c r="E84" t="s">
+        <v>991</v>
+      </c>
+      <c r="F84" t="s">
+        <v>664</v>
+      </c>
+      <c r="G84" t="s">
+        <v>992</v>
+      </c>
+      <c r="H84" t="s">
+        <v>52</v>
+      </c>
+      <c r="I84" t="s">
+        <v>53</v>
+      </c>
+      <c r="J84" t="s">
+        <v>54</v>
+      </c>
+      <c r="K84" t="s">
+        <v>355</v>
+      </c>
+      <c r="L84" t="s">
+        <v>664</v>
+      </c>
+      <c r="M84" t="s">
+        <v>212</v>
+      </c>
+      <c r="N84" t="s">
+        <v>57</v>
+      </c>
+      <c r="O84" t="s">
+        <v>58</v>
+      </c>
+      <c r="P84" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>60</v>
+      </c>
+      <c r="R84" t="s">
+        <v>48</v>
+      </c>
+      <c r="S84" t="s">
+        <v>61</v>
+      </c>
+      <c r="T84" t="s">
+        <v>993</v>
+      </c>
+      <c r="U84" s="1">
+        <v>3822.4</v>
+      </c>
+      <c r="V84" s="1">
+        <v>3799.7</v>
+      </c>
+      <c r="W84" s="1">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="X84" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z84" s="1">
+        <v>1228</v>
+      </c>
+      <c r="AA84" s="1">
+        <v>4693907.2</v>
+      </c>
+      <c r="AB84" s="1">
+        <v>75153.600000000006</v>
+      </c>
+      <c r="AC84" s="1">
+        <v>5035205</v>
+      </c>
+      <c r="AD84" s="1">
+        <v>24750</v>
+      </c>
+      <c r="AE84" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH84" t="s">
+        <v>994</v>
+      </c>
+      <c r="AI84" s="1">
+        <v>16500</v>
+      </c>
+      <c r="AJ84" s="1">
+        <v>61760</v>
+      </c>
+      <c r="AK84" s="1">
         <v>187884</v>
       </c>
-      <c r="AL76" s="1">
+      <c r="AL84" s="1">
         <v>75153.600000000006</v>
       </c>
-      <c r="AM76" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN76" s="1">
-        <v>0</v>
-      </c>
-      <c r="AO76" s="1">
+      <c r="AM84" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN84" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="1">
         <v>251761</v>
       </c>
-      <c r="AP76" s="1">
+      <c r="AP84" s="1">
         <v>341297.6</v>
       </c>
-      <c r="AQ76" s="1">
+      <c r="AQ84" s="1">
         <v>5286966</v>
       </c>
-      <c r="AR76" s="1">
+      <c r="AR84" s="1">
         <v>5311716</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR73" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>